--- a/English1.xlsx
+++ b/English1.xlsx
@@ -27,21 +27,21 @@
     <t>status</t>
   </si>
   <si>
+    <t>question</t>
+  </si>
+  <si>
     <t>answers</t>
   </si>
   <si>
     <t>correctAnswer</t>
   </si>
   <si>
-    <t>question</t>
+    <t>What is the name of a person that starts with the letter 'B'?</t>
   </si>
   <si>
     <t>Bill</t>
   </si>
   <si>
-    <t>What is the name of a person that starts with the letter 'B'?</t>
-  </si>
-  <si>
     <t>ball</t>
   </si>
   <si>
@@ -60,12 +60,12 @@
     <t>What item do you read that contains stories or information?</t>
   </si>
   <si>
+    <t>What is his name?</t>
+  </si>
+  <si>
     <t>Ba</t>
   </si>
   <si>
-    <t>What is his name?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rearrange our letters: k/o/b/o </t>
   </si>
   <si>
@@ -78,48 +78,48 @@
     <t>obok</t>
   </si>
   <si>
+    <t xml:space="preserve">Rearrange our letters: i/k/b/e </t>
+  </si>
+  <si>
     <t>beki</t>
   </si>
   <si>
-    <t xml:space="preserve">Rearrange our letters: i/k/b/e </t>
-  </si>
-  <si>
     <t>kibe</t>
   </si>
   <si>
     <t>kebi</t>
   </si>
   <si>
+    <t xml:space="preserve">Rearrange our letters: l/B/l/i </t>
+  </si>
+  <si>
     <t>lilb</t>
   </si>
   <si>
-    <t xml:space="preserve">Rearrange our letters: l/B/l/i </t>
-  </si>
-  <si>
     <t>illb</t>
   </si>
   <si>
     <t>Blli</t>
   </si>
   <si>
+    <t xml:space="preserve">Rearrange our letters: l/a/l/b </t>
+  </si>
+  <si>
     <t>lalb</t>
   </si>
   <si>
-    <t xml:space="preserve">Rearrange our letters: l/a/l/b </t>
-  </si>
-  <si>
     <t>abll</t>
   </si>
   <si>
     <t>blla</t>
   </si>
   <si>
+    <t xml:space="preserve">Rearrange our letters: y/b/e </t>
+  </si>
+  <si>
     <t>bye</t>
   </si>
   <si>
-    <t xml:space="preserve">Rearrange our letters: y/b/e </t>
-  </si>
-  <si>
     <t>ybe</t>
   </si>
   <si>
@@ -129,12 +129,12 @@
     <t>bey</t>
   </si>
   <si>
+    <t>What pet is known for saying "meow"?</t>
+  </si>
+  <si>
     <t>cat</t>
   </si>
   <si>
-    <t>What pet is known for saying "meow"?</t>
-  </si>
-  <si>
     <t>car</t>
   </si>
   <si>
@@ -153,18 +153,18 @@
     <t>What do you use to drink tea or coffee?</t>
   </si>
   <si>
+    <t>What do you call your father in a simple and affectionate way?</t>
+  </si>
+  <si>
     <t>dad</t>
   </si>
   <si>
-    <t>What do you call your father in a simple and affectionate way?</t>
+    <t>Rearrange our letters: a/r/c</t>
   </si>
   <si>
     <t>arc</t>
   </si>
   <si>
-    <t>Rearrange our letters: a/r/c</t>
-  </si>
-  <si>
     <t>rac</t>
   </si>
   <si>
@@ -195,33 +195,33 @@
     <t>pcu</t>
   </si>
   <si>
+    <t>Rearrange our letters: a/k/c/e</t>
+  </si>
+  <si>
     <t>ceka</t>
   </si>
   <si>
-    <t>Rearrange our letters: a/k/c/e</t>
-  </si>
-  <si>
     <t>kace</t>
   </si>
   <si>
     <t>keca</t>
   </si>
   <si>
+    <t>Rearrange our letters: d/a/d</t>
+  </si>
+  <si>
     <t>dda</t>
   </si>
   <si>
-    <t>Rearrange our letters: d/a/d</t>
-  </si>
-  <si>
     <t>add</t>
   </si>
   <si>
+    <t>What is the verb that means to be able to do something?</t>
+  </si>
+  <si>
     <t>can</t>
   </si>
   <si>
-    <t>What is the verb that means to be able to do something?</t>
-  </si>
-  <si>
     <t>bar</t>
   </si>
   <si>
@@ -240,18 +240,18 @@
     <t>What is something people wear on their heads to protect from the sun or cold?</t>
   </si>
   <si>
+    <t xml:space="preserve">What do you call an item used to carry things, often made of plastic, cloth, or leather? </t>
+  </si>
+  <si>
     <t>bag</t>
   </si>
   <si>
-    <t xml:space="preserve">What do you call an item used to carry things, often made of plastic, cloth, or leather? </t>
+    <t>h_t</t>
   </si>
   <si>
     <t>a</t>
   </si>
   <si>
-    <t>h_t</t>
-  </si>
-  <si>
     <t>e</t>
   </si>
   <si>
@@ -261,33 +261,33 @@
     <t>u</t>
   </si>
   <si>
+    <t>ca_</t>
+  </si>
+  <si>
     <t>Quả trứng</t>
   </si>
   <si>
-    <t>ca_</t>
-  </si>
-  <si>
     <t>n</t>
   </si>
   <si>
     <t>_pple</t>
   </si>
   <si>
+    <t>_ag</t>
+  </si>
+  <si>
     <t>b</t>
   </si>
   <si>
-    <t>_ag</t>
-  </si>
-  <si>
     <t>c_t</t>
   </si>
   <si>
+    <t>What is the term for a young female child?</t>
+  </si>
+  <si>
     <t>Girl</t>
   </si>
   <si>
-    <t>What is the term for a young female child?</t>
-  </si>
-  <si>
     <t>Boy</t>
   </si>
   <si>
@@ -297,78 +297,78 @@
     <t>Baby</t>
   </si>
   <si>
+    <t>What do you call a place where people grow flowers, vegetables, and plants?</t>
+  </si>
+  <si>
     <t>Garden</t>
   </si>
   <si>
-    <t>What do you call a place where people grow flowers, vegetables, and plants?</t>
-  </si>
-  <si>
     <t>Field</t>
   </si>
   <si>
     <t>Grass field</t>
   </si>
   <si>
+    <t>What is the structure that you open and close to enter a yard or a fenced area?</t>
+  </si>
+  <si>
     <t>Gate</t>
   </si>
   <si>
-    <t>What is the structure that you open and close to enter a yard or a fenced area?</t>
-  </si>
-  <si>
     <t>Chick</t>
   </si>
   <si>
+    <t>Which farm animal is known for having horns and eating grass?</t>
+  </si>
+  <si>
     <t>Cow</t>
   </si>
   <si>
     <t>Goat</t>
   </si>
   <si>
-    <t>Which farm animal is known for having horns and eating grass?</t>
-  </si>
-  <si>
     <t>Mouse</t>
   </si>
   <si>
     <t>Horse</t>
   </si>
   <si>
+    <t>How would you describe that specific garden in the distance?</t>
+  </si>
+  <si>
     <t>The goat over there</t>
   </si>
   <si>
     <t>The garden over there</t>
   </si>
   <si>
-    <t>How would you describe that specific garden in the distance?</t>
-  </si>
-  <si>
     <t>The cow over there</t>
   </si>
   <si>
     <t>The grass field over there</t>
   </si>
   <si>
+    <t>What is the part of the body that contains the brain, eyes, nose, and mouth?</t>
+  </si>
+  <si>
     <t>Foot</t>
   </si>
   <si>
     <t>Head</t>
   </si>
   <si>
-    <t>What is the part of the body that contains the brain, eyes, nose, and mouth?</t>
-  </si>
-  <si>
     <t>Hand</t>
   </si>
   <si>
     <t>Eye</t>
   </si>
   <si>
+    <t>What grows on your head and can be short, long, curly, or straight?</t>
+  </si>
+  <si>
     <t>Hair</t>
   </si>
   <si>
-    <t>What grows on your head and can be short, long, curly, or straight?</t>
-  </si>
-  <si>
     <t>Ear</t>
   </si>
   <si>
@@ -378,42 +378,42 @@
     <t>Shoulder</t>
   </si>
   <si>
+    <t>Who has short hair?</t>
+  </si>
+  <si>
     <t>Hoa has long hair.</t>
   </si>
   <si>
     <t>Hoa has a short hair</t>
   </si>
   <si>
-    <t>Who has short hair?</t>
-  </si>
-  <si>
     <t>Hoa has hair.</t>
   </si>
   <si>
     <t>Hoa has beautiful hair.</t>
   </si>
   <si>
+    <t>Which two body parts are mentioned in this sentence: 'Your ___ and your ___', where one is used for holding things and the other contains the brain?</t>
+  </si>
+  <si>
     <t>Your hands and your feet.</t>
   </si>
   <si>
     <t>Your hand and your head</t>
   </si>
   <si>
-    <t>Which two body parts are mentioned in this sentence: 'Your ___ and your ___', where one is used for holding things and the other contains the brain?</t>
-  </si>
-  <si>
     <t>Your head and your feet.</t>
   </si>
   <si>
     <t>Your feet and your head.</t>
   </si>
   <si>
+    <t xml:space="preserve">What do we use to store or carry things, usually made of cardboard or plastic? </t>
+  </si>
+  <si>
     <t>Boxes</t>
   </si>
   <si>
-    <t xml:space="preserve">What do we use to store or carry things, usually made of cardboard or plastic? </t>
-  </si>
-  <si>
     <t>Pots</t>
   </si>
   <si>
@@ -423,28 +423,31 @@
     <t>Pans</t>
   </si>
   <si>
+    <t>What do we use to store liquids, often made of glass or plastic?</t>
+  </si>
+  <si>
     <t>Bottles</t>
   </si>
   <si>
-    <t>What do we use to store liquids, often made of glass or plastic?</t>
-  </si>
-  <si>
     <t>Barrels</t>
   </si>
   <si>
     <t>Bowls</t>
   </si>
   <si>
+    <t>What cleaning tool is used to wipe floors?</t>
+  </si>
+  <si>
     <t>Mops</t>
   </si>
   <si>
-    <t>What cleaning tool is used to wipe floors?</t>
+    <t>What kitchen item is used for cooking soups and stews?</t>
   </si>
   <si>
     <t>Brooms</t>
   </si>
   <si>
-    <t>What kitchen item is used for cooking soups and stews?</t>
+    <t>What is this object? (made of cardboard)</t>
   </si>
   <si>
     <t>This is a pot</t>
@@ -453,24 +456,21 @@
     <t>This is a box</t>
   </si>
   <si>
-    <t>What is this object? (made of cardboard)</t>
-  </si>
-  <si>
     <t>This is a bottle</t>
   </si>
   <si>
     <t xml:space="preserve"> This is a bowl</t>
   </si>
   <si>
+    <t>What do we call a female parent?</t>
+  </si>
+  <si>
     <t>Grandmother</t>
   </si>
   <si>
     <t>Mother</t>
   </si>
   <si>
-    <t>What do we call a female parent?</t>
-  </si>
-  <si>
     <t>Father</t>
   </si>
   <si>
@@ -486,21 +486,21 @@
     <t>Dog</t>
   </si>
   <si>
+    <t>Which animal is known for climbing trees and eating bananas?</t>
+  </si>
+  <si>
     <t>Duck</t>
   </si>
   <si>
     <t>Monkey</t>
   </si>
   <si>
-    <t>Which animal is known for climbing trees and eating bananas?</t>
+    <t>How does Mary look?</t>
   </si>
   <si>
     <t>Mary looks so beautiful</t>
   </si>
   <si>
-    <t>How does Mary look?</t>
-  </si>
-  <si>
     <t>Mary is not very pretty</t>
   </si>
   <si>
@@ -510,28 +510,28 @@
     <t>Mary studies very well</t>
   </si>
   <si>
+    <t>How many mice are there?</t>
+  </si>
+  <si>
     <t>There are two cats</t>
   </si>
   <si>
     <t>There are two mouses</t>
   </si>
   <si>
-    <t>How many mice are there?</t>
-  </si>
-  <si>
     <t>There are three mice</t>
   </si>
   <si>
     <t>There are three cats</t>
-  </si>
-  <si>
-    <t>What’s your name?</t>
   </si>
   <si>
     <t>Rearrange our words:
  name/?/ What’s/ your/</t>
   </si>
   <si>
+    <t>What’s your name?</t>
+  </si>
+  <si>
     <t>What’s name your?</t>
   </si>
   <si>
@@ -539,49 +539,49 @@
   </si>
   <si>
     <t>What’s name? your</t>
-  </si>
-  <si>
-    <t>some desks. I have</t>
-  </si>
-  <si>
-    <t>I have some desks.</t>
   </si>
   <si>
     <t>Rearrange our words:
  desks./ I/ some/ have</t>
   </si>
   <si>
+    <t>some desks. I have</t>
+  </si>
+  <si>
+    <t>I have some desks.</t>
+  </si>
+  <si>
     <t>I have desks. some</t>
   </si>
   <si>
     <t>I some desks. have</t>
-  </si>
-  <si>
-    <t>Open book your.</t>
-  </si>
-  <si>
-    <t>Open your book.</t>
   </si>
   <si>
     <t>Rearrange our words:
  book/ your/ Open/ ./</t>
   </si>
   <si>
+    <t>Open book your.</t>
+  </si>
+  <si>
+    <t>Open your book.</t>
+  </si>
+  <si>
     <t>your book Open.</t>
   </si>
   <si>
     <t>your Open book.</t>
   </si>
   <si>
+    <t>What is a soft toy that looks like a bear?</t>
+  </si>
+  <si>
     <t>Truck</t>
   </si>
   <si>
     <t>Teddy bear</t>
   </si>
   <si>
-    <t>What is a soft toy that looks like a bear?</t>
-  </si>
-  <si>
     <t>Eraser</t>
   </si>
   <si>
@@ -591,10 +591,10 @@
     <t>What is a large vehicle used to transport goods?</t>
   </si>
   <si>
+    <t>What is a toy that flies in the sky when the wind blows?</t>
+  </si>
+  <si>
     <t>Kite</t>
-  </si>
-  <si>
-    <t>What is a toy that flies in the sky when the wind blows?</t>
   </si>
   <si>
     <t>What do students use to remove pencil marks?</t>
@@ -614,16 +614,16 @@
   C _ r</t>
   </si>
   <si>
-    <t>i/p</t>
-  </si>
-  <si>
-    <t>i/t</t>
-  </si>
-  <si>
     <t>Fill in the missing letter:
   S _ s _ er</t>
   </si>
   <si>
+    <t>i/p</t>
+  </si>
+  <si>
+    <t>i/t</t>
+  </si>
+  <si>
     <t>o/p</t>
   </si>
   <si>
@@ -638,29 +638,29 @@
   T _ y</t>
   </si>
   <si>
-    <t>is father Where?</t>
-  </si>
-  <si>
-    <t>Where is father?</t>
-  </si>
-  <si>
     <t>Rearrange our words:
  Where/ father/ is/ ?/</t>
   </si>
   <si>
+    <t>is father Where?</t>
+  </si>
+  <si>
+    <t>Where is father?</t>
+  </si>
+  <si>
     <t>Where father is?</t>
   </si>
   <si>
     <t>is Where father?</t>
-  </si>
-  <si>
-    <t>He is in bedroom.</t>
   </si>
   <si>
     <t>Rearrange our words:
  in/ bedroom/ is/ He/ ./</t>
   </si>
   <si>
+    <t>He is in bedroom.</t>
+  </si>
+  <si>
     <t>He in is bedroom.</t>
   </si>
   <si>
@@ -668,50 +668,50 @@
   </si>
   <si>
     <t>He in bedroom is.</t>
-  </si>
-  <si>
-    <t>It is brother my.</t>
-  </si>
-  <si>
-    <t>It is my brother.</t>
   </si>
   <si>
     <t>Rearrange our words:
  my/ It/ brother/ is/ ./</t>
   </si>
   <si>
+    <t>It is brother my.</t>
+  </si>
+  <si>
+    <t>It is my brother.</t>
+  </si>
+  <si>
     <t>is It my brother.</t>
   </si>
   <si>
     <t>It my brother is.</t>
-  </si>
-  <si>
-    <t>have I a ball.</t>
-  </si>
-  <si>
-    <t>I have a ball.</t>
   </si>
   <si>
     <t>Rearrange our words:
  ball/ I/ a/ have/ ./</t>
   </si>
   <si>
+    <t>have I a ball.</t>
+  </si>
+  <si>
+    <t>I have a ball.</t>
+  </si>
+  <si>
     <t>I a have ball.</t>
   </si>
   <si>
     <t>I have ball a.</t>
-  </si>
-  <si>
-    <t>my grandfather love I.</t>
-  </si>
-  <si>
-    <t>I love my grandfather.</t>
   </si>
   <si>
     <t>Rearrange our words:
  love/ my/ I/ grandfather/ ./</t>
   </si>
   <si>
+    <t>my grandfather love I.</t>
+  </si>
+  <si>
+    <t>I love my grandfather.</t>
+  </si>
+  <si>
     <t>I my grandfather love.</t>
   </si>
   <si>
@@ -753,13 +753,13 @@
   n_se</t>
   </si>
   <si>
-    <t>r</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fill in the missing letter: 
   a_m </t>
   </si>
   <si>
+    <t>r</t>
+  </si>
+  <si>
     <t>t</t>
   </si>
   <si>
@@ -797,10 +797,10 @@
     <t>ten</t>
   </si>
   <si>
+    <t>sister</t>
+  </si>
+  <si>
     <t>queen</t>
-  </si>
-  <si>
-    <t>sister</t>
   </si>
   <si>
     <t>water</t>
@@ -841,13 +841,13 @@
 c...t</t>
   </si>
   <si>
-    <t>s</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fill in the missing letter:
 fi...h </t>
   </si>
   <si>
+    <t>s</t>
+  </si>
+  <si>
     <t>c</t>
   </si>
   <si>
@@ -867,42 +867,42 @@
 h..n</t>
   </si>
   <si>
+    <t>Hi! How are you?</t>
+  </si>
+  <si>
     <t>down, please.</t>
   </si>
   <si>
     <t>Fine, Thank you.</t>
   </si>
   <si>
-    <t>Hi! How are you?</t>
-  </si>
-  <si>
     <t>school every day.</t>
   </si>
   <si>
     <t>is in the garden.</t>
   </si>
   <si>
+    <t>Look at ...</t>
+  </si>
+  <si>
     <t>the board, please.</t>
   </si>
   <si>
-    <t>Look at ...</t>
-  </si>
-  <si>
     <t>I go to ...</t>
   </si>
   <si>
     <t>are in the garden.</t>
   </si>
   <si>
+    <t>3  + 1 =  ?</t>
+  </si>
+  <si>
     <t>One</t>
   </si>
   <si>
     <t>Four</t>
   </si>
   <si>
-    <t>3  + 1 =  ?</t>
-  </si>
-  <si>
     <t>Two</t>
   </si>
   <si>
@@ -915,15 +915,15 @@
     <t>The goat and the pig ...</t>
   </si>
   <si>
+    <t>The ___________ is running in the park.</t>
+  </si>
+  <si>
     <t>down</t>
   </si>
   <si>
     <t>horse</t>
   </si>
   <si>
-    <t>The ___________ is running in the park.</t>
-  </si>
-  <si>
     <t>school</t>
   </si>
   <si>
@@ -948,10 +948,10 @@
     <t>The goat and ___________ are in the garden.</t>
   </si>
   <si>
+    <t>The ___________ is finding food in the garden.</t>
+  </si>
+  <si>
     <t>up</t>
-  </si>
-  <si>
-    <t>The ___________ is finding food in the garden.</t>
   </si>
   <si>
     <t>Five</t>
@@ -964,20 +964,20 @@
 p_n</t>
   </si>
   <si>
-    <t>k</t>
-  </si>
-  <si>
-    <t>h</t>
-  </si>
-  <si>
     <t>Fill in the missing letter:
 _orse</t>
   </si>
   <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>___ apple</t>
+  </si>
+  <si>
     <t>an</t>
-  </si>
-  <si>
-    <t>___ apple</t>
   </si>
   <si>
     <t>many</t>
@@ -1053,15 +1053,15 @@
     <t>How many letters are there in the alphabet?</t>
   </si>
   <si>
+    <t>What color is the sky?</t>
+  </si>
+  <si>
     <t>Green</t>
   </si>
   <si>
     <t>Blue</t>
   </si>
   <si>
-    <t>What color is the sky?</t>
-  </si>
-  <si>
     <t>Red</t>
   </si>
   <si>
@@ -1074,12 +1074,12 @@
     <t>Sheep</t>
   </si>
   <si>
+    <t>What do we use to write?</t>
+  </si>
+  <si>
     <t>Pen</t>
   </si>
   <si>
-    <t>What do we use to write?</t>
-  </si>
-  <si>
     <t>Ball</t>
   </si>
   <si>
@@ -1092,22 +1092,25 @@
     <t>What is 2 + 2?</t>
   </si>
   <si>
+    <t>Which fruit is red?</t>
+  </si>
+  <si>
     <t>Banana</t>
   </si>
   <si>
-    <t>Which fruit is red?</t>
-  </si>
-  <si>
     <t>Grape</t>
   </si>
   <si>
     <t>Orange</t>
   </si>
   <si>
+    <t>Which animal is big and gray?</t>
+  </si>
+  <si>
     <t>Elephant</t>
   </si>
   <si>
-    <t>Which animal is big and gray?</t>
+    <t>What do we drink when thirsty?</t>
   </si>
   <si>
     <t>Juice</t>
@@ -1116,9 +1119,6 @@
     <t>Water</t>
   </si>
   <si>
-    <t>What do we drink when thirsty?</t>
-  </si>
-  <si>
     <t>Milk</t>
   </si>
   <si>
@@ -1128,27 +1128,27 @@
     <t>What is 1 + 1?</t>
   </si>
   <si>
+    <t>Which season is hot?</t>
+  </si>
+  <si>
     <t>Winter</t>
   </si>
   <si>
     <t>Summer</t>
   </si>
   <si>
-    <t>Which season is hot?</t>
-  </si>
-  <si>
     <t>Spring</t>
   </si>
   <si>
     <t>Autumn</t>
   </si>
   <si>
+    <t>Which one is an insect?</t>
+  </si>
+  <si>
     <t>Butterfly</t>
   </si>
   <si>
-    <t>Which one is an insect?</t>
-  </si>
-  <si>
     <t>Fish</t>
   </si>
   <si>
@@ -1158,25 +1158,25 @@
     <t>Which animal barks?</t>
   </si>
   <si>
+    <t>What do bees make?</t>
+  </si>
+  <si>
     <t>Honey</t>
   </si>
   <si>
-    <t>What do bees make?</t>
-  </si>
-  <si>
     <t>Butter</t>
   </si>
   <si>
     <t>Cheese</t>
   </si>
   <si>
+    <t>What is the shape of the sun?</t>
+  </si>
+  <si>
     <t>Square</t>
   </si>
   <si>
     <t>Circle</t>
-  </si>
-  <si>
-    <t>What is the shape of the sun?</t>
   </si>
   <si>
     <t>Triangle</t>
@@ -1446,21 +1446,24 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="3.25"/>
-    <col customWidth="1" min="2" max="2" width="26.25"/>
-    <col customWidth="1" min="3" max="3" width="25.0"/>
-    <col customWidth="1" min="4" max="4" width="4.25"/>
-    <col customWidth="1" min="5" max="5" width="65.63"/>
+    <col customWidth="1" min="2" max="2" width="65.63"/>
+    <col customWidth="1" min="3" max="3" width="26.25"/>
+    <col customWidth="1" min="4" max="4" width="25.0"/>
+    <col customWidth="1" min="5" max="5" width="4.25"/>
     <col customWidth="1" min="6" max="6" width="6.38"/>
-    <col customWidth="1" min="7" max="26" width="8.63"/>
+    <col customWidth="1" min="8" max="26" width="8.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
       <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
@@ -1473,10 +1476,10 @@
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>0</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1">
@@ -1487,117 +1490,117 @@
         <v>6</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="2">
+        <v>7</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="2">
         <v>1.0</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>7</v>
       </c>
       <c r="F3" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1">
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1">
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
       <c r="B7" s="3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="2">
+      <c r="E7" s="2">
         <v>2.0</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
       <c r="B11" s="3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="2">
+      <c r="E11" s="2">
         <v>3.0</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1">
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" ht="12.75" customHeight="1">
       <c r="B15" s="3" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="2">
+      <c r="E15" s="2">
         <v>4.0</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="17" ht="12.75" customHeight="1">
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="18" ht="12.75" customHeight="1">
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1606,27 +1609,27 @@
         <v>14</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" s="2">
+        <v>15</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="2">
         <v>5.0</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="20" ht="12.75" customHeight="1">
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="21" ht="12.75" customHeight="1">
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="22" ht="12.75" customHeight="1">
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1635,33 +1638,33 @@
         <v>2.0</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="2">
         <v>6.0</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="F23" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="24" ht="12.75" customHeight="1">
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="25" ht="12.75" customHeight="1">
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="26" ht="12.75" customHeight="1">
-      <c r="B26" s="3" t="s">
+      <c r="C26" s="3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1670,27 +1673,27 @@
         <v>20</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="2">
+      <c r="E27" s="2">
         <v>7.0</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row r="28" ht="12.75" customHeight="1">
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="29" ht="12.75" customHeight="1">
-      <c r="B29" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="30" ht="12.75" customHeight="1">
-      <c r="B30" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1699,28 +1702,28 @@
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31" s="2">
+        <v>25</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" s="2">
         <v>8.0</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="32" ht="12.75" customHeight="1">
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="33" ht="12.75" customHeight="1">
-      <c r="B33" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="34" ht="12.75" customHeight="1">
-      <c r="B34" s="3" t="s">
-        <v>6</v>
+      <c r="C34" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="35" ht="12.75" customHeight="1">
@@ -1728,27 +1731,27 @@
         <v>28</v>
       </c>
       <c r="C35" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D35" s="2">
+      <c r="E35" s="2">
         <v>9.0</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>29</v>
-      </c>
     </row>
     <row r="36" ht="12.75" customHeight="1">
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="37" ht="12.75" customHeight="1">
-      <c r="B37" s="3" t="s">
+      <c r="C37" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="38" ht="12.75" customHeight="1">
-      <c r="B38" s="3" t="s">
+      <c r="C38" s="3" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1757,27 +1760,27 @@
         <v>32</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D39" s="2">
+        <v>33</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E39" s="2">
         <v>10.0</v>
       </c>
-      <c r="E39" s="3" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="40" ht="12.75" customHeight="1">
-      <c r="B40" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="41" ht="12.75" customHeight="1">
-      <c r="B41" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="42" ht="12.75" customHeight="1">
-      <c r="B42" s="3" t="s">
+      <c r="C42" s="3" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1789,117 +1792,117 @@
         <v>37</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D43" s="2">
+        <v>38</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E43" s="2">
         <v>11.0</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F43" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="44" ht="12.75" customHeight="1">
-      <c r="B44" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="45" ht="12.75" customHeight="1">
-      <c r="B45" s="3" t="s">
+      <c r="C45" s="3" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="46" ht="12.75" customHeight="1">
-      <c r="B46" s="3" t="s">
+      <c r="C46" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="47" ht="12.75" customHeight="1">
       <c r="B47" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C47" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D47" s="2">
+      <c r="E47" s="2">
         <v>12.0</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>42</v>
-      </c>
     </row>
     <row r="48" ht="12.75" customHeight="1">
-      <c r="B48" s="3" t="s">
+      <c r="C48" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="49" ht="12.75" customHeight="1">
-      <c r="B49" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="50" ht="12.75" customHeight="1">
-      <c r="B50" s="3" t="s">
+      <c r="C50" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="51" ht="12.75" customHeight="1">
       <c r="B51" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C51" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D51" s="2">
+      <c r="E51" s="2">
         <v>13.0</v>
       </c>
-      <c r="E51" s="3" t="s">
-        <v>43</v>
-      </c>
     </row>
     <row r="52" ht="12.75" customHeight="1">
-      <c r="B52" s="3" t="s">
+      <c r="C52" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="53" ht="12.75" customHeight="1">
-      <c r="B53" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="54" ht="12.75" customHeight="1">
-      <c r="B54" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="55" ht="12.75" customHeight="1">
       <c r="B55" s="3" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C55" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D55" s="2">
+      <c r="E55" s="2">
         <v>14.0</v>
       </c>
-      <c r="E55" s="3" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="56" ht="12.75" customHeight="1">
-      <c r="B56" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="57" ht="12.75" customHeight="1">
-      <c r="B57" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="58" ht="12.75" customHeight="1">
-      <c r="B58" s="3" t="s">
+      <c r="C58" s="3" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1908,27 +1911,27 @@
         <v>45</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D59" s="2">
+        <v>46</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E59" s="2">
         <v>15.0</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>46</v>
-      </c>
     </row>
     <row r="60" ht="12.75" customHeight="1">
-      <c r="B60" s="3" t="s">
+      <c r="C60" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="61" ht="12.75" customHeight="1">
-      <c r="B61" s="3" t="s">
+      <c r="C61" s="3" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="62" ht="12.75" customHeight="1">
-      <c r="B62" s="3" t="s">
+      <c r="C62" s="3" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1940,88 +1943,88 @@
         <v>47</v>
       </c>
       <c r="C63" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D63" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D63" s="2">
+      <c r="E63" s="2">
         <v>16.0</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="F63" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="64" ht="12.75" customHeight="1">
-      <c r="B64" s="3" t="s">
+      <c r="C64" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="65" ht="12.75" customHeight="1">
-      <c r="B65" s="3" t="s">
+      <c r="C65" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="66" ht="12.75" customHeight="1">
-      <c r="B66" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="67" ht="12.75" customHeight="1">
       <c r="B67" s="3" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D67" s="2">
+        <v>38</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E67" s="2">
         <v>17.0</v>
       </c>
-      <c r="E67" s="3" t="s">
-        <v>51</v>
-      </c>
     </row>
     <row r="68" ht="12.75" customHeight="1">
-      <c r="B68" s="3" t="s">
+      <c r="C68" s="3" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="69" ht="12.75" customHeight="1">
-      <c r="B69" s="3" t="s">
+      <c r="C69" s="3" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="70" ht="12.75" customHeight="1">
-      <c r="B70" s="3" t="s">
+      <c r="C70" s="3" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="71" ht="12.75" customHeight="1">
       <c r="B71" s="3" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D71" s="2">
+      <c r="D71" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E71" s="2">
         <v>18.0</v>
       </c>
-      <c r="E71" s="3" t="s">
-        <v>55</v>
-      </c>
     </row>
     <row r="72" ht="12.75" customHeight="1">
-      <c r="B72" s="3" t="s">
+      <c r="C72" s="3" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="73" ht="12.75" customHeight="1">
-      <c r="B73" s="3" t="s">
+      <c r="C73" s="3" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="74" ht="12.75" customHeight="1">
-      <c r="B74" s="3" t="s">
+      <c r="C74" s="3" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2030,27 +2033,27 @@
         <v>59</v>
       </c>
       <c r="C75" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D75" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D75" s="2">
+      <c r="E75" s="2">
         <v>19.0</v>
       </c>
-      <c r="E75" s="3" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="76" ht="12.75" customHeight="1">
-      <c r="B76" s="3" t="s">
+      <c r="C76" s="3" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="77" ht="12.75" customHeight="1">
-      <c r="B77" s="3" t="s">
+      <c r="C77" s="3" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="78" ht="12.75" customHeight="1">
-      <c r="B78" s="3" t="s">
+      <c r="C78" s="3" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2059,27 +2062,27 @@
         <v>63</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D79" s="2">
+        <v>64</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E79" s="2">
         <v>20.0</v>
       </c>
-      <c r="E79" s="3" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="80" ht="12.75" customHeight="1">
-      <c r="B80" s="3" t="s">
-        <v>45</v>
+      <c r="C80" s="3" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="81" ht="12.75" customHeight="1">
-      <c r="B81" s="3" t="s">
+      <c r="C81" s="3" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="82" ht="12.75" customHeight="1">
-      <c r="B82" s="3" t="s">
+      <c r="C82" s="3" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2091,147 +2094,147 @@
         <v>66</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D83" s="2">
+        <v>67</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E83" s="2">
         <v>21.0</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="F83" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="84" ht="12.75" customHeight="1">
-      <c r="B84" s="3" t="s">
+      <c r="C84" s="3" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="85" ht="12.75" customHeight="1">
-      <c r="B85" s="3" t="s">
+      <c r="C85" s="3" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="86" ht="12.75" customHeight="1">
-      <c r="B86" s="3" t="s">
+      <c r="C86" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="87" ht="12.75" customHeight="1">
       <c r="B87" s="3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C87" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D87" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D87" s="2">
+      <c r="E87" s="2">
         <v>22.0</v>
       </c>
-      <c r="E87" s="3" t="s">
-        <v>71</v>
-      </c>
     </row>
     <row r="88" ht="12.75" customHeight="1">
-      <c r="B88" s="3" t="s">
+      <c r="C88" s="3" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="89" ht="12.75" customHeight="1">
-      <c r="B89" s="3" t="s">
+      <c r="C89" s="3" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="90" ht="12.75" customHeight="1">
-      <c r="B90" s="3" t="s">
+      <c r="C90" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="91" ht="12.75" customHeight="1">
       <c r="B91" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C91" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D91" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D91" s="2">
+      <c r="E91" s="2">
         <v>23.0</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>72</v>
-      </c>
     </row>
     <row r="92" ht="12.75" customHeight="1">
-      <c r="B92" s="3" t="s">
+      <c r="C92" s="3" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="93" ht="12.75" customHeight="1">
-      <c r="B93" s="3" t="s">
+      <c r="C93" s="3" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="94" ht="12.75" customHeight="1">
-      <c r="B94" s="3" t="s">
+      <c r="C94" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="95" ht="12.75" customHeight="1">
       <c r="B95" s="3" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C95" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D95" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D95" s="2">
+      <c r="E95" s="2">
         <v>24.0</v>
       </c>
-      <c r="E95" s="3" t="s">
-        <v>73</v>
-      </c>
     </row>
     <row r="96" ht="12.75" customHeight="1">
-      <c r="B96" s="3" t="s">
+      <c r="C96" s="3" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="97" ht="12.75" customHeight="1">
-      <c r="B97" s="3" t="s">
+      <c r="C97" s="3" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="98" ht="12.75" customHeight="1">
-      <c r="B98" s="3" t="s">
+      <c r="C98" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="99" ht="12.75" customHeight="1">
       <c r="B99" s="3" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D99" s="2">
+        <v>67</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E99" s="2">
         <v>25.0</v>
       </c>
-      <c r="E99" s="3" t="s">
+    </row>
+    <row r="100" ht="12.75" customHeight="1">
+      <c r="C100" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="101" ht="12.75" customHeight="1">
+      <c r="C101" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="102" ht="12.75" customHeight="1">
+      <c r="C102" s="3" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="100" ht="12.75" customHeight="1">
-      <c r="B100" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="101" ht="12.75" customHeight="1">
-      <c r="B101" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="102" ht="12.75" customHeight="1">
-      <c r="B102" s="3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="103" ht="12.75" customHeight="1">
@@ -2242,146 +2245,146 @@
         <v>76</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D103" s="2">
+        <v>77</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E103" s="2">
         <v>26.0</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="F103" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="104" ht="12.75" customHeight="1">
-      <c r="B104" s="3" t="s">
+      <c r="C104" s="3" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="105" ht="12.75" customHeight="1">
-      <c r="B105" s="3" t="s">
+      <c r="C105" s="3" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="106" ht="12.75" customHeight="1">
-      <c r="B106" s="3" t="s">
+      <c r="C106" s="3" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="107" ht="12.75" customHeight="1">
       <c r="B107" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C107" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D107" s="2">
+      <c r="C107" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E107" s="2">
         <v>27.0</v>
       </c>
-      <c r="E107" s="3" t="s">
-        <v>82</v>
-      </c>
     </row>
     <row r="108" ht="12.75" customHeight="1">
-      <c r="B108" s="3" t="s">
+      <c r="C108" s="3" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="109" ht="12.75" customHeight="1">
-      <c r="B109" s="3" t="s">
+      <c r="C109" s="3" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="110" ht="12.75" customHeight="1">
-      <c r="B110" s="3" t="s">
+      <c r="C110" s="3" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="111" ht="12.75" customHeight="1">
       <c r="B111" s="3" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D111" s="2">
+        <v>77</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E111" s="2">
         <v>28.0</v>
       </c>
-      <c r="E111" s="3" t="s">
-        <v>84</v>
-      </c>
     </row>
     <row r="112" ht="12.75" customHeight="1">
-      <c r="B112" s="3" t="s">
+      <c r="C112" s="3" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="113" ht="12.75" customHeight="1">
-      <c r="B113" s="3" t="s">
+      <c r="C113" s="3" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="114" ht="12.75" customHeight="1">
-      <c r="B114" s="3" t="s">
+      <c r="C114" s="3" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="115" ht="12.75" customHeight="1">
       <c r="B115" s="3" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D115" s="2">
+        <v>77</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E115" s="2">
         <v>29.0</v>
       </c>
-      <c r="E115" s="3" t="s">
+    </row>
+    <row r="116" ht="12.75" customHeight="1">
+      <c r="C116" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="116" ht="12.75" customHeight="1">
-      <c r="B116" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
     <row r="117" ht="12.75" customHeight="1">
-      <c r="B117" s="3" t="s">
+      <c r="C117" s="3" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="118" ht="12.75" customHeight="1">
-      <c r="B118" s="3" t="s">
+      <c r="C118" s="3" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="119" ht="12.75" customHeight="1">
       <c r="B119" s="3" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D119" s="2">
+        <v>77</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E119" s="2">
         <v>30.0</v>
       </c>
-      <c r="E119" s="3" t="s">
-        <v>87</v>
-      </c>
     </row>
     <row r="120" ht="12.75" customHeight="1">
-      <c r="B120" s="3" t="s">
+      <c r="C120" s="3" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="121" ht="12.75" customHeight="1">
-      <c r="B121" s="3" t="s">
+      <c r="C121" s="3" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="122" ht="12.75" customHeight="1">
-      <c r="B122" s="3" t="s">
+      <c r="C122" s="3" t="s">
         <v>80</v>
       </c>
     </row>
@@ -2389,63 +2392,63 @@
       <c r="A123" s="2">
         <v>7.0</v>
       </c>
-      <c r="B123" s="2" t="s">
+      <c r="B123" s="3" t="s">
         <v>88</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D123" s="2">
+        <v>89</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E123" s="2">
         <v>31.0</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="F123" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="124" ht="12.75" customHeight="1">
-      <c r="B124" s="3" t="s">
+      <c r="C124" s="3" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="125" ht="12.75" customHeight="1">
-      <c r="B125" s="3" t="s">
+      <c r="C125" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="126" ht="12.75" customHeight="1">
-      <c r="B126" s="3" t="s">
+      <c r="C126" s="3" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="127" ht="12.75" customHeight="1">
-      <c r="B127" s="2" t="s">
-        <v>88</v>
+      <c r="B127" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D127" s="2">
+        <v>89</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E127" s="2">
         <v>32.0</v>
       </c>
-      <c r="E127" s="3" t="s">
+    </row>
+    <row r="128" ht="12.75" customHeight="1">
+      <c r="C128" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="129" ht="12.75" customHeight="1">
+      <c r="C129" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="128" ht="12.75" customHeight="1">
-      <c r="B128" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="129" ht="12.75" customHeight="1">
-      <c r="B129" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
     <row r="130" ht="12.75" customHeight="1">
-      <c r="B130" s="3" t="s">
+      <c r="C130" s="3" t="s">
         <v>96</v>
       </c>
     </row>
@@ -2454,28 +2457,28 @@
         <v>97</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D131" s="2">
+        <v>98</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E131" s="2">
         <v>33.0</v>
       </c>
-      <c r="E131" s="3" t="s">
-        <v>98</v>
-      </c>
     </row>
     <row r="132" ht="12.75" customHeight="1">
-      <c r="B132" s="2" t="s">
-        <v>93</v>
+      <c r="C132" s="2" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="133" ht="12.75" customHeight="1">
-      <c r="B133" s="3" t="s">
+      <c r="C133" s="3" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="134" ht="12.75" customHeight="1">
-      <c r="B134" s="2" t="s">
-        <v>88</v>
+      <c r="C134" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="135" ht="12.75" customHeight="1">
@@ -2485,26 +2488,26 @@
       <c r="C135" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D135" s="2">
+      <c r="D135" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E135" s="2">
         <v>34.0</v>
       </c>
-      <c r="E135" s="3" t="s">
+    </row>
+    <row r="136" ht="12.75" customHeight="1">
+      <c r="C136" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="137" ht="12.75" customHeight="1">
+      <c r="C137" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="138" ht="12.75" customHeight="1">
+      <c r="C138" s="3" t="s">
         <v>102</v>
-      </c>
-    </row>
-    <row r="136" ht="12.75" customHeight="1">
-      <c r="B136" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="137" ht="12.75" customHeight="1">
-      <c r="B137" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="138" ht="12.75" customHeight="1">
-      <c r="B138" s="3" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="139" ht="12.75" customHeight="1">
@@ -2514,25 +2517,25 @@
       <c r="C139" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D139" s="2">
+      <c r="D139" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E139" s="2">
         <v>35.0</v>
       </c>
-      <c r="E139" s="3" t="s">
+    </row>
+    <row r="140" ht="12.75" customHeight="1">
+      <c r="C140" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="141" ht="12.75" customHeight="1">
+      <c r="C141" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="140" ht="12.75" customHeight="1">
-      <c r="B140" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="141" ht="12.75" customHeight="1">
-      <c r="B141" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
     <row r="142" ht="12.75" customHeight="1">
-      <c r="B142" s="3" t="s">
+      <c r="C142" s="3" t="s">
         <v>109</v>
       </c>
     </row>
@@ -2543,89 +2546,89 @@
       <c r="B143" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C143" s="2" t="s">
+      <c r="C143" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D143" s="2">
+      <c r="D143" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E143" s="2">
         <v>36.0</v>
-      </c>
-      <c r="E143" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="F143" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="144" ht="12.75" customHeight="1">
-      <c r="B144" s="3" t="s">
+      <c r="C144" s="3" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="145" ht="12.75" customHeight="1">
-      <c r="B145" s="2" t="s">
-        <v>111</v>
+      <c r="C145" s="2" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="146" ht="12.75" customHeight="1">
-      <c r="B146" s="3" t="s">
+      <c r="C146" s="3" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="147" ht="12.75" customHeight="1">
-      <c r="B147" s="2" t="s">
-        <v>111</v>
+      <c r="B147" s="3" t="s">
+        <v>115</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D147" s="2">
+        <v>112</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E147" s="2">
         <v>37.0</v>
       </c>
-      <c r="E147" s="3" t="s">
+    </row>
+    <row r="148" ht="12.75" customHeight="1">
+      <c r="C148" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="148" ht="12.75" customHeight="1">
-      <c r="B148" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
     <row r="149" ht="12.75" customHeight="1">
-      <c r="B149" s="3" t="s">
+      <c r="C149" s="3" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="150" ht="12.75" customHeight="1">
-      <c r="B150" s="3" t="s">
+      <c r="C150" s="3" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="151" ht="12.75" customHeight="1">
-      <c r="B151" s="2" t="s">
-        <v>113</v>
+      <c r="B151" s="3" t="s">
+        <v>118</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D151" s="2">
+      <c r="D151" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E151" s="2">
         <v>38.0</v>
       </c>
-      <c r="E151" s="3" t="s">
-        <v>118</v>
-      </c>
     </row>
     <row r="152" ht="12.75" customHeight="1">
-      <c r="B152" s="3" t="s">
-        <v>110</v>
+      <c r="C152" s="3" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="153" ht="12.75" customHeight="1">
-      <c r="B153" s="2" t="s">
-        <v>111</v>
+      <c r="C153" s="2" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="154" ht="12.75" customHeight="1">
-      <c r="B154" s="3" t="s">
+      <c r="C154" s="3" t="s">
         <v>119</v>
       </c>
     </row>
@@ -2633,28 +2636,28 @@
       <c r="B155" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C155" s="2" t="s">
+      <c r="C155" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D155" s="2">
+      <c r="D155" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E155" s="2">
         <v>39.0</v>
       </c>
-      <c r="E155" s="3" t="s">
+    </row>
+    <row r="156" ht="12.75" customHeight="1">
+      <c r="C156" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="157" ht="12.75" customHeight="1">
+      <c r="C157" s="2" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="156" ht="12.75" customHeight="1">
-      <c r="B156" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="157" ht="12.75" customHeight="1">
-      <c r="B157" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
     <row r="158" ht="12.75" customHeight="1">
-      <c r="B158" s="3" t="s">
+      <c r="C158" s="3" t="s">
         <v>124</v>
       </c>
     </row>
@@ -2662,28 +2665,28 @@
       <c r="B159" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C159" s="2" t="s">
+      <c r="C159" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D159" s="2">
+      <c r="D159" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E159" s="2">
         <v>40.0</v>
       </c>
-      <c r="E159" s="3" t="s">
+    </row>
+    <row r="160" ht="12.75" customHeight="1">
+      <c r="C160" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="161" ht="12.75" customHeight="1">
+      <c r="C161" s="2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="160" ht="12.75" customHeight="1">
-      <c r="B160" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="161" ht="12.75" customHeight="1">
-      <c r="B161" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
     <row r="162" ht="12.75" customHeight="1">
-      <c r="B162" s="3" t="s">
+      <c r="C162" s="3" t="s">
         <v>129</v>
       </c>
     </row>
@@ -2691,121 +2694,121 @@
       <c r="A163" s="2">
         <v>9.0</v>
       </c>
-      <c r="B163" s="2" t="s">
+      <c r="B163" s="3" t="s">
         <v>130</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D163" s="2">
+        <v>131</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E163" s="2">
         <v>41.0</v>
-      </c>
-      <c r="E163" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="F163" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="164" ht="12.75" customHeight="1">
-      <c r="B164" s="3" t="s">
+      <c r="C164" s="3" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="165" ht="12.75" customHeight="1">
-      <c r="B165" s="3" t="s">
+      <c r="C165" s="3" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="166" ht="12.75" customHeight="1">
-      <c r="B166" s="3" t="s">
+      <c r="C166" s="3" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="167" ht="12.75" customHeight="1">
       <c r="B167" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C167" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D167" s="2">
+      <c r="C167" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E167" s="2">
         <v>42.0</v>
       </c>
-      <c r="E167" s="3" t="s">
+    </row>
+    <row r="168" ht="12.75" customHeight="1">
+      <c r="C168" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="168" ht="12.75" customHeight="1">
-      <c r="B168" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
     <row r="169" ht="12.75" customHeight="1">
-      <c r="B169" s="3" t="s">
+      <c r="C169" s="3" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="170" ht="12.75" customHeight="1">
-      <c r="B170" s="3" t="s">
+      <c r="C170" s="3" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="171" ht="12.75" customHeight="1">
       <c r="B171" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C171" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C171" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="D171" s="2">
+      <c r="D171" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E171" s="2">
         <v>43.0</v>
       </c>
-      <c r="E171" s="3" t="s">
+    </row>
+    <row r="172" ht="12.75" customHeight="1">
+      <c r="C172" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="173" ht="12.75" customHeight="1">
+      <c r="C173" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="174" ht="12.75" customHeight="1">
+      <c r="C174" s="2" t="s">
         <v>140</v>
-      </c>
-    </row>
-    <row r="172" ht="12.75" customHeight="1">
-      <c r="B172" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="173" ht="12.75" customHeight="1">
-      <c r="B173" s="3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="174" ht="12.75" customHeight="1">
-      <c r="B174" s="2" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="175" ht="12.75" customHeight="1">
       <c r="B175" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C175" s="2" t="s">
+      <c r="C175" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D175" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D175" s="2">
+      <c r="E175" s="2">
         <v>44.0</v>
       </c>
-      <c r="E175" s="3" t="s">
-        <v>142</v>
-      </c>
     </row>
     <row r="176" ht="12.75" customHeight="1">
-      <c r="B176" s="3" t="s">
-        <v>130</v>
+      <c r="C176" s="3" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="177" ht="12.75" customHeight="1">
-      <c r="B177" s="2" t="s">
+      <c r="C177" s="2" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="178" ht="12.75" customHeight="1">
-      <c r="B178" s="3" t="s">
+      <c r="C178" s="3" t="s">
         <v>138</v>
       </c>
     </row>
@@ -2813,28 +2816,28 @@
       <c r="B179" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C179" s="2" t="s">
+      <c r="C179" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D179" s="2">
+      <c r="D179" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E179" s="2">
         <v>45.0</v>
       </c>
-      <c r="E179" s="3" t="s">
+    </row>
+    <row r="180" ht="12.75" customHeight="1">
+      <c r="C180" s="2" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="180" ht="12.75" customHeight="1">
-      <c r="B180" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
     <row r="181" ht="12.75" customHeight="1">
-      <c r="B181" s="3" t="s">
+      <c r="C181" s="3" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="182" ht="12.75" customHeight="1">
-      <c r="B182" s="3" t="s">
+      <c r="C182" s="3" t="s">
         <v>147</v>
       </c>
     </row>
@@ -2845,118 +2848,118 @@
       <c r="B183" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C183" s="2" t="s">
+      <c r="C183" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D183" s="2">
+      <c r="D183" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E183" s="2">
         <v>46.0</v>
-      </c>
-      <c r="E183" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="F183" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="184" ht="12.75" customHeight="1">
-      <c r="B184" s="3" t="s">
+      <c r="C184" s="3" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="185" ht="12.75" customHeight="1">
-      <c r="B185" s="2" t="s">
-        <v>149</v>
+      <c r="C185" s="2" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="186" ht="12.75" customHeight="1">
-      <c r="B186" s="3" t="s">
+      <c r="C186" s="3" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="187" ht="12.75" customHeight="1">
-      <c r="B187" s="2" t="s">
-        <v>103</v>
+      <c r="B187" s="3" t="s">
+        <v>153</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D187" s="2">
+      <c r="D187" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E187" s="2">
         <v>47.0</v>
       </c>
-      <c r="E187" s="3" t="s">
-        <v>153</v>
-      </c>
     </row>
     <row r="188" ht="12.75" customHeight="1">
-      <c r="B188" s="3" t="s">
+      <c r="C188" s="3" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="189" ht="12.75" customHeight="1">
-      <c r="B189" s="3" t="s">
+      <c r="C189" s="3" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="190" ht="12.75" customHeight="1">
-      <c r="B190" s="3" t="s">
-        <v>101</v>
+      <c r="C190" s="3" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="191" ht="12.75" customHeight="1">
       <c r="B191" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C191" s="2" t="s">
+      <c r="C191" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="D191" s="2">
+      <c r="D191" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E191" s="2">
         <v>48.0</v>
       </c>
-      <c r="E191" s="3" t="s">
+    </row>
+    <row r="192" ht="12.75" customHeight="1">
+      <c r="C192" s="2" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="192" ht="12.75" customHeight="1">
-      <c r="B192" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
     <row r="193" ht="12.75" customHeight="1">
-      <c r="B193" s="3" t="s">
+      <c r="C193" s="3" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="194" ht="12.75" customHeight="1">
-      <c r="B194" s="3" t="s">
+      <c r="C194" s="3" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="195" ht="12.75" customHeight="1">
-      <c r="B195" s="2" t="s">
+      <c r="B195" s="3" t="s">
         <v>159</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D195" s="2">
+        <v>160</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E195" s="2">
         <v>49.0</v>
       </c>
-      <c r="E195" s="3" t="s">
-        <v>160</v>
-      </c>
     </row>
     <row r="196" ht="12.75" customHeight="1">
-      <c r="B196" s="3" t="s">
+      <c r="C196" s="3" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="197" ht="12.75" customHeight="1">
-      <c r="B197" s="3" t="s">
+      <c r="C197" s="3" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="198" ht="12.75" customHeight="1">
-      <c r="B198" s="3" t="s">
+      <c r="C198" s="3" t="s">
         <v>163</v>
       </c>
     </row>
@@ -2964,121 +2967,121 @@
       <c r="B199" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C199" s="2" t="s">
+      <c r="C199" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D199" s="2">
+      <c r="D199" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E199" s="2">
         <v>50.0</v>
       </c>
-      <c r="E199" s="3" t="s">
+    </row>
+    <row r="200" ht="12.75" customHeight="1">
+      <c r="C200" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="201" ht="12.75" customHeight="1">
+      <c r="C201" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="202" ht="12.75" customHeight="1">
+      <c r="C202" s="2" t="s">
         <v>166</v>
-      </c>
-    </row>
-    <row r="200" ht="12.75" customHeight="1">
-      <c r="B200" s="3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="201" ht="12.75" customHeight="1">
-      <c r="B201" s="3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="202" ht="12.75" customHeight="1">
-      <c r="B202" s="2" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="203" ht="12.75" customHeight="1">
       <c r="A203" s="2">
         <v>11.0</v>
       </c>
-      <c r="B203" s="2" t="s">
+      <c r="B203" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D203" s="2">
+        <v>170</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E203" s="2">
         <v>51.0</v>
-      </c>
-      <c r="E203" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="F203" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="204" ht="12.75" customHeight="1">
-      <c r="B204" s="2" t="s">
+      <c r="C204" s="2" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="205" ht="12.75" customHeight="1">
-      <c r="B205" s="2" t="s">
+      <c r="C205" s="2" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="206" ht="12.75" customHeight="1">
-      <c r="B206" s="2" t="s">
+      <c r="C206" s="2" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="207" ht="12.75" customHeight="1">
-      <c r="B207" s="2" t="s">
+      <c r="B207" s="3" t="s">
         <v>174</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D207" s="2">
+      <c r="D207" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E207" s="2">
         <v>52.0</v>
       </c>
-      <c r="E207" s="3" t="s">
+    </row>
+    <row r="208" ht="12.75" customHeight="1">
+      <c r="C208" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="209" ht="12.75" customHeight="1">
+      <c r="C209" s="2" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="208" ht="12.75" customHeight="1">
-      <c r="B208" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="209" ht="12.75" customHeight="1">
-      <c r="B209" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
     <row r="210" ht="12.75" customHeight="1">
-      <c r="B210" s="2" t="s">
+      <c r="C210" s="2" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="211" ht="12.75" customHeight="1">
-      <c r="B211" s="2" t="s">
+      <c r="B211" s="3" t="s">
         <v>179</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D211" s="2">
+      <c r="D211" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E211" s="2">
         <v>53.0</v>
       </c>
-      <c r="E211" s="3" t="s">
+    </row>
+    <row r="212" ht="12.75" customHeight="1">
+      <c r="C212" s="2" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="212" ht="12.75" customHeight="1">
-      <c r="B212" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
     <row r="213" ht="12.75" customHeight="1">
-      <c r="B213" s="2" t="s">
+      <c r="C213" s="2" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="214" ht="12.75" customHeight="1">
-      <c r="B214" s="2" t="s">
+      <c r="C214" s="2" t="s">
         <v>183</v>
       </c>
     </row>
@@ -3086,208 +3089,208 @@
       <c r="B215" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C215" s="2" t="s">
+      <c r="C215" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D215" s="2">
+      <c r="D215" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E215" s="2">
         <v>54.0</v>
       </c>
-      <c r="E215" s="3" t="s">
+    </row>
+    <row r="216" ht="12.75" customHeight="1">
+      <c r="C216" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="217" ht="12.75" customHeight="1">
+      <c r="C217" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="218" ht="12.75" customHeight="1">
+      <c r="C218" s="2" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="216" ht="12.75" customHeight="1">
-      <c r="B216" s="3" t="s">
+    <row r="219" ht="12.75" customHeight="1">
+      <c r="B219" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E219" s="2">
+        <v>55.0</v>
+      </c>
+    </row>
+    <row r="220" ht="12.75" customHeight="1">
+      <c r="C220" s="3" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="217" ht="12.75" customHeight="1">
-      <c r="B217" s="3" t="s">
+    <row r="221" ht="12.75" customHeight="1">
+      <c r="C221" s="3" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="218" ht="12.75" customHeight="1">
-      <c r="B218" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="219" ht="12.75" customHeight="1">
-      <c r="B219" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C219" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D219" s="2">
-        <v>55.0</v>
-      </c>
-      <c r="E219" s="3" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="220" ht="12.75" customHeight="1">
-      <c r="B220" s="3" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="221" ht="12.75" customHeight="1">
-      <c r="B221" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
     <row r="222" ht="12.75" customHeight="1">
-      <c r="B222" s="2" t="s">
-        <v>185</v>
+      <c r="C222" s="2" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="223" ht="12.75" customHeight="1">
       <c r="A223" s="2">
         <v>12.0</v>
       </c>
-      <c r="B223" s="2" t="s">
+      <c r="B223" s="3" t="s">
         <v>190</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D223" s="2">
+        <v>191</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E223" s="2">
         <v>56.0</v>
-      </c>
-      <c r="E223" s="3" t="s">
-        <v>191</v>
       </c>
       <c r="F223" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="224" ht="12.75" customHeight="1">
-      <c r="B224" s="3" t="s">
+      <c r="C224" s="3" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="225" ht="12.75" customHeight="1">
-      <c r="B225" s="2" t="s">
+      <c r="C225" s="2" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="226" ht="12.75" customHeight="1">
-      <c r="B226" s="2" t="s">
-        <v>185</v>
+      <c r="C226" s="2" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="227" ht="12.75" customHeight="1">
-      <c r="B227" s="2" t="s">
-        <v>190</v>
+      <c r="B227" s="3" t="s">
+        <v>192</v>
       </c>
       <c r="C227" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D227" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D227" s="2">
+      <c r="E227" s="2">
         <v>57.0</v>
       </c>
-      <c r="E227" s="3" t="s">
-        <v>192</v>
-      </c>
     </row>
     <row r="228" ht="12.75" customHeight="1">
-      <c r="B228" s="2" t="s">
+      <c r="C228" s="2" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="229" ht="12.75" customHeight="1">
-      <c r="B229" s="2" t="s">
+      <c r="C229" s="2" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="230" ht="12.75" customHeight="1">
-      <c r="B230" s="2" t="s">
-        <v>190</v>
+      <c r="C230" s="2" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="231" ht="12.75" customHeight="1">
-      <c r="B231" s="2" t="s">
-        <v>190</v>
+      <c r="B231" s="3" t="s">
+        <v>193</v>
       </c>
       <c r="C231" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D231" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="D231" s="2">
+      <c r="E231" s="2">
         <v>58.0</v>
       </c>
-      <c r="E231" s="3" t="s">
-        <v>193</v>
-      </c>
     </row>
     <row r="232" ht="12.75" customHeight="1">
-      <c r="B232" s="3" t="s">
+      <c r="C232" s="3" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="233" ht="12.75" customHeight="1">
-      <c r="B233" s="2" t="s">
+      <c r="C233" s="2" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="234" ht="12.75" customHeight="1">
-      <c r="B234" s="2" t="s">
-        <v>185</v>
+      <c r="C234" s="2" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="235" ht="12.75" customHeight="1">
-      <c r="B235" s="2" t="s">
-        <v>76</v>
+      <c r="B235" s="3" t="s">
+        <v>194</v>
       </c>
       <c r="C235" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D235" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D235" s="2">
+      <c r="E235" s="2">
         <v>59.0</v>
       </c>
-      <c r="E235" s="3" t="s">
-        <v>194</v>
-      </c>
     </row>
     <row r="236" ht="12.75" customHeight="1">
-      <c r="B236" s="2" t="s">
+      <c r="C236" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="237" ht="12.75" customHeight="1">
-      <c r="B237" s="2" t="s">
+      <c r="C237" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="238" ht="12.75" customHeight="1">
-      <c r="B238" s="2" t="s">
+      <c r="C238" s="2" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="239" ht="12.75" customHeight="1">
-      <c r="B239" s="2" t="s">
-        <v>76</v>
+      <c r="B239" s="3" t="s">
+        <v>196</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D239" s="2">
+        <v>77</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E239" s="2">
         <v>60.0</v>
       </c>
-      <c r="E239" s="3" t="s">
-        <v>196</v>
-      </c>
     </row>
     <row r="240" ht="12.75" customHeight="1">
-      <c r="B240" s="2" t="s">
+      <c r="C240" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="241" ht="12.75" customHeight="1">
-      <c r="B241" s="2" t="s">
+      <c r="C241" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="242" ht="12.75" customHeight="1">
-      <c r="B242" s="2" t="s">
+      <c r="C242" s="2" t="s">
         <v>195</v>
       </c>
     </row>
@@ -3295,150 +3298,150 @@
       <c r="A243" s="2">
         <v>13.0</v>
       </c>
-      <c r="B243" s="2" t="s">
+      <c r="B243" s="3" t="s">
         <v>197</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="D243" s="2">
+      <c r="D243" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E243" s="2">
         <v>61.0</v>
-      </c>
-      <c r="E243" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="F243" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="244" ht="12.75" customHeight="1">
-      <c r="B244" s="2" t="s">
+      <c r="C244" s="2" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="245" ht="12.75" customHeight="1">
-      <c r="B245" s="2" t="s">
-        <v>198</v>
+      <c r="C245" s="2" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="246" ht="12.75" customHeight="1">
-      <c r="B246" s="2" t="s">
+      <c r="C246" s="2" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="247" ht="12.75" customHeight="1">
-      <c r="B247" s="2" t="s">
-        <v>76</v>
+      <c r="B247" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="C247" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D247" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D247" s="2">
+      <c r="E247" s="2">
         <v>62.0</v>
       </c>
-      <c r="E247" s="3" t="s">
-        <v>202</v>
-      </c>
     </row>
     <row r="248" ht="12.75" customHeight="1">
-      <c r="B248" s="2" t="s">
+      <c r="C248" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="249" ht="12.75" customHeight="1">
-      <c r="B249" s="2" t="s">
+      <c r="C249" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="250" ht="12.75" customHeight="1">
-      <c r="B250" s="2" t="s">
+      <c r="C250" s="2" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="251" ht="12.75" customHeight="1">
-      <c r="B251" s="2" t="s">
-        <v>76</v>
+      <c r="B251" s="3" t="s">
+        <v>203</v>
       </c>
       <c r="C251" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D251" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D251" s="2">
+      <c r="E251" s="2">
         <v>63.0</v>
       </c>
-      <c r="E251" s="3" t="s">
-        <v>203</v>
-      </c>
     </row>
     <row r="252" ht="12.75" customHeight="1">
-      <c r="B252" s="2" t="s">
+      <c r="C252" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="253" ht="12.75" customHeight="1">
-      <c r="B253" s="2" t="s">
+      <c r="C253" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="254" ht="12.75" customHeight="1">
-      <c r="B254" s="2" t="s">
+      <c r="C254" s="2" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="255" ht="12.75" customHeight="1">
-      <c r="B255" s="2" t="s">
+      <c r="B255" s="3" t="s">
         <v>204</v>
       </c>
       <c r="C255" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="D255" s="2">
+      <c r="D255" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E255" s="2">
         <v>64.0</v>
       </c>
-      <c r="E255" s="3" t="s">
+    </row>
+    <row r="256" ht="12.75" customHeight="1">
+      <c r="C256" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="257" ht="12.75" customHeight="1">
+      <c r="C257" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="258" ht="12.75" customHeight="1">
+      <c r="C258" s="2" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="256" ht="12.75" customHeight="1">
-      <c r="B256" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="257" ht="12.75" customHeight="1">
-      <c r="B257" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="258" ht="12.75" customHeight="1">
-      <c r="B258" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
     <row r="259" ht="12.75" customHeight="1">
-      <c r="B259" s="2" t="s">
+      <c r="B259" s="3" t="s">
         <v>209</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="D259" s="2">
+        <v>210</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E259" s="2">
         <v>65.0</v>
       </c>
-      <c r="E259" s="3" t="s">
-        <v>210</v>
-      </c>
     </row>
     <row r="260" ht="12.75" customHeight="1">
-      <c r="B260" s="2" t="s">
+      <c r="C260" s="2" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="261" ht="12.75" customHeight="1">
-      <c r="B261" s="2" t="s">
+      <c r="C261" s="2" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="262" ht="12.75" customHeight="1">
-      <c r="B262" s="2" t="s">
+      <c r="C262" s="2" t="s">
         <v>213</v>
       </c>
     </row>
@@ -3446,150 +3449,150 @@
       <c r="A263" s="2">
         <v>14.0</v>
       </c>
-      <c r="B263" s="2" t="s">
+      <c r="B263" s="3" t="s">
         <v>214</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="D263" s="2">
+      <c r="D263" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E263" s="2">
         <v>66.0</v>
-      </c>
-      <c r="E263" s="3" t="s">
-        <v>216</v>
       </c>
       <c r="F263" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="264" ht="12.75" customHeight="1">
-      <c r="B264" s="2" t="s">
-        <v>215</v>
+      <c r="C264" s="2" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="265" ht="12.75" customHeight="1">
-      <c r="B265" s="2" t="s">
+      <c r="C265" s="2" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="266" ht="12.75" customHeight="1">
-      <c r="B266" s="2" t="s">
+      <c r="C266" s="2" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="267" ht="12.75" customHeight="1">
-      <c r="B267" s="2" t="s">
+      <c r="B267" s="3" t="s">
         <v>219</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="D267" s="2">
+      <c r="D267" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E267" s="2">
         <v>67.0</v>
       </c>
-      <c r="E267" s="3" t="s">
+    </row>
+    <row r="268" ht="12.75" customHeight="1">
+      <c r="C268" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="269" ht="12.75" customHeight="1">
+      <c r="C269" s="2" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="268" ht="12.75" customHeight="1">
-      <c r="B268" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="269" ht="12.75" customHeight="1">
-      <c r="B269" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
     <row r="270" ht="12.75" customHeight="1">
-      <c r="B270" s="2" t="s">
+      <c r="C270" s="2" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="271" ht="12.75" customHeight="1">
-      <c r="B271" s="2" t="s">
+      <c r="B271" s="3" t="s">
         <v>224</v>
       </c>
       <c r="C271" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="D271" s="2">
+      <c r="D271" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E271" s="2">
         <v>68.0</v>
       </c>
-      <c r="E271" s="3" t="s">
+    </row>
+    <row r="272" ht="12.75" customHeight="1">
+      <c r="C272" s="2" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="272" ht="12.75" customHeight="1">
-      <c r="B272" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
     <row r="273" ht="12.75" customHeight="1">
-      <c r="B273" s="2" t="s">
+      <c r="C273" s="2" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="274" ht="12.75" customHeight="1">
-      <c r="B274" s="2" t="s">
+      <c r="C274" s="2" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="275" ht="12.75" customHeight="1">
-      <c r="B275" s="2" t="s">
-        <v>76</v>
+      <c r="B275" s="3" t="s">
+        <v>229</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D275" s="2">
+        <v>77</v>
+      </c>
+      <c r="D275" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E275" s="2">
         <v>69.0</v>
       </c>
-      <c r="E275" s="3" t="s">
-        <v>229</v>
-      </c>
     </row>
     <row r="276" ht="12.75" customHeight="1">
-      <c r="B276" s="2" t="s">
+      <c r="C276" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="277" ht="12.75" customHeight="1">
-      <c r="B277" s="2" t="s">
+      <c r="C277" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="278" ht="12.75" customHeight="1">
-      <c r="B278" s="2" t="s">
+      <c r="C278" s="2" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="279" ht="12.75" customHeight="1">
-      <c r="B279" s="2" t="s">
-        <v>76</v>
+      <c r="B279" s="3" t="s">
+        <v>230</v>
       </c>
       <c r="C279" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D279" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D279" s="2">
+      <c r="E279" s="2">
         <v>70.0</v>
       </c>
-      <c r="E279" s="3" t="s">
-        <v>230</v>
-      </c>
     </row>
     <row r="280" ht="12.75" customHeight="1">
-      <c r="B280" s="2" t="s">
+      <c r="C280" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="281" ht="12.75" customHeight="1">
-      <c r="B281" s="2" t="s">
+      <c r="C281" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="282" ht="12.75" customHeight="1">
-      <c r="B282" s="2" t="s">
+      <c r="C282" s="2" t="s">
         <v>195</v>
       </c>
     </row>
@@ -3597,150 +3600,150 @@
       <c r="A283" s="2">
         <v>15.0</v>
       </c>
-      <c r="B283" s="2" t="s">
-        <v>76</v>
+      <c r="B283" s="3" t="s">
+        <v>231</v>
       </c>
       <c r="C283" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D283" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="D283" s="2">
+      <c r="E283" s="2">
         <v>71.0</v>
-      </c>
-      <c r="E283" s="3" t="s">
-        <v>231</v>
       </c>
       <c r="F283" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="284" ht="12.75" customHeight="1">
-      <c r="B284" s="2" t="s">
+      <c r="C284" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="285" ht="12.75" customHeight="1">
-      <c r="B285" s="2" t="s">
+      <c r="C285" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="286" ht="12.75" customHeight="1">
-      <c r="B286" s="2" t="s">
+      <c r="C286" s="2" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="287" ht="12.75" customHeight="1">
-      <c r="B287" s="2" t="s">
-        <v>76</v>
+      <c r="B287" s="3" t="s">
+        <v>232</v>
       </c>
       <c r="C287" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D287" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D287" s="2">
+      <c r="E287" s="2">
         <v>72.0</v>
       </c>
-      <c r="E287" s="3" t="s">
-        <v>232</v>
-      </c>
     </row>
     <row r="288" ht="12.75" customHeight="1">
-      <c r="B288" s="2" t="s">
+      <c r="C288" s="2" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="289" ht="12.75" customHeight="1">
-      <c r="B289" s="2" t="s">
+      <c r="C289" s="2" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="290" ht="12.75" customHeight="1">
-      <c r="B290" s="2" t="s">
+      <c r="C290" s="2" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="291" ht="12.75" customHeight="1">
-      <c r="B291" s="2" t="s">
-        <v>76</v>
+      <c r="B291" s="3" t="s">
+        <v>234</v>
       </c>
       <c r="C291" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D291" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D291" s="2">
+      <c r="E291" s="2">
         <v>73.0</v>
       </c>
-      <c r="E291" s="3" t="s">
-        <v>234</v>
-      </c>
     </row>
     <row r="292" ht="12.75" customHeight="1">
-      <c r="B292" s="2" t="s">
+      <c r="C292" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="293" ht="12.75" customHeight="1">
-      <c r="B293" s="2" t="s">
+      <c r="C293" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="294" ht="12.75" customHeight="1">
-      <c r="B294" s="2" t="s">
+      <c r="C294" s="2" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="295" ht="12.75" customHeight="1">
-      <c r="B295" s="2" t="s">
-        <v>76</v>
+      <c r="B295" s="3" t="s">
+        <v>235</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D295" s="2">
+        <v>77</v>
+      </c>
+      <c r="D295" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E295" s="2">
         <v>74.0</v>
       </c>
-      <c r="E295" s="3" t="s">
-        <v>235</v>
-      </c>
     </row>
     <row r="296" ht="12.75" customHeight="1">
-      <c r="B296" s="2" t="s">
+      <c r="C296" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="297" ht="12.75" customHeight="1">
-      <c r="B297" s="2" t="s">
+      <c r="C297" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="298" ht="12.75" customHeight="1">
-      <c r="B298" s="2" t="s">
+      <c r="C298" s="2" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="299" ht="12.75" customHeight="1">
-      <c r="B299" s="2" t="s">
-        <v>76</v>
+      <c r="B299" s="3" t="s">
+        <v>236</v>
       </c>
       <c r="C299" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D299" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D299" s="2">
+      <c r="E299" s="2">
         <v>75.0</v>
       </c>
-      <c r="E299" s="3" t="s">
-        <v>236</v>
-      </c>
     </row>
     <row r="300" ht="12.75" customHeight="1">
-      <c r="B300" s="2" t="s">
+      <c r="C300" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="301" ht="12.75" customHeight="1">
-      <c r="B301" s="2" t="s">
+      <c r="C301" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="302" ht="12.75" customHeight="1">
-      <c r="B302" s="2" t="s">
+      <c r="C302" s="2" t="s">
         <v>195</v>
       </c>
     </row>
@@ -3748,150 +3751,150 @@
       <c r="A303" s="2">
         <v>16.0</v>
       </c>
-      <c r="B303" s="2" t="s">
-        <v>76</v>
+      <c r="B303" s="3" t="s">
+        <v>237</v>
       </c>
       <c r="C303" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D303" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D303" s="2">
+      <c r="E303" s="2">
         <v>76.0</v>
-      </c>
-      <c r="E303" s="3" t="s">
-        <v>237</v>
       </c>
       <c r="F303" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="304" ht="12.75" customHeight="1">
-      <c r="B304" s="2" t="s">
+      <c r="C304" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="305" ht="12.75" customHeight="1">
-      <c r="B305" s="2" t="s">
+      <c r="C305" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="306" ht="12.75" customHeight="1">
-      <c r="B306" s="2" t="s">
+      <c r="C306" s="2" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="307" ht="12.75" customHeight="1">
-      <c r="B307" s="2" t="s">
-        <v>76</v>
+      <c r="B307" s="3" t="s">
+        <v>238</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D307" s="2">
+        <v>77</v>
+      </c>
+      <c r="D307" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E307" s="2">
         <v>77.0</v>
       </c>
-      <c r="E307" s="3" t="s">
+    </row>
+    <row r="308" ht="12.75" customHeight="1">
+      <c r="C308" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="309" ht="12.75" customHeight="1">
+      <c r="C309" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="310" ht="12.75" customHeight="1">
+      <c r="C310" s="2" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="308" ht="12.75" customHeight="1">
-      <c r="B308" s="2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="309" ht="12.75" customHeight="1">
-      <c r="B309" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="310" ht="12.75" customHeight="1">
-      <c r="B310" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
     <row r="311" ht="12.75" customHeight="1">
-      <c r="B311" s="2" t="s">
-        <v>76</v>
+      <c r="B311" s="3" t="s">
+        <v>241</v>
       </c>
       <c r="C311" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D311" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D311" s="2">
+      <c r="E311" s="2">
         <v>78.0</v>
       </c>
-      <c r="E311" s="3" t="s">
-        <v>241</v>
-      </c>
     </row>
     <row r="312" ht="12.75" customHeight="1">
-      <c r="B312" s="2" t="s">
+      <c r="C312" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="313" ht="12.75" customHeight="1">
-      <c r="B313" s="2" t="s">
+      <c r="C313" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="314" ht="12.75" customHeight="1">
-      <c r="B314" s="2" t="s">
+      <c r="C314" s="2" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="315" ht="12.75" customHeight="1">
-      <c r="B315" s="2" t="s">
-        <v>242</v>
+      <c r="B315" s="3">
+        <v>1.0</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D315" s="2">
+      <c r="D315" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E315" s="2">
         <v>79.0</v>
       </c>
-      <c r="E315" s="3">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="316" ht="12.75" customHeight="1">
-      <c r="B316" s="2" t="s">
+      <c r="C316" s="2" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="317" ht="12.75" customHeight="1">
-      <c r="B317" s="2" t="s">
+      <c r="C317" s="2" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="318" ht="12.75" customHeight="1">
-      <c r="B318" s="2" t="s">
+      <c r="C318" s="2" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="319" ht="12.75" customHeight="1">
-      <c r="B319" s="2" t="s">
+      <c r="B319" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="C319" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="C319" s="2" t="s">
+      <c r="D319" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D319" s="2">
+      <c r="E319" s="2">
         <v>80.0</v>
       </c>
-      <c r="E319" s="3">
-        <v>3.0</v>
-      </c>
     </row>
     <row r="320" ht="12.75" customHeight="1">
-      <c r="B320" s="2" t="s">
+      <c r="C320" s="2" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="321" ht="12.75" customHeight="1">
-      <c r="B321" s="2" t="s">
+      <c r="C321" s="2" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="322" ht="12.75" customHeight="1">
-      <c r="B322" s="2" t="s">
+      <c r="C322" s="2" t="s">
         <v>245</v>
       </c>
     </row>
@@ -3899,150 +3902,150 @@
       <c r="A323" s="2">
         <v>17.0</v>
       </c>
-      <c r="B323" s="2" t="s">
+      <c r="B323" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="C323" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="C323" s="2" t="s">
+      <c r="D323" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="D323" s="2">
+      <c r="E323" s="2">
         <v>81.0</v>
-      </c>
-      <c r="E323" s="3">
-        <v>4.0</v>
       </c>
       <c r="F323" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="324" ht="12.75" customHeight="1">
-      <c r="B324" s="2" t="s">
+      <c r="C324" s="2" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="325" ht="12.75" customHeight="1">
-      <c r="B325" s="2" t="s">
+      <c r="C325" s="2" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="326" ht="12.75" customHeight="1">
-      <c r="B326" s="2" t="s">
+      <c r="C326" s="2" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="327" ht="12.75" customHeight="1">
-      <c r="B327" s="2" t="s">
+      <c r="B327" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="C327" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="C327" s="2" t="s">
+      <c r="D327" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="D327" s="2">
+      <c r="E327" s="2">
         <v>82.0</v>
       </c>
-      <c r="E327" s="3">
-        <v>2.0</v>
-      </c>
     </row>
     <row r="328" ht="12.75" customHeight="1">
-      <c r="B328" s="2" t="s">
+      <c r="C328" s="2" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="329" ht="12.75" customHeight="1">
-      <c r="B329" s="2" t="s">
+      <c r="C329" s="2" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="330" ht="12.75" customHeight="1">
-      <c r="B330" s="2" t="s">
+      <c r="C330" s="2" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="331" ht="12.75" customHeight="1">
-      <c r="B331" s="2" t="s">
+      <c r="B331" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="C331" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C331" s="2" t="s">
+      <c r="D331" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D331" s="2">
+      <c r="E331" s="2">
         <v>83.0</v>
       </c>
-      <c r="E331" s="3">
-        <v>5.0</v>
-      </c>
     </row>
     <row r="332" ht="12.75" customHeight="1">
-      <c r="B332" s="2" t="s">
+      <c r="C332" s="2" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="333" ht="12.75" customHeight="1">
-      <c r="B333" s="2" t="s">
+      <c r="C333" s="2" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="334" ht="12.75" customHeight="1">
-      <c r="B334" s="2" t="s">
+      <c r="C334" s="2" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="335" ht="12.75" customHeight="1">
-      <c r="B335" s="2" t="s">
+      <c r="B335" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="C335" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C335" s="2" t="s">
+      <c r="D335" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D335" s="2">
+      <c r="E335" s="2">
         <v>84.0</v>
       </c>
-      <c r="E335" s="3">
-        <v>7.0</v>
-      </c>
     </row>
     <row r="336" ht="12.75" customHeight="1">
-      <c r="B336" s="2" t="s">
+      <c r="C336" s="2" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="337" ht="12.75" customHeight="1">
-      <c r="B337" s="2" t="s">
+      <c r="C337" s="2" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="338" ht="12.75" customHeight="1">
-      <c r="B338" s="2" t="s">
+      <c r="C338" s="2" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="339" ht="12.75" customHeight="1">
-      <c r="B339" s="2" t="s">
-        <v>246</v>
+      <c r="B339" s="3">
+        <v>6.0</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D339" s="2">
+      <c r="D339" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E339" s="2">
         <v>85.0</v>
       </c>
-      <c r="E339" s="3">
-        <v>6.0</v>
-      </c>
     </row>
     <row r="340" ht="12.75" customHeight="1">
-      <c r="B340" s="2" t="s">
+      <c r="C340" s="2" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="341" ht="12.75" customHeight="1">
-      <c r="B341" s="2" t="s">
+      <c r="C341" s="2" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="342" ht="12.75" customHeight="1">
-      <c r="B342" s="2" t="s">
+      <c r="C342" s="2" t="s">
         <v>249</v>
       </c>
     </row>
@@ -4050,92 +4053,92 @@
       <c r="A343" s="2">
         <v>18.0</v>
       </c>
-      <c r="B343" s="2" t="s">
+      <c r="B343" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="C343" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C343" s="2" t="s">
+      <c r="D343" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="D343" s="2">
+      <c r="E343" s="2">
         <v>86.0</v>
-      </c>
-      <c r="E343" s="3">
-        <v>8.0</v>
       </c>
       <c r="F343" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="344" ht="12.75" customHeight="1">
-      <c r="B344" s="2" t="s">
+      <c r="C344" s="2" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="345" ht="12.75" customHeight="1">
-      <c r="B345" s="2" t="s">
+      <c r="C345" s="2" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="346" ht="12.75" customHeight="1">
-      <c r="B346" s="2" t="s">
+      <c r="C346" s="2" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="347" ht="12.75" customHeight="1">
-      <c r="B347" s="2" t="s">
+      <c r="B347" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="C347" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C347" s="2" t="s">
+      <c r="D347" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="D347" s="2">
+      <c r="E347" s="2">
         <v>87.0</v>
       </c>
-      <c r="E347" s="3">
-        <v>9.0</v>
-      </c>
     </row>
     <row r="348" ht="12.75" customHeight="1">
-      <c r="B348" s="2" t="s">
+      <c r="C348" s="2" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="349" ht="12.75" customHeight="1">
-      <c r="B349" s="2" t="s">
+      <c r="C349" s="2" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="350" ht="12.75" customHeight="1">
-      <c r="B350" s="2" t="s">
+      <c r="C350" s="2" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="351" ht="12.75" customHeight="1">
-      <c r="B351" s="2" t="s">
+      <c r="B351" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="C351" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C351" s="2" t="s">
+      <c r="D351" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="D351" s="2">
+      <c r="E351" s="2">
         <v>88.0</v>
       </c>
-      <c r="E351" s="3">
-        <v>10.0</v>
-      </c>
     </row>
     <row r="352" ht="12.75" customHeight="1">
-      <c r="B352" s="2" t="s">
+      <c r="C352" s="2" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="353" ht="12.75" customHeight="1">
-      <c r="B353" s="2" t="s">
+      <c r="C353" s="2" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="354" ht="12.75" customHeight="1">
-      <c r="B354" s="2" t="s">
+      <c r="C354" s="2" t="s">
         <v>251</v>
       </c>
     </row>
@@ -4146,54 +4149,54 @@
       <c r="C355" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="D355" s="2">
+      <c r="D355" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E355" s="2">
         <v>89.0</v>
       </c>
-      <c r="E355" s="2" t="s">
-        <v>253</v>
-      </c>
     </row>
     <row r="356" ht="12.75" customHeight="1">
-      <c r="B356" s="2" t="s">
+      <c r="C356" s="2" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="357" ht="12.75" customHeight="1">
-      <c r="B357" s="2" t="s">
-        <v>253</v>
+      <c r="C357" s="2" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="358" ht="12.75" customHeight="1">
-      <c r="B358" s="2" t="s">
+      <c r="C358" s="2" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="359" ht="12.75" customHeight="1">
       <c r="B359" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C359" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D359" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E359" s="2">
+        <v>90.0</v>
+      </c>
+    </row>
+    <row r="360" ht="12.75" customHeight="1">
+      <c r="C360" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="361" ht="12.75" customHeight="1">
+      <c r="C361" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="C359" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="D359" s="2">
-        <v>90.0</v>
-      </c>
-      <c r="E359" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="360" ht="12.75" customHeight="1">
-      <c r="B360" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="361" ht="12.75" customHeight="1">
-      <c r="B361" s="2" t="s">
-        <v>253</v>
-      </c>
     </row>
     <row r="362" ht="12.75" customHeight="1">
-      <c r="B362" s="2" t="s">
+      <c r="C362" s="2" t="s">
         <v>255</v>
       </c>
     </row>
@@ -4202,62 +4205,62 @@
         <v>19.0</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D363" s="2">
+        <v>253</v>
+      </c>
+      <c r="D363" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E363" s="2">
         <v>91.0</v>
-      </c>
-      <c r="E363" s="2" t="s">
-        <v>252</v>
       </c>
       <c r="F363" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="364" ht="12.75" customHeight="1">
-      <c r="B364" s="2" t="s">
+      <c r="C364" s="2" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="365" ht="12.75" customHeight="1">
-      <c r="B365" s="2" t="s">
-        <v>253</v>
+      <c r="C365" s="2" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="366" ht="12.75" customHeight="1">
-      <c r="B366" s="2" t="s">
+      <c r="C366" s="2" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="367" ht="12.75" customHeight="1">
       <c r="B367" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C367" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D367" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E367" s="2">
+        <v>92.0</v>
+      </c>
+    </row>
+    <row r="368" ht="12.75" customHeight="1">
+      <c r="C368" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="369" ht="12.75" customHeight="1">
+      <c r="C369" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="C367" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="D367" s="2">
-        <v>92.0</v>
-      </c>
-      <c r="E367" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="368" ht="12.75" customHeight="1">
-      <c r="B368" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="369" ht="12.75" customHeight="1">
-      <c r="B369" s="2" t="s">
-        <v>253</v>
-      </c>
     </row>
     <row r="370" ht="12.75" customHeight="1">
-      <c r="B370" s="2" t="s">
+      <c r="C370" s="2" t="s">
         <v>255</v>
       </c>
     </row>
@@ -4268,83 +4271,83 @@
       <c r="C371" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="D371" s="2">
+      <c r="D371" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E371" s="2">
         <v>93.0</v>
       </c>
-      <c r="E371" s="2" t="s">
-        <v>256</v>
-      </c>
     </row>
     <row r="372" ht="12.75" customHeight="1">
-      <c r="B372" s="2" t="s">
+      <c r="C372" s="2" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="373" ht="12.75" customHeight="1">
-      <c r="B373" s="2" t="s">
+      <c r="C373" s="2" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="374" ht="12.75" customHeight="1">
-      <c r="B374" s="2" t="s">
+      <c r="C374" s="2" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="375" ht="12.75" customHeight="1">
       <c r="B375" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C375" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="C375" s="2" t="s">
+      <c r="D375" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="D375" s="2">
+      <c r="E375" s="2">
         <v>94.0</v>
       </c>
-      <c r="E375" s="2" t="s">
+    </row>
+    <row r="376" ht="12.75" customHeight="1">
+      <c r="C376" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="377" ht="12.75" customHeight="1">
+      <c r="C377" s="2" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="376" ht="12.75" customHeight="1">
-      <c r="B376" s="2" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="377" ht="12.75" customHeight="1">
-      <c r="B377" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
     <row r="378" ht="12.75" customHeight="1">
-      <c r="B378" s="2" t="s">
+      <c r="C378" s="2" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="379" ht="12.75" customHeight="1">
       <c r="B379" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C379" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="C379" s="2" t="s">
+      <c r="D379" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D379" s="2">
+      <c r="E379" s="2">
         <v>95.0</v>
       </c>
-      <c r="E379" s="2" t="s">
+    </row>
+    <row r="380" ht="12.75" customHeight="1">
+      <c r="C380" s="2" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="380" ht="12.75" customHeight="1">
-      <c r="B380" s="2" t="s">
-        <v>257</v>
-      </c>
-    </row>
     <row r="381" ht="12.75" customHeight="1">
-      <c r="B381" s="2" t="s">
+      <c r="C381" s="2" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="382" ht="12.75" customHeight="1">
-      <c r="B382" s="2" t="s">
+      <c r="C382" s="2" t="s">
         <v>259</v>
       </c>
     </row>
@@ -4353,149 +4356,149 @@
         <v>20.0</v>
       </c>
       <c r="B383" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C383" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="C383" s="2" t="s">
+      <c r="D383" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="D383" s="2">
+      <c r="E383" s="2">
         <v>96.0</v>
-      </c>
-      <c r="E383" s="2" t="s">
-        <v>259</v>
       </c>
       <c r="F383" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="384" ht="12.75" customHeight="1">
-      <c r="B384" s="2" t="s">
+      <c r="C384" s="2" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="385" ht="12.75" customHeight="1">
-      <c r="B385" s="2" t="s">
+      <c r="C385" s="2" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="386" ht="12.75" customHeight="1">
-      <c r="B386" s="2" t="s">
+      <c r="C386" s="2" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="387" ht="12.75" customHeight="1">
-      <c r="B387" s="2" t="s">
-        <v>76</v>
+      <c r="B387" s="3" t="s">
+        <v>260</v>
       </c>
       <c r="C387" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D387" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D387" s="2">
+      <c r="E387" s="2">
         <v>97.0</v>
       </c>
-      <c r="E387" s="3" t="s">
-        <v>260</v>
-      </c>
     </row>
     <row r="388" ht="12.75" customHeight="1">
-      <c r="B388" s="2" t="s">
+      <c r="C388" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="389" ht="12.75" customHeight="1">
-      <c r="B389" s="2" t="s">
+      <c r="C389" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="390" ht="12.75" customHeight="1">
-      <c r="B390" s="2" t="s">
+      <c r="C390" s="2" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="391" ht="12.75" customHeight="1">
-      <c r="B391" s="2" t="s">
-        <v>76</v>
+      <c r="B391" s="3" t="s">
+        <v>261</v>
       </c>
       <c r="C391" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D391" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D391" s="2">
+      <c r="E391" s="2">
         <v>98.0</v>
       </c>
-      <c r="E391" s="3" t="s">
-        <v>261</v>
-      </c>
     </row>
     <row r="392" ht="12.75" customHeight="1">
-      <c r="B392" s="2" t="s">
+      <c r="C392" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="393" ht="12.75" customHeight="1">
-      <c r="B393" s="2" t="s">
+      <c r="C393" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="394" ht="12.75" customHeight="1">
-      <c r="B394" s="2" t="s">
+      <c r="C394" s="2" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="395" ht="12.75" customHeight="1">
-      <c r="B395" s="2" t="s">
-        <v>76</v>
+      <c r="B395" s="3" t="s">
+        <v>262</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D395" s="2">
+        <v>77</v>
+      </c>
+      <c r="D395" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E395" s="2">
         <v>99.0</v>
       </c>
-      <c r="E395" s="3" t="s">
-        <v>262</v>
-      </c>
     </row>
     <row r="396" ht="12.75" customHeight="1">
-      <c r="B396" s="2" t="s">
+      <c r="C396" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="397" ht="12.75" customHeight="1">
-      <c r="B397" s="2" t="s">
+      <c r="C397" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="398" ht="12.75" customHeight="1">
-      <c r="B398" s="2" t="s">
+      <c r="C398" s="2" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="399" ht="12.75" customHeight="1">
-      <c r="B399" s="2" t="s">
-        <v>76</v>
+      <c r="B399" s="3" t="s">
+        <v>263</v>
       </c>
       <c r="C399" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D399" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D399" s="2">
+      <c r="E399" s="2">
         <v>100.0</v>
       </c>
-      <c r="E399" s="3" t="s">
-        <v>263</v>
-      </c>
     </row>
     <row r="400" ht="12.75" customHeight="1">
-      <c r="B400" s="2" t="s">
+      <c r="C400" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="401" ht="12.75" customHeight="1">
-      <c r="B401" s="2" t="s">
+      <c r="C401" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="402" ht="12.75" customHeight="1">
-      <c r="B402" s="2" t="s">
+      <c r="C402" s="2" t="s">
         <v>195</v>
       </c>
     </row>
@@ -4503,150 +4506,150 @@
       <c r="A403" s="2">
         <v>21.0</v>
       </c>
-      <c r="B403" s="2" t="s">
-        <v>76</v>
+      <c r="B403" s="3" t="s">
+        <v>264</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D403" s="2">
+        <v>77</v>
+      </c>
+      <c r="D403" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E403" s="2">
         <v>101.0</v>
-      </c>
-      <c r="E403" s="3" t="s">
-        <v>264</v>
       </c>
       <c r="F403" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="404" ht="12.75" customHeight="1">
-      <c r="B404" s="2" t="s">
+      <c r="C404" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="405" ht="12.75" customHeight="1">
-      <c r="B405" s="2" t="s">
+      <c r="C405" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="406" ht="12.75" customHeight="1">
-      <c r="B406" s="2" t="s">
+      <c r="C406" s="2" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="407" ht="12.75" customHeight="1">
-      <c r="B407" s="2" t="s">
+      <c r="B407" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C407" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C407" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="D407" s="2">
+      <c r="D407" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E407" s="2">
         <v>102.0</v>
       </c>
-      <c r="E407" s="3" t="s">
+    </row>
+    <row r="408" ht="12.75" customHeight="1">
+      <c r="C408" s="2" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="408" ht="12.75" customHeight="1">
-      <c r="B408" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
     <row r="409" ht="12.75" customHeight="1">
-      <c r="B409" s="2" t="s">
+      <c r="C409" s="2" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="410" ht="12.75" customHeight="1">
-      <c r="B410" s="2" t="s">
+      <c r="C410" s="2" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="411" ht="12.75" customHeight="1">
-      <c r="B411" s="2" t="s">
-        <v>76</v>
+      <c r="B411" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="C411" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D411" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D411" s="2">
+      <c r="E411" s="2">
         <v>103.0</v>
       </c>
-      <c r="E411" s="3" t="s">
-        <v>268</v>
-      </c>
     </row>
     <row r="412" ht="12.75" customHeight="1">
-      <c r="B412" s="2" t="s">
+      <c r="C412" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="413" ht="12.75" customHeight="1">
-      <c r="B413" s="2" t="s">
+      <c r="C413" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="414" ht="12.75" customHeight="1">
-      <c r="B414" s="2" t="s">
+      <c r="C414" s="2" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="415" ht="12.75" customHeight="1">
-      <c r="B415" s="2" t="s">
-        <v>233</v>
+      <c r="B415" s="3" t="s">
+        <v>269</v>
       </c>
       <c r="C415" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="D415" s="2">
+      <c r="D415" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E415" s="2">
         <v>104.0</v>
       </c>
-      <c r="E415" s="3" t="s">
-        <v>269</v>
-      </c>
     </row>
     <row r="416" ht="12.75" customHeight="1">
-      <c r="B416" s="2" t="s">
-        <v>265</v>
+      <c r="C416" s="2" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="417" ht="12.75" customHeight="1">
-      <c r="B417" s="2" t="s">
+      <c r="C417" s="2" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="418" ht="12.75" customHeight="1">
-      <c r="B418" s="2" t="s">
+      <c r="C418" s="2" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="419" ht="12.75" customHeight="1">
-      <c r="B419" s="2" t="s">
-        <v>76</v>
+      <c r="B419" s="3" t="s">
+        <v>270</v>
       </c>
       <c r="C419" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D419" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D419" s="2">
+      <c r="E419" s="2">
         <v>105.0</v>
       </c>
-      <c r="E419" s="3" t="s">
-        <v>270</v>
-      </c>
     </row>
     <row r="420" ht="12.75" customHeight="1">
-      <c r="B420" s="2" t="s">
+      <c r="C420" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="421" ht="12.75" customHeight="1">
-      <c r="B421" s="2" t="s">
+      <c r="C421" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="422" ht="12.75" customHeight="1">
-      <c r="B422" s="2" t="s">
+      <c r="C422" s="2" t="s">
         <v>195</v>
       </c>
     </row>
@@ -4654,34 +4657,34 @@
       <c r="A423" s="2">
         <v>22.0</v>
       </c>
-      <c r="B423" s="2" t="s">
-        <v>76</v>
+      <c r="B423" s="3" t="s">
+        <v>271</v>
       </c>
       <c r="C423" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D423" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D423" s="2">
+      <c r="E423" s="2">
         <v>106.0</v>
-      </c>
-      <c r="E423" s="3" t="s">
-        <v>271</v>
       </c>
       <c r="F423" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="424" ht="12.75" customHeight="1">
-      <c r="B424" s="2" t="s">
+      <c r="C424" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="425" ht="12.75" customHeight="1">
-      <c r="B425" s="2" t="s">
+      <c r="C425" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="426" ht="12.75" customHeight="1">
-      <c r="B426" s="2" t="s">
+      <c r="C426" s="2" t="s">
         <v>195</v>
       </c>
     </row>
@@ -4692,113 +4695,113 @@
       <c r="C427" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D427" s="2">
+      <c r="D427" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E427" s="2">
         <v>107.0</v>
       </c>
-      <c r="E427" s="2" t="s">
+    </row>
+    <row r="428" ht="12.75" customHeight="1">
+      <c r="C428" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="429" ht="12.75" customHeight="1">
+      <c r="C429" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="430" ht="12.75" customHeight="1">
+      <c r="C430" s="2" t="s">
         <v>274</v>
-      </c>
-    </row>
-    <row r="428" ht="12.75" customHeight="1">
-      <c r="B428" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="429" ht="12.75" customHeight="1">
-      <c r="B429" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="430" ht="12.75" customHeight="1">
-      <c r="B430" s="2" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="431" ht="12.75" customHeight="1">
       <c r="B431" s="2" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D431" s="2">
+        <v>273</v>
+      </c>
+      <c r="D431" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E431" s="2">
         <v>108.0</v>
       </c>
-      <c r="E431" s="2" t="s">
+    </row>
+    <row r="432" ht="12.75" customHeight="1">
+      <c r="C432" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="433" ht="12.75" customHeight="1">
+      <c r="C433" s="2" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="432" ht="12.75" customHeight="1">
-      <c r="B432" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="433" ht="12.75" customHeight="1">
-      <c r="B433" s="2" t="s">
-        <v>277</v>
-      </c>
-    </row>
     <row r="434" ht="12.75" customHeight="1">
-      <c r="B434" s="2" t="s">
+      <c r="C434" s="2" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="435" ht="12.75" customHeight="1">
       <c r="B435" s="2" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="C435" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D435" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D435" s="2">
+      <c r="E435" s="2">
         <v>109.0</v>
       </c>
-      <c r="E435" s="2" t="s">
-        <v>279</v>
-      </c>
     </row>
     <row r="436" ht="12.75" customHeight="1">
-      <c r="B436" s="2" t="s">
+      <c r="C436" s="2" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="437" ht="12.75" customHeight="1">
-      <c r="B437" s="2" t="s">
+      <c r="C437" s="2" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="438" ht="12.75" customHeight="1">
-      <c r="B438" s="2" t="s">
+      <c r="C438" s="2" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="439" ht="12.75" customHeight="1">
-      <c r="B439" s="2" t="s">
+      <c r="B439" s="3" t="s">
         <v>281</v>
       </c>
       <c r="C439" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D439" s="2">
+      <c r="D439" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E439" s="2">
         <v>110.0</v>
       </c>
-      <c r="E439" s="3" t="s">
+    </row>
+    <row r="440" ht="12.75" customHeight="1">
+      <c r="C440" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="441" ht="12.75" customHeight="1">
+      <c r="C441" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="442" ht="12.75" customHeight="1">
+      <c r="C442" s="2" t="s">
         <v>283</v>
-      </c>
-    </row>
-    <row r="440" ht="12.75" customHeight="1">
-      <c r="B440" s="2" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="441" ht="12.75" customHeight="1">
-      <c r="B441" s="2" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="442" ht="12.75" customHeight="1">
-      <c r="B442" s="2" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="443" ht="12.75" customHeight="1">
@@ -4806,62 +4809,62 @@
         <v>23.0</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="C443" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D443" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D443" s="2">
+      <c r="E443" s="2">
         <v>111.0</v>
-      </c>
-      <c r="E443" s="2" t="s">
-        <v>286</v>
       </c>
       <c r="F443" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="444" ht="12.75" customHeight="1">
-      <c r="B444" s="2" t="s">
-        <v>273</v>
+      <c r="C444" s="2" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="445" ht="12.75" customHeight="1">
-      <c r="B445" s="2" t="s">
+      <c r="C445" s="2" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="446" ht="12.75" customHeight="1">
-      <c r="B446" s="2" t="s">
+      <c r="C446" s="2" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="447" ht="12.75" customHeight="1">
       <c r="B447" s="2" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="C447" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D447" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D447" s="2">
+      <c r="E447" s="2">
         <v>112.0</v>
       </c>
-      <c r="E447" s="2" t="s">
-        <v>287</v>
-      </c>
     </row>
     <row r="448" ht="12.75" customHeight="1">
-      <c r="B448" s="2" t="s">
+      <c r="C448" s="2" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="449" ht="12.75" customHeight="1">
-      <c r="B449" s="2" t="s">
+      <c r="C449" s="2" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="450" ht="12.75" customHeight="1">
-      <c r="B450" s="2" t="s">
+      <c r="C450" s="2" t="s">
         <v>276</v>
       </c>
     </row>
@@ -4872,83 +4875,83 @@
       <c r="C451" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="D451" s="2">
+      <c r="D451" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="E451" s="2">
         <v>113.0</v>
       </c>
-      <c r="E451" s="2" t="s">
+    </row>
+    <row r="452" ht="12.75" customHeight="1">
+      <c r="C452" s="2" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="452" ht="12.75" customHeight="1">
-      <c r="B452" s="2" t="s">
-        <v>289</v>
-      </c>
-    </row>
     <row r="453" ht="12.75" customHeight="1">
-      <c r="B453" s="2" t="s">
+      <c r="C453" s="2" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="454" ht="12.75" customHeight="1">
-      <c r="B454" s="2" t="s">
+      <c r="C454" s="2" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="455" ht="12.75" customHeight="1">
       <c r="B455" s="2" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D455" s="2">
+        <v>289</v>
+      </c>
+      <c r="D455" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E455" s="2">
         <v>114.0</v>
       </c>
-      <c r="E455" s="2" t="s">
-        <v>293</v>
-      </c>
     </row>
     <row r="456" ht="12.75" customHeight="1">
-      <c r="B456" s="2" t="s">
+      <c r="C456" s="2" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="457" ht="12.75" customHeight="1">
-      <c r="B457" s="2" t="s">
+      <c r="C457" s="2" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="458" ht="12.75" customHeight="1">
-      <c r="B458" s="2" t="s">
+      <c r="C458" s="2" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="459" ht="12.75" customHeight="1">
       <c r="B459" s="2" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="C459" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D459" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="D459" s="2">
+      <c r="E459" s="2">
         <v>116.0</v>
       </c>
-      <c r="E459" s="2" t="s">
-        <v>297</v>
-      </c>
     </row>
     <row r="460" ht="12.75" customHeight="1">
-      <c r="B460" s="2" t="s">
+      <c r="C460" s="2" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="461" ht="12.75" customHeight="1">
-      <c r="B461" s="2" t="s">
+      <c r="C461" s="2" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="462" ht="12.75" customHeight="1">
-      <c r="B462" s="2" t="s">
+      <c r="C462" s="2" t="s">
         <v>296</v>
       </c>
     </row>
@@ -4957,34 +4960,34 @@
         <v>24.0</v>
       </c>
       <c r="B463" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C463" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="C463" s="2" t="s">
+      <c r="D463" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D463" s="2">
+      <c r="E463" s="2">
         <v>117.0</v>
-      </c>
-      <c r="E463" s="2" t="s">
-        <v>298</v>
       </c>
       <c r="F463" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="464" ht="12.75" customHeight="1">
-      <c r="B464" s="2" t="s">
+      <c r="C464" s="2" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="465" ht="12.75" customHeight="1">
-      <c r="B465" s="2" t="s">
+      <c r="C465" s="2" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="466" ht="12.75" customHeight="1">
-      <c r="B466" s="2" t="s">
-        <v>288</v>
+      <c r="C466" s="2" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="467" ht="12.75" customHeight="1">
@@ -4992,265 +4995,265 @@
         <v>299</v>
       </c>
       <c r="C467" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D467" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="D467" s="2">
+      <c r="E467" s="2">
         <v>118.0</v>
       </c>
-      <c r="E467" s="2" t="s">
-        <v>300</v>
-      </c>
     </row>
     <row r="468" ht="12.75" customHeight="1">
-      <c r="B468" s="2" t="s">
+      <c r="C468" s="2" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="469" ht="12.75" customHeight="1">
-      <c r="B469" s="2" t="s">
-        <v>288</v>
+      <c r="C469" s="2" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="470" ht="12.75" customHeight="1">
-      <c r="B470" s="2" t="s">
+      <c r="C470" s="2" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="471" ht="12.75" customHeight="1">
-      <c r="B471" s="2" t="s">
-        <v>281</v>
+      <c r="B471" s="3">
+        <v>1.0</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D471" s="2">
+        <v>282</v>
+      </c>
+      <c r="D471" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="E471" s="2">
         <v>119.0</v>
       </c>
-      <c r="E471" s="3">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="472" ht="12.75" customHeight="1">
-      <c r="B472" s="2" t="s">
+      <c r="C472" s="2" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="473" ht="12.75" customHeight="1">
-      <c r="B473" s="2" t="s">
+      <c r="C473" s="2" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="474" ht="12.75" customHeight="1">
-      <c r="B474" s="2" t="s">
+      <c r="C474" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="475" ht="12.75" customHeight="1">
+      <c r="B475" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="C475" s="2" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="475" ht="12.75" customHeight="1">
-      <c r="B475" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C475" s="2" t="s">
+      <c r="D475" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D475" s="2">
+      <c r="E475" s="2">
         <v>110.0</v>
       </c>
-      <c r="E475" s="3">
-        <v>3.0</v>
-      </c>
     </row>
     <row r="476" ht="12.75" customHeight="1">
-      <c r="B476" s="2" t="s">
+      <c r="C476" s="2" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="477" ht="12.75" customHeight="1">
-      <c r="B477" s="2" t="s">
+      <c r="C477" s="2" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="478" ht="12.75" customHeight="1">
-      <c r="B478" s="2" t="s">
+      <c r="C478" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="479" ht="12.75" customHeight="1">
+      <c r="B479" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="C479" s="2" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="479" ht="12.75" customHeight="1">
-      <c r="B479" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C479" s="2" t="s">
+      <c r="D479" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D479" s="2">
+      <c r="E479" s="2">
         <v>120.0</v>
       </c>
-      <c r="E479" s="3">
-        <v>2.0</v>
-      </c>
     </row>
     <row r="480" ht="12.75" customHeight="1">
-      <c r="B480" s="2" t="s">
+      <c r="C480" s="2" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="481" ht="12.75" customHeight="1">
-      <c r="B481" s="2" t="s">
+      <c r="C481" s="2" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="482" ht="12.75" customHeight="1">
-      <c r="B482" s="2" t="s">
-        <v>282</v>
+      <c r="C482" s="2" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="483" ht="12.75" customHeight="1">
       <c r="A483" s="2">
         <v>25.0</v>
       </c>
-      <c r="B483" s="2" t="s">
-        <v>281</v>
+      <c r="B483" s="3">
+        <v>4.0</v>
       </c>
       <c r="C483" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D483" s="2">
+      <c r="D483" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E483" s="2">
         <v>121.0</v>
-      </c>
-      <c r="E483" s="3">
-        <v>4.0</v>
       </c>
       <c r="F483" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="484" ht="12.75" customHeight="1">
-      <c r="B484" s="2" t="s">
+      <c r="C484" s="2" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="485" ht="12.75" customHeight="1">
-      <c r="B485" s="2" t="s">
+      <c r="C485" s="2" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="486" ht="12.75" customHeight="1">
-      <c r="B486" s="2" t="s">
+      <c r="C486" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="487" ht="12.75" customHeight="1">
+      <c r="B487" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="C487" s="2" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="487" ht="12.75" customHeight="1">
-      <c r="B487" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C487" s="2" t="s">
+      <c r="D487" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="D487" s="2">
+      <c r="E487" s="2">
         <v>122.0</v>
       </c>
-      <c r="E487" s="3">
-        <v>5.0</v>
-      </c>
     </row>
     <row r="488" ht="12.75" customHeight="1">
-      <c r="B488" s="2" t="s">
+      <c r="C488" s="2" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="489" ht="12.75" customHeight="1">
-      <c r="B489" s="2" t="s">
+      <c r="C489" s="2" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="490" ht="12.75" customHeight="1">
-      <c r="B490" s="2" t="s">
-        <v>282</v>
+      <c r="C490" s="2" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="491" ht="12.75" customHeight="1">
-      <c r="B491" s="2" t="s">
-        <v>302</v>
+      <c r="B491" s="3">
+        <v>6.0</v>
       </c>
       <c r="C491" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="D491" s="2">
+      <c r="D491" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E491" s="2">
         <v>123.0</v>
       </c>
-      <c r="E491" s="3">
-        <v>6.0</v>
-      </c>
     </row>
     <row r="492" ht="12.75" customHeight="1">
-      <c r="B492" s="2" t="s">
+      <c r="C492" s="2" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="493" ht="12.75" customHeight="1">
-      <c r="B493" s="2" t="s">
+      <c r="C493" s="2" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="494" ht="12.75" customHeight="1">
-      <c r="B494" s="2" t="s">
-        <v>282</v>
+      <c r="C494" s="2" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="495" ht="12.75" customHeight="1">
-      <c r="B495" s="2" t="s">
-        <v>76</v>
+      <c r="B495" s="3" t="s">
+        <v>303</v>
       </c>
       <c r="C495" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D495" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D495" s="2">
+      <c r="E495" s="2">
         <v>124.0</v>
       </c>
-      <c r="E495" s="3" t="s">
-        <v>303</v>
-      </c>
     </row>
     <row r="496" ht="12.75" customHeight="1">
-      <c r="B496" s="2" t="s">
+      <c r="C496" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="497" ht="12.75" customHeight="1">
-      <c r="B497" s="2" t="s">
+      <c r="C497" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="498" ht="12.75" customHeight="1">
-      <c r="B498" s="2" t="s">
+      <c r="C498" s="2" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="499" ht="12.75" customHeight="1">
-      <c r="B499" s="2" t="s">
+      <c r="B499" s="3" t="s">
         <v>304</v>
       </c>
       <c r="C499" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="D499" s="2">
+      <c r="D499" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E499" s="2">
         <v>125.0</v>
       </c>
-      <c r="E499" s="3" t="s">
+    </row>
+    <row r="500" ht="12.75" customHeight="1">
+      <c r="C500" s="2" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="500" ht="12.75" customHeight="1">
-      <c r="B500" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
     <row r="501" ht="12.75" customHeight="1">
-      <c r="B501" s="2" t="s">
+      <c r="C501" s="2" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="502" ht="12.75" customHeight="1">
-      <c r="B502" s="2" t="s">
+      <c r="C502" s="2" t="s">
         <v>240</v>
       </c>
     </row>
@@ -5259,149 +5262,149 @@
         <v>26.0</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>76</v>
+        <v>307</v>
       </c>
       <c r="C503" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D503" s="2">
+        <v>77</v>
+      </c>
+      <c r="D503" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="E503" s="2">
         <v>126.0</v>
-      </c>
-      <c r="E503" s="2" t="s">
-        <v>308</v>
       </c>
       <c r="F503" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="504" ht="12.75" customHeight="1">
-      <c r="B504" s="2" t="s">
-        <v>307</v>
+      <c r="C504" s="2" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="505" ht="12.75" customHeight="1">
-      <c r="B505" s="2" t="s">
+      <c r="C505" s="2" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="506" ht="12.75" customHeight="1">
-      <c r="B506" s="2" t="s">
+      <c r="C506" s="2" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="507" ht="12.75" customHeight="1">
       <c r="B507" s="2" t="s">
-        <v>76</v>
+        <v>311</v>
       </c>
       <c r="C507" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D507" s="2">
+        <v>77</v>
+      </c>
+      <c r="D507" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E507" s="2">
         <v>127.0</v>
       </c>
-      <c r="E507" s="2" t="s">
-        <v>311</v>
-      </c>
     </row>
     <row r="508" ht="12.75" customHeight="1">
-      <c r="B508" s="2" t="s">
-        <v>307</v>
+      <c r="C508" s="2" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="509" ht="12.75" customHeight="1">
-      <c r="B509" s="2" t="s">
+      <c r="C509" s="2" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="510" ht="12.75" customHeight="1">
-      <c r="B510" s="2" t="s">
+      <c r="C510" s="2" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="511" ht="12.75" customHeight="1">
       <c r="B511" s="2" t="s">
-        <v>76</v>
+        <v>312</v>
       </c>
       <c r="C511" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D511" s="2">
+        <v>77</v>
+      </c>
+      <c r="D511" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="E511" s="2">
         <v>128.0</v>
       </c>
-      <c r="E511" s="2" t="s">
-        <v>312</v>
-      </c>
     </row>
     <row r="512" ht="12.75" customHeight="1">
-      <c r="B512" s="2" t="s">
-        <v>307</v>
+      <c r="C512" s="2" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="513" ht="12.75" customHeight="1">
-      <c r="B513" s="2" t="s">
+      <c r="C513" s="2" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="514" ht="12.75" customHeight="1">
-      <c r="B514" s="2" t="s">
+      <c r="C514" s="2" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="515" ht="12.75" customHeight="1">
       <c r="B515" s="2" t="s">
-        <v>76</v>
+        <v>313</v>
       </c>
       <c r="C515" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D515" s="2">
+        <v>77</v>
+      </c>
+      <c r="D515" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E515" s="2">
         <v>129.0</v>
       </c>
-      <c r="E515" s="2" t="s">
-        <v>313</v>
-      </c>
     </row>
     <row r="516" ht="12.75" customHeight="1">
-      <c r="B516" s="2" t="s">
-        <v>307</v>
+      <c r="C516" s="2" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="517" ht="12.75" customHeight="1">
-      <c r="B517" s="2" t="s">
+      <c r="C517" s="2" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="518" ht="12.75" customHeight="1">
-      <c r="B518" s="2" t="s">
+      <c r="C518" s="2" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="519" ht="12.75" customHeight="1">
       <c r="B519" s="2" t="s">
-        <v>76</v>
+        <v>314</v>
       </c>
       <c r="C519" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D519" s="2">
+        <v>77</v>
+      </c>
+      <c r="D519" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E519" s="2">
         <v>130.0</v>
       </c>
-      <c r="E519" s="2" t="s">
-        <v>314</v>
-      </c>
     </row>
     <row r="520" ht="12.75" customHeight="1">
-      <c r="B520" s="2" t="s">
-        <v>307</v>
+      <c r="C520" s="2" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="521" ht="12.75" customHeight="1">
-      <c r="B521" s="2" t="s">
+      <c r="C521" s="2" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="522" ht="12.75" customHeight="1">
-      <c r="B522" s="2" t="s">
+      <c r="C522" s="2" t="s">
         <v>310</v>
       </c>
     </row>
@@ -5409,150 +5412,150 @@
       <c r="A523" s="2">
         <v>27.0</v>
       </c>
-      <c r="B523" s="2" t="s">
-        <v>76</v>
+      <c r="B523" s="3" t="s">
+        <v>315</v>
       </c>
       <c r="C523" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D523" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D523" s="2">
+      <c r="E523" s="2">
         <v>131.0</v>
-      </c>
-      <c r="E523" s="3" t="s">
-        <v>315</v>
       </c>
       <c r="F523" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="524" ht="12.75" customHeight="1">
-      <c r="B524" s="2" t="s">
+      <c r="C524" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="525" ht="12.75" customHeight="1">
-      <c r="B525" s="2" t="s">
+      <c r="C525" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="526" ht="12.75" customHeight="1">
-      <c r="B526" s="2" t="s">
+      <c r="C526" s="2" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="527" ht="12.75" customHeight="1">
-      <c r="B527" s="2" t="s">
-        <v>76</v>
+      <c r="B527" s="3" t="s">
+        <v>316</v>
       </c>
       <c r="C527" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D527" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D527" s="2">
+      <c r="E527" s="2">
         <v>132.0</v>
       </c>
-      <c r="E527" s="3" t="s">
-        <v>316</v>
-      </c>
     </row>
     <row r="528" ht="12.75" customHeight="1">
-      <c r="B528" s="2" t="s">
+      <c r="C528" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="529" ht="12.75" customHeight="1">
-      <c r="B529" s="2" t="s">
+      <c r="C529" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="530" ht="12.75" customHeight="1">
-      <c r="B530" s="2" t="s">
+      <c r="C530" s="2" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="531" ht="12.75" customHeight="1">
-      <c r="B531" s="2" t="s">
-        <v>76</v>
+      <c r="B531" s="3" t="s">
+        <v>317</v>
       </c>
       <c r="C531" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D531" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D531" s="2">
+      <c r="E531" s="2">
         <v>133.0</v>
       </c>
-      <c r="E531" s="3" t="s">
-        <v>317</v>
-      </c>
     </row>
     <row r="532" ht="12.75" customHeight="1">
-      <c r="B532" s="2" t="s">
+      <c r="C532" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="533" ht="12.75" customHeight="1">
-      <c r="B533" s="2" t="s">
+      <c r="C533" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="534" ht="12.75" customHeight="1">
-      <c r="B534" s="2" t="s">
+      <c r="C534" s="2" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="535" ht="12.75" customHeight="1">
-      <c r="B535" s="2" t="s">
+      <c r="B535" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C535" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="C535" s="2" t="s">
+      <c r="D535" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="D535" s="2">
+      <c r="E535" s="2">
         <v>134.0</v>
       </c>
-      <c r="E535" s="3" t="s">
-        <v>318</v>
-      </c>
     </row>
     <row r="536" ht="12.75" customHeight="1">
-      <c r="B536" s="2" t="s">
+      <c r="C536" s="2" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="537" ht="12.75" customHeight="1">
-      <c r="B537" s="2" t="s">
+      <c r="C537" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="538" ht="12.75" customHeight="1">
-      <c r="B538" s="2" t="s">
+      <c r="C538" s="2" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="539" ht="12.75" customHeight="1">
-      <c r="B539" s="2" t="s">
-        <v>76</v>
+      <c r="B539" s="3" t="s">
+        <v>319</v>
       </c>
       <c r="C539" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D539" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D539" s="2">
+      <c r="E539" s="2">
         <v>135.0</v>
       </c>
-      <c r="E539" s="3" t="s">
-        <v>319</v>
-      </c>
     </row>
     <row r="540" ht="12.75" customHeight="1">
-      <c r="B540" s="2" t="s">
+      <c r="C540" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="541" ht="12.75" customHeight="1">
-      <c r="B541" s="2" t="s">
+      <c r="C541" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="542" ht="12.75" customHeight="1">
-      <c r="B542" s="2" t="s">
+      <c r="C542" s="2" t="s">
         <v>195</v>
       </c>
     </row>
@@ -5561,149 +5564,149 @@
         <v>28.0</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>76</v>
+        <v>320</v>
       </c>
       <c r="C543" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D543" s="2">
+        <v>77</v>
+      </c>
+      <c r="D543" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E543" s="2">
         <v>136.0</v>
-      </c>
-      <c r="E543" s="2" t="s">
-        <v>320</v>
       </c>
       <c r="F543" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="544" ht="12.75" customHeight="1">
-      <c r="B544" s="2" t="s">
-        <v>307</v>
+      <c r="C544" s="2" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="545" ht="12.75" customHeight="1">
-      <c r="B545" s="2" t="s">
+      <c r="C545" s="2" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="546" ht="12.75" customHeight="1">
-      <c r="B546" s="2" t="s">
+      <c r="C546" s="2" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="547" ht="12.75" customHeight="1">
       <c r="B547" s="2" t="s">
-        <v>76</v>
+        <v>321</v>
       </c>
       <c r="C547" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D547" s="2">
+        <v>77</v>
+      </c>
+      <c r="D547" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="E547" s="2">
         <v>137.0</v>
       </c>
-      <c r="E547" s="2" t="s">
-        <v>321</v>
-      </c>
     </row>
     <row r="548" ht="12.75" customHeight="1">
-      <c r="B548" s="2" t="s">
-        <v>307</v>
+      <c r="C548" s="2" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="549" ht="12.75" customHeight="1">
-      <c r="B549" s="2" t="s">
+      <c r="C549" s="2" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="550" ht="12.75" customHeight="1">
-      <c r="B550" s="2" t="s">
+      <c r="C550" s="2" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="551" ht="12.75" customHeight="1">
       <c r="B551" s="2" t="s">
-        <v>76</v>
+        <v>322</v>
       </c>
       <c r="C551" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D551" s="2">
+        <v>77</v>
+      </c>
+      <c r="D551" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E551" s="2">
         <v>138.0</v>
       </c>
-      <c r="E551" s="2" t="s">
-        <v>322</v>
-      </c>
     </row>
     <row r="552" ht="12.75" customHeight="1">
-      <c r="B552" s="2" t="s">
-        <v>307</v>
+      <c r="C552" s="2" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="553" ht="12.75" customHeight="1">
-      <c r="B553" s="2" t="s">
+      <c r="C553" s="2" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="554" ht="12.75" customHeight="1">
-      <c r="B554" s="2" t="s">
+      <c r="C554" s="2" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="555" ht="12.75" customHeight="1">
       <c r="B555" s="2" t="s">
-        <v>76</v>
+        <v>307</v>
       </c>
       <c r="C555" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D555" s="2">
+        <v>77</v>
+      </c>
+      <c r="D555" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="E555" s="2">
         <v>139.0</v>
       </c>
-      <c r="E555" s="2" t="s">
+    </row>
+    <row r="556" ht="12.75" customHeight="1">
+      <c r="C556" s="2" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="556" ht="12.75" customHeight="1">
-      <c r="B556" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
     <row r="557" ht="12.75" customHeight="1">
-      <c r="B557" s="2" t="s">
+      <c r="C557" s="2" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="558" ht="12.75" customHeight="1">
-      <c r="B558" s="2" t="s">
+      <c r="C558" s="2" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="559" ht="12.75" customHeight="1">
       <c r="B559" s="2" t="s">
-        <v>76</v>
+        <v>323</v>
       </c>
       <c r="C559" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D559" s="2">
+        <v>77</v>
+      </c>
+      <c r="D559" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="E559" s="2">
         <v>140.0</v>
       </c>
-      <c r="E559" s="2" t="s">
-        <v>323</v>
-      </c>
     </row>
     <row r="560" ht="12.75" customHeight="1">
-      <c r="B560" s="2" t="s">
-        <v>307</v>
+      <c r="C560" s="2" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="561" ht="12.75" customHeight="1">
-      <c r="B561" s="2" t="s">
+      <c r="C561" s="2" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="562" ht="12.75" customHeight="1">
-      <c r="B562" s="2" t="s">
+      <c r="C562" s="2" t="s">
         <v>310</v>
       </c>
     </row>
@@ -5711,150 +5714,150 @@
       <c r="A563" s="2">
         <v>29.0</v>
       </c>
-      <c r="B563" s="2" t="s">
+      <c r="B563" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C563" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C563" s="2" t="s">
+      <c r="D563" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D563" s="2">
+      <c r="E563" s="2">
         <v>141.0</v>
-      </c>
-      <c r="E563" s="3" t="s">
-        <v>324</v>
       </c>
       <c r="F563" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="564" ht="12.75" customHeight="1">
-      <c r="B564" s="2" t="s">
+      <c r="C564" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="565" ht="12.75" customHeight="1">
-      <c r="B565" s="2" t="s">
-        <v>76</v>
+      <c r="C565" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="566" ht="12.75" customHeight="1">
-      <c r="B566" s="2" t="s">
+      <c r="C566" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="567" ht="12.75" customHeight="1">
-      <c r="B567" s="2" t="s">
-        <v>76</v>
+      <c r="B567" s="3" t="s">
+        <v>325</v>
       </c>
       <c r="C567" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D567" s="2">
+        <v>77</v>
+      </c>
+      <c r="D567" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E567" s="2">
         <v>142.0</v>
       </c>
-      <c r="E567" s="3" t="s">
-        <v>325</v>
-      </c>
     </row>
     <row r="568" ht="12.75" customHeight="1">
-      <c r="B568" s="2" t="s">
+      <c r="C568" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="569" ht="12.75" customHeight="1">
-      <c r="B569" s="2" t="s">
+      <c r="C569" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="570" ht="12.75" customHeight="1">
-      <c r="B570" s="2" t="s">
+      <c r="C570" s="2" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="571" ht="12.75" customHeight="1">
-      <c r="B571" s="2" t="s">
-        <v>76</v>
+      <c r="B571" s="3" t="s">
+        <v>326</v>
       </c>
       <c r="C571" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D571" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D571" s="2">
+      <c r="E571" s="2">
         <v>143.0</v>
       </c>
-      <c r="E571" s="3" t="s">
-        <v>326</v>
-      </c>
     </row>
     <row r="572" ht="12.75" customHeight="1">
-      <c r="B572" s="2" t="s">
+      <c r="C572" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="573" ht="12.75" customHeight="1">
-      <c r="B573" s="2" t="s">
+      <c r="C573" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="574" ht="12.75" customHeight="1">
-      <c r="B574" s="2" t="s">
+      <c r="C574" s="2" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="575" ht="12.75" customHeight="1">
-      <c r="B575" s="2" t="s">
-        <v>76</v>
+      <c r="B575" s="3" t="s">
+        <v>327</v>
       </c>
       <c r="C575" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D575" s="2">
+        <v>77</v>
+      </c>
+      <c r="D575" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E575" s="2">
         <v>144.0</v>
       </c>
-      <c r="E575" s="3" t="s">
-        <v>327</v>
-      </c>
     </row>
     <row r="576" ht="12.75" customHeight="1">
-      <c r="B576" s="2" t="s">
+      <c r="C576" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="577" ht="12.75" customHeight="1">
-      <c r="B577" s="2" t="s">
+      <c r="C577" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="578" ht="12.75" customHeight="1">
-      <c r="B578" s="2" t="s">
+      <c r="C578" s="2" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="579" ht="12.75" customHeight="1">
-      <c r="B579" s="2" t="s">
-        <v>76</v>
+      <c r="B579" s="3" t="s">
+        <v>328</v>
       </c>
       <c r="C579" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D579" s="2">
+        <v>77</v>
+      </c>
+      <c r="D579" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E579" s="2">
         <v>145.0</v>
       </c>
-      <c r="E579" s="3" t="s">
-        <v>328</v>
-      </c>
     </row>
     <row r="580" ht="12.75" customHeight="1">
-      <c r="B580" s="2" t="s">
+      <c r="C580" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="581" ht="12.75" customHeight="1">
-      <c r="B581" s="2" t="s">
+      <c r="C581" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="582" ht="12.75" customHeight="1">
-      <c r="B582" s="2" t="s">
+      <c r="C582" s="2" t="s">
         <v>195</v>
       </c>
     </row>
@@ -5862,34 +5865,34 @@
       <c r="A583" s="2">
         <v>30.0</v>
       </c>
-      <c r="B583" s="2">
+      <c r="B583" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C583" s="2">
         <v>24.0</v>
       </c>
-      <c r="C583" s="2">
+      <c r="D583" s="2">
         <v>26.0</v>
       </c>
-      <c r="D583" s="2">
+      <c r="E583" s="2">
         <v>146.0</v>
-      </c>
-      <c r="E583" s="2" t="s">
-        <v>329</v>
       </c>
       <c r="F583" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="584" ht="12.75" customHeight="1">
-      <c r="B584" s="2">
+      <c r="C584" s="2">
         <v>25.0</v>
       </c>
     </row>
     <row r="585" ht="12.75" customHeight="1">
-      <c r="B585" s="2">
+      <c r="C585" s="2">
         <v>26.0</v>
       </c>
     </row>
     <row r="586" ht="12.75" customHeight="1">
-      <c r="B586" s="2">
+      <c r="C586" s="2">
         <v>27.0</v>
       </c>
     </row>
@@ -5900,54 +5903,54 @@
       <c r="C587" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="D587" s="2">
+      <c r="D587" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="E587" s="2">
         <v>147.0</v>
       </c>
-      <c r="E587" s="2" t="s">
+    </row>
+    <row r="588" ht="12.75" customHeight="1">
+      <c r="C588" s="2" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="588" ht="12.75" customHeight="1">
-      <c r="B588" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
     <row r="589" ht="12.75" customHeight="1">
-      <c r="B589" s="2" t="s">
+      <c r="C589" s="2" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="590" ht="12.75" customHeight="1">
-      <c r="B590" s="2" t="s">
+      <c r="C590" s="2" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="591" ht="12.75" customHeight="1">
       <c r="B591" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C591" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C591" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D591" s="2">
+      <c r="D591" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E591" s="2">
         <v>148.0</v>
       </c>
-      <c r="E591" s="2" t="s">
-        <v>335</v>
-      </c>
     </row>
     <row r="592" ht="12.75" customHeight="1">
-      <c r="B592" s="2" t="s">
+      <c r="C592" s="2" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="593" ht="12.75" customHeight="1">
-      <c r="B593" s="2" t="s">
-        <v>100</v>
+      <c r="C593" s="2" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="594" ht="12.75" customHeight="1">
-      <c r="B594" s="2" t="s">
+      <c r="C594" s="2" t="s">
         <v>336</v>
       </c>
     </row>
@@ -5956,56 +5959,56 @@
         <v>337</v>
       </c>
       <c r="C595" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="D595" s="2">
+        <v>338</v>
+      </c>
+      <c r="D595" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E595" s="2">
         <v>149.0</v>
       </c>
-      <c r="E595" s="2" t="s">
-        <v>338</v>
-      </c>
     </row>
     <row r="596" ht="12.75" customHeight="1">
-      <c r="B596" s="2" t="s">
+      <c r="C596" s="2" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="597" ht="12.75" customHeight="1">
-      <c r="B597" s="2" t="s">
+      <c r="C597" s="2" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="598" ht="12.75" customHeight="1">
-      <c r="B598" s="2" t="s">
+      <c r="C598" s="2" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="599" ht="12.75" customHeight="1">
-      <c r="B599" s="2">
+      <c r="B599" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C599" s="2">
         <v>3.0</v>
       </c>
-      <c r="C599" s="2">
+      <c r="D599" s="2">
         <v>4.0</v>
       </c>
-      <c r="D599" s="2">
+      <c r="E599" s="2">
         <v>150.0</v>
       </c>
-      <c r="E599" s="2" t="s">
-        <v>342</v>
-      </c>
     </row>
     <row r="600" ht="12.75" customHeight="1">
-      <c r="B600" s="2">
+      <c r="C600" s="2">
         <v>4.0</v>
       </c>
     </row>
     <row r="601" ht="12.75" customHeight="1">
-      <c r="B601" s="2">
+      <c r="C601" s="2">
         <v>5.0</v>
       </c>
     </row>
     <row r="602" ht="12.75" customHeight="1">
-      <c r="B602" s="2">
+      <c r="C602" s="2">
         <v>6.0</v>
       </c>
     </row>
@@ -6017,30 +6020,30 @@
         <v>343</v>
       </c>
       <c r="C603" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D603" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="D603" s="2">
+      <c r="E603" s="2">
         <v>151.0</v>
-      </c>
-      <c r="E603" s="2" t="s">
-        <v>344</v>
       </c>
       <c r="F603" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="604" ht="12.75" customHeight="1">
-      <c r="B604" s="2" t="s">
+      <c r="C604" s="2" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="605" ht="12.75" customHeight="1">
-      <c r="B605" s="2" t="s">
+      <c r="C605" s="2" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="606" ht="12.75" customHeight="1">
-      <c r="B606" s="2" t="s">
+      <c r="C606" s="2" t="s">
         <v>346</v>
       </c>
     </row>
@@ -6049,27 +6052,27 @@
         <v>347</v>
       </c>
       <c r="C607" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="D607" s="2">
+        <v>348</v>
+      </c>
+      <c r="D607" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E607" s="2">
         <v>152.0</v>
       </c>
-      <c r="E607" s="2" t="s">
-        <v>348</v>
-      </c>
     </row>
     <row r="608" ht="12.75" customHeight="1">
-      <c r="B608" s="2" t="s">
+      <c r="C608" s="2" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="609" ht="12.75" customHeight="1">
-      <c r="B609" s="2" t="s">
+      <c r="C609" s="2" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="610" ht="12.75" customHeight="1">
-      <c r="B610" s="2" t="s">
+      <c r="C610" s="2" t="s">
         <v>103</v>
       </c>
     </row>
@@ -6080,54 +6083,54 @@
       <c r="C611" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="D611" s="2">
+      <c r="D611" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="E611" s="2">
         <v>153.0</v>
       </c>
-      <c r="E611" s="2" t="s">
+    </row>
+    <row r="612" ht="12.75" customHeight="1">
+      <c r="C612" s="2" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="612" ht="12.75" customHeight="1">
-      <c r="B612" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
     <row r="613" ht="12.75" customHeight="1">
-      <c r="B613" s="2" t="s">
+      <c r="C613" s="2" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="614" ht="12.75" customHeight="1">
-      <c r="B614" s="2" t="s">
+      <c r="C614" s="2" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="615" ht="12.75" customHeight="1">
-      <c r="B615" s="2">
+      <c r="B615" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C615" s="2">
         <v>1.0</v>
       </c>
-      <c r="C615" s="2">
+      <c r="D615" s="2">
         <v>2.0</v>
       </c>
-      <c r="D615" s="2">
+      <c r="E615" s="2">
         <v>154.0</v>
       </c>
-      <c r="E615" s="2" t="s">
-        <v>354</v>
-      </c>
     </row>
     <row r="616" ht="12.75" customHeight="1">
-      <c r="B616" s="2">
+      <c r="C616" s="2">
         <v>2.0</v>
       </c>
     </row>
     <row r="617" ht="12.75" customHeight="1">
-      <c r="B617" s="2">
+      <c r="C617" s="2">
         <v>3.0</v>
       </c>
     </row>
     <row r="618" ht="12.75" customHeight="1">
-      <c r="B618" s="2">
+      <c r="C618" s="2">
         <v>4.0</v>
       </c>
     </row>
@@ -6138,25 +6141,25 @@
       <c r="C619" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="D619" s="2">
+      <c r="D619" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E619" s="2">
         <v>155.0</v>
       </c>
-      <c r="E619" s="2" t="s">
+    </row>
+    <row r="620" ht="12.75" customHeight="1">
+      <c r="C620" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="621" ht="12.75" customHeight="1">
+      <c r="C621" s="2" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="620" ht="12.75" customHeight="1">
-      <c r="B620" s="2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="621" ht="12.75" customHeight="1">
-      <c r="B621" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
     <row r="622" ht="12.75" customHeight="1">
-      <c r="B622" s="2" t="s">
+      <c r="C622" s="2" t="s">
         <v>359</v>
       </c>
     </row>
@@ -6165,120 +6168,120 @@
         <v>32.0</v>
       </c>
       <c r="B623" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C623" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C623" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="D623" s="2">
+      <c r="D623" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="E623" s="2">
         <v>156.0</v>
-      </c>
-      <c r="E623" s="2" t="s">
-        <v>361</v>
       </c>
       <c r="F623" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="624" ht="12.75" customHeight="1">
-      <c r="B624" s="2" t="s">
-        <v>360</v>
+      <c r="C624" s="2" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="625" ht="12.75" customHeight="1">
-      <c r="B625" s="2" t="s">
+      <c r="C625" s="2" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="626" ht="12.75" customHeight="1">
-      <c r="B626" s="2" t="s">
+      <c r="C626" s="2" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="627" ht="12.75" customHeight="1">
       <c r="B627" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C627" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="C627" s="2" t="s">
+      <c r="D627" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="D627" s="2">
+      <c r="E627" s="2">
         <v>157.0</v>
       </c>
-      <c r="E627" s="2" t="s">
-        <v>363</v>
-      </c>
     </row>
     <row r="628" ht="12.75" customHeight="1">
-      <c r="B628" s="2" t="s">
-        <v>330</v>
+      <c r="C628" s="2" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="629" ht="12.75" customHeight="1">
-      <c r="B629" s="2" t="s">
+      <c r="C629" s="2" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="630" ht="12.75" customHeight="1">
-      <c r="B630" s="2" t="s">
-        <v>331</v>
+      <c r="C630" s="2" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="631" ht="12.75" customHeight="1">
       <c r="B631" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C631" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C631" s="2" t="s">
+      <c r="D631" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D631" s="2">
+      <c r="E631" s="2">
         <v>158.0</v>
       </c>
-      <c r="E631" s="2" t="s">
-        <v>364</v>
-      </c>
     </row>
     <row r="632" ht="12.75" customHeight="1">
-      <c r="B632" s="2" t="s">
+      <c r="C632" s="2" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="633" ht="12.75" customHeight="1">
-      <c r="B633" s="2" t="s">
-        <v>100</v>
+      <c r="C633" s="2" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="634" ht="12.75" customHeight="1">
-      <c r="B634" s="2" t="s">
+      <c r="C634" s="2" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="635" ht="12.75" customHeight="1">
       <c r="B635" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C635" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="C635" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="D635" s="2">
+      <c r="D635" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="E635" s="2">
         <v>159.0</v>
       </c>
-      <c r="E635" s="2" t="s">
+    </row>
+    <row r="636" ht="12.75" customHeight="1">
+      <c r="C636" s="2" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="636" ht="12.75" customHeight="1">
-      <c r="B636" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="637" ht="12.75" customHeight="1">
-      <c r="B637" s="2" t="s">
+      <c r="C637" s="2" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="638" ht="12.75" customHeight="1">
-      <c r="B638" s="2" t="s">
+      <c r="C638" s="2" t="s">
         <v>368</v>
       </c>
     </row>
@@ -6289,25 +6292,25 @@
       <c r="C639" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="D639" s="2">
+      <c r="D639" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E639" s="2">
         <v>160.0</v>
       </c>
-      <c r="E639" s="2" t="s">
+    </row>
+    <row r="640" ht="12.75" customHeight="1">
+      <c r="C640" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="641" ht="12.75" customHeight="1">
+      <c r="C641" s="2" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="640" ht="12.75" customHeight="1">
-      <c r="B640" s="2" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="641" ht="12.75" customHeight="1">
-      <c r="B641" s="2" t="s">
-        <v>370</v>
-      </c>
-    </row>
     <row r="642" ht="12.75" customHeight="1">
-      <c r="B642" s="2" t="s">
+      <c r="C642" s="2" t="s">
         <v>373</v>
       </c>
     </row>
@@ -6670,9 +6673,8 @@
     <row r="999" ht="12.75" customHeight="1"/>
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:E1"/>
     <mergeCell ref="F1:F2"/>
   </mergeCells>
   <printOptions/>

--- a/English1.xlsx
+++ b/English1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="373">
   <si>
     <t>id</t>
   </si>
@@ -262,9 +262,6 @@
   </si>
   <si>
     <t>ca_</t>
-  </si>
-  <si>
-    <t>Quả trứng</t>
   </si>
   <si>
     <t>n</t>
@@ -2279,7 +2276,7 @@
       <c r="C107" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D107" s="2" t="s">
+      <c r="D107" s="3" t="s">
         <v>82</v>
       </c>
       <c r="E107" s="2">
@@ -2298,12 +2295,12 @@
     </row>
     <row r="110" ht="12.75" customHeight="1">
       <c r="C110" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="111" ht="12.75" customHeight="1">
       <c r="B111" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>77</v>
@@ -2332,13 +2329,13 @@
     </row>
     <row r="115" ht="12.75" customHeight="1">
       <c r="B115" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>77</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E115" s="2">
         <v>29.0</v>
@@ -2346,7 +2343,7 @@
     </row>
     <row r="116" ht="12.75" customHeight="1">
       <c r="C116" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="117" ht="12.75" customHeight="1">
@@ -2361,7 +2358,7 @@
     </row>
     <row r="119" ht="12.75" customHeight="1">
       <c r="B119" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C119" s="3" t="s">
         <v>77</v>
@@ -2393,13 +2390,13 @@
         <v>7.0</v>
       </c>
       <c r="B123" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C123" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C123" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="D123" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E123" s="2">
         <v>31.0</v>
@@ -2410,28 +2407,28 @@
     </row>
     <row r="124" ht="12.75" customHeight="1">
       <c r="C124" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="125" ht="12.75" customHeight="1">
       <c r="C125" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="126" ht="12.75" customHeight="1">
       <c r="C126" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="127" ht="12.75" customHeight="1">
       <c r="B127" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D127" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>94</v>
       </c>
       <c r="E127" s="2">
         <v>32.0</v>
@@ -2439,28 +2436,28 @@
     </row>
     <row r="128" ht="12.75" customHeight="1">
       <c r="C128" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="129" ht="12.75" customHeight="1">
       <c r="C129" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="130" ht="12.75" customHeight="1">
       <c r="C130" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="131" ht="12.75" customHeight="1">
       <c r="B131" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C131" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C131" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="D131" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E131" s="2">
         <v>33.0</v>
@@ -2468,28 +2465,28 @@
     </row>
     <row r="132" ht="12.75" customHeight="1">
       <c r="C132" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="133" ht="12.75" customHeight="1">
       <c r="C133" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="134" ht="12.75" customHeight="1">
       <c r="C134" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="135" ht="12.75" customHeight="1">
       <c r="B135" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C135" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C135" s="3" t="s">
+      <c r="D135" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="D135" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="E135" s="2">
         <v>34.0</v>
@@ -2497,28 +2494,28 @@
     </row>
     <row r="136" ht="12.75" customHeight="1">
       <c r="C136" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="137" ht="12.75" customHeight="1">
       <c r="C137" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="138" ht="12.75" customHeight="1">
       <c r="C138" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="139" ht="12.75" customHeight="1">
       <c r="B139" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C139" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C139" s="3" t="s">
+      <c r="D139" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="D139" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="E139" s="2">
         <v>35.0</v>
@@ -2526,17 +2523,17 @@
     </row>
     <row r="140" ht="12.75" customHeight="1">
       <c r="C140" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="141" ht="12.75" customHeight="1">
       <c r="C141" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="142" ht="12.75" customHeight="1">
       <c r="C142" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="143" ht="12.75" customHeight="1">
@@ -2544,13 +2541,13 @@
         <v>8.0</v>
       </c>
       <c r="B143" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C143" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C143" s="3" t="s">
+      <c r="D143" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="D143" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="E143" s="2">
         <v>36.0</v>
@@ -2561,28 +2558,28 @@
     </row>
     <row r="144" ht="12.75" customHeight="1">
       <c r="C144" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="145" ht="12.75" customHeight="1">
       <c r="C145" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="146" ht="12.75" customHeight="1">
       <c r="C146" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="147" ht="12.75" customHeight="1">
       <c r="B147" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D147" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D147" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="E147" s="2">
         <v>37.0</v>
@@ -2590,28 +2587,28 @@
     </row>
     <row r="148" ht="12.75" customHeight="1">
       <c r="C148" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="149" ht="12.75" customHeight="1">
       <c r="C149" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="150" ht="12.75" customHeight="1">
       <c r="C150" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="151" ht="12.75" customHeight="1">
       <c r="B151" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E151" s="2">
         <v>38.0</v>
@@ -2619,28 +2616,28 @@
     </row>
     <row r="152" ht="12.75" customHeight="1">
       <c r="C152" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="153" ht="12.75" customHeight="1">
       <c r="C153" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="154" ht="12.75" customHeight="1">
       <c r="C154" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="155" ht="12.75" customHeight="1">
       <c r="B155" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C155" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C155" s="3" t="s">
+      <c r="D155" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="D155" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="E155" s="2">
         <v>39.0</v>
@@ -2648,28 +2645,28 @@
     </row>
     <row r="156" ht="12.75" customHeight="1">
       <c r="C156" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="157" ht="12.75" customHeight="1">
       <c r="C157" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="158" ht="12.75" customHeight="1">
       <c r="C158" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="159" ht="12.75" customHeight="1">
       <c r="B159" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C159" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C159" s="3" t="s">
+      <c r="D159" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="D159" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="E159" s="2">
         <v>40.0</v>
@@ -2677,17 +2674,17 @@
     </row>
     <row r="160" ht="12.75" customHeight="1">
       <c r="C160" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="161" ht="12.75" customHeight="1">
       <c r="C161" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="162" ht="12.75" customHeight="1">
       <c r="C162" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="163" ht="12.75" customHeight="1">
@@ -2695,13 +2692,13 @@
         <v>9.0</v>
       </c>
       <c r="B163" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C163" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C163" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="D163" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E163" s="2">
         <v>41.0</v>
@@ -2712,28 +2709,28 @@
     </row>
     <row r="164" ht="12.75" customHeight="1">
       <c r="C164" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="165" ht="12.75" customHeight="1">
       <c r="C165" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="166" ht="12.75" customHeight="1">
       <c r="C166" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="167" ht="12.75" customHeight="1">
       <c r="B167" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D167" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="C167" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D167" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="E167" s="2">
         <v>42.0</v>
@@ -2741,28 +2738,28 @@
     </row>
     <row r="168" ht="12.75" customHeight="1">
       <c r="C168" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="169" ht="12.75" customHeight="1">
       <c r="C169" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="170" ht="12.75" customHeight="1">
       <c r="C170" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="171" ht="12.75" customHeight="1">
       <c r="B171" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D171" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="C171" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D171" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="E171" s="2">
         <v>43.0</v>
@@ -2770,28 +2767,28 @@
     </row>
     <row r="172" ht="12.75" customHeight="1">
       <c r="C172" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="173" ht="12.75" customHeight="1">
       <c r="C173" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="174" ht="12.75" customHeight="1">
       <c r="C174" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="175" ht="12.75" customHeight="1">
       <c r="B175" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C175" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C175" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="D175" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E175" s="2">
         <v>44.0</v>
@@ -2799,28 +2796,28 @@
     </row>
     <row r="176" ht="12.75" customHeight="1">
       <c r="C176" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="177" ht="12.75" customHeight="1">
       <c r="C177" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="178" ht="12.75" customHeight="1">
       <c r="C178" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="179" ht="12.75" customHeight="1">
       <c r="B179" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C179" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C179" s="3" t="s">
+      <c r="D179" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="D179" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="E179" s="2">
         <v>45.0</v>
@@ -2828,17 +2825,17 @@
     </row>
     <row r="180" ht="12.75" customHeight="1">
       <c r="C180" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="181" ht="12.75" customHeight="1">
       <c r="C181" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="182" ht="12.75" customHeight="1">
       <c r="C182" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="183" ht="12.75" customHeight="1">
@@ -2846,13 +2843,13 @@
         <v>10.0</v>
       </c>
       <c r="B183" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C183" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C183" s="3" t="s">
+      <c r="D183" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="D183" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="E183" s="2">
         <v>46.0</v>
@@ -2863,28 +2860,28 @@
     </row>
     <row r="184" ht="12.75" customHeight="1">
       <c r="C184" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="185" ht="12.75" customHeight="1">
       <c r="C185" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="186" ht="12.75" customHeight="1">
       <c r="C186" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="187" ht="12.75" customHeight="1">
       <c r="B187" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E187" s="2">
         <v>47.0</v>
@@ -2892,28 +2889,28 @@
     </row>
     <row r="188" ht="12.75" customHeight="1">
       <c r="C188" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="189" ht="12.75" customHeight="1">
       <c r="C189" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="190" ht="12.75" customHeight="1">
       <c r="C190" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="191" ht="12.75" customHeight="1">
       <c r="B191" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C191" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C191" s="3" t="s">
+      <c r="D191" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="D191" s="2" t="s">
-        <v>158</v>
       </c>
       <c r="E191" s="2">
         <v>48.0</v>
@@ -2921,28 +2918,28 @@
     </row>
     <row r="192" ht="12.75" customHeight="1">
       <c r="C192" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="193" ht="12.75" customHeight="1">
       <c r="C193" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="194" ht="12.75" customHeight="1">
       <c r="C194" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="195" ht="12.75" customHeight="1">
       <c r="B195" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C195" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C195" s="2" t="s">
-        <v>160</v>
-      </c>
       <c r="D195" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E195" s="2">
         <v>49.0</v>
@@ -2950,28 +2947,28 @@
     </row>
     <row r="196" ht="12.75" customHeight="1">
       <c r="C196" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="197" ht="12.75" customHeight="1">
       <c r="C197" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="198" ht="12.75" customHeight="1">
       <c r="C198" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="199" ht="12.75" customHeight="1">
       <c r="B199" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C199" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C199" s="3" t="s">
+      <c r="D199" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="D199" s="2" t="s">
-        <v>166</v>
       </c>
       <c r="E199" s="2">
         <v>50.0</v>
@@ -2979,17 +2976,17 @@
     </row>
     <row r="200" ht="12.75" customHeight="1">
       <c r="C200" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="201" ht="12.75" customHeight="1">
       <c r="C201" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="202" ht="12.75" customHeight="1">
       <c r="C202" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="203" ht="12.75" customHeight="1">
@@ -2997,13 +2994,13 @@
         <v>11.0</v>
       </c>
       <c r="B203" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C203" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C203" s="2" t="s">
-        <v>170</v>
-      </c>
       <c r="D203" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E203" s="2">
         <v>51.0</v>
@@ -3014,28 +3011,28 @@
     </row>
     <row r="204" ht="12.75" customHeight="1">
       <c r="C204" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="205" ht="12.75" customHeight="1">
       <c r="C205" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="206" ht="12.75" customHeight="1">
       <c r="C206" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="207" ht="12.75" customHeight="1">
       <c r="B207" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C207" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C207" s="2" t="s">
+      <c r="D207" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="D207" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="E207" s="2">
         <v>52.0</v>
@@ -3043,28 +3040,28 @@
     </row>
     <row r="208" ht="12.75" customHeight="1">
       <c r="C208" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="209" ht="12.75" customHeight="1">
       <c r="C209" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="210" ht="12.75" customHeight="1">
       <c r="C210" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="211" ht="12.75" customHeight="1">
       <c r="B211" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C211" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C211" s="2" t="s">
+      <c r="D211" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="D211" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="E211" s="2">
         <v>53.0</v>
@@ -3072,28 +3069,28 @@
     </row>
     <row r="212" ht="12.75" customHeight="1">
       <c r="C212" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="213" ht="12.75" customHeight="1">
       <c r="C213" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="214" ht="12.75" customHeight="1">
       <c r="C214" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="215" ht="12.75" customHeight="1">
       <c r="B215" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C215" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C215" s="3" t="s">
+      <c r="D215" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="D215" s="2" t="s">
-        <v>186</v>
       </c>
       <c r="E215" s="2">
         <v>54.0</v>
@@ -3101,28 +3098,28 @@
     </row>
     <row r="216" ht="12.75" customHeight="1">
       <c r="C216" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="217" ht="12.75" customHeight="1">
       <c r="C217" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="218" ht="12.75" customHeight="1">
       <c r="C218" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="219" ht="12.75" customHeight="1">
       <c r="B219" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E219" s="2">
         <v>55.0</v>
@@ -3130,17 +3127,17 @@
     </row>
     <row r="220" ht="12.75" customHeight="1">
       <c r="C220" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="221" ht="12.75" customHeight="1">
       <c r="C221" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="222" ht="12.75" customHeight="1">
       <c r="C222" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="223" ht="12.75" customHeight="1">
@@ -3148,13 +3145,13 @@
         <v>12.0</v>
       </c>
       <c r="B223" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C223" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C223" s="2" t="s">
-        <v>191</v>
-      </c>
       <c r="D223" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E223" s="2">
         <v>56.0</v>
@@ -3165,28 +3162,28 @@
     </row>
     <row r="224" ht="12.75" customHeight="1">
       <c r="C224" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="225" ht="12.75" customHeight="1">
       <c r="C225" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="226" ht="12.75" customHeight="1">
       <c r="C226" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="227" ht="12.75" customHeight="1">
       <c r="B227" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E227" s="2">
         <v>57.0</v>
@@ -3194,28 +3191,28 @@
     </row>
     <row r="228" ht="12.75" customHeight="1">
       <c r="C228" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="229" ht="12.75" customHeight="1">
       <c r="C229" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="230" ht="12.75" customHeight="1">
       <c r="C230" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="231" ht="12.75" customHeight="1">
       <c r="B231" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E231" s="2">
         <v>58.0</v>
@@ -3223,22 +3220,22 @@
     </row>
     <row r="232" ht="12.75" customHeight="1">
       <c r="C232" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="233" ht="12.75" customHeight="1">
       <c r="C233" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="234" ht="12.75" customHeight="1">
       <c r="C234" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="235" ht="12.75" customHeight="1">
       <c r="B235" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>77</v>
@@ -3262,12 +3259,12 @@
     </row>
     <row r="238" ht="12.75" customHeight="1">
       <c r="C238" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="239" ht="12.75" customHeight="1">
       <c r="B239" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>77</v>
@@ -3291,7 +3288,7 @@
     </row>
     <row r="242" ht="12.75" customHeight="1">
       <c r="C242" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="243" ht="12.75" customHeight="1">
@@ -3299,13 +3296,13 @@
         <v>13.0</v>
       </c>
       <c r="B243" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C243" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C243" s="2" t="s">
+      <c r="D243" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="D243" s="2" t="s">
-        <v>199</v>
       </c>
       <c r="E243" s="2">
         <v>61.0</v>
@@ -3316,22 +3313,22 @@
     </row>
     <row r="244" ht="12.75" customHeight="1">
       <c r="C244" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="245" ht="12.75" customHeight="1">
       <c r="C245" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="246" ht="12.75" customHeight="1">
       <c r="C246" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="247" ht="12.75" customHeight="1">
       <c r="B247" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>77</v>
@@ -3355,12 +3352,12 @@
     </row>
     <row r="250" ht="12.75" customHeight="1">
       <c r="C250" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="251" ht="12.75" customHeight="1">
       <c r="B251" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>77</v>
@@ -3384,18 +3381,18 @@
     </row>
     <row r="254" ht="12.75" customHeight="1">
       <c r="C254" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="255" ht="12.75" customHeight="1">
       <c r="B255" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C255" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C255" s="2" t="s">
+      <c r="D255" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="D255" s="2" t="s">
-        <v>206</v>
       </c>
       <c r="E255" s="2">
         <v>64.0</v>
@@ -3403,28 +3400,28 @@
     </row>
     <row r="256" ht="12.75" customHeight="1">
       <c r="C256" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="257" ht="12.75" customHeight="1">
       <c r="C257" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="258" ht="12.75" customHeight="1">
       <c r="C258" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="259" ht="12.75" customHeight="1">
       <c r="B259" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C259" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C259" s="2" t="s">
-        <v>210</v>
-      </c>
       <c r="D259" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E259" s="2">
         <v>65.0</v>
@@ -3432,17 +3429,17 @@
     </row>
     <row r="260" ht="12.75" customHeight="1">
       <c r="C260" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="261" ht="12.75" customHeight="1">
       <c r="C261" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="262" ht="12.75" customHeight="1">
       <c r="C262" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="263" ht="12.75" customHeight="1">
@@ -3450,13 +3447,13 @@
         <v>14.0</v>
       </c>
       <c r="B263" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C263" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="C263" s="2" t="s">
+      <c r="D263" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="D263" s="2" t="s">
-        <v>216</v>
       </c>
       <c r="E263" s="2">
         <v>66.0</v>
@@ -3467,28 +3464,28 @@
     </row>
     <row r="264" ht="12.75" customHeight="1">
       <c r="C264" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="265" ht="12.75" customHeight="1">
       <c r="C265" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="266" ht="12.75" customHeight="1">
       <c r="C266" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="267" ht="12.75" customHeight="1">
       <c r="B267" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C267" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C267" s="2" t="s">
+      <c r="D267" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="D267" s="2" t="s">
-        <v>221</v>
       </c>
       <c r="E267" s="2">
         <v>67.0</v>
@@ -3496,28 +3493,28 @@
     </row>
     <row r="268" ht="12.75" customHeight="1">
       <c r="C268" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="269" ht="12.75" customHeight="1">
       <c r="C269" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="270" ht="12.75" customHeight="1">
       <c r="C270" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="271" ht="12.75" customHeight="1">
       <c r="B271" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C271" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C271" s="2" t="s">
+      <c r="D271" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="D271" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="E271" s="2">
         <v>68.0</v>
@@ -3525,22 +3522,22 @@
     </row>
     <row r="272" ht="12.75" customHeight="1">
       <c r="C272" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="273" ht="12.75" customHeight="1">
       <c r="C273" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="274" ht="12.75" customHeight="1">
       <c r="C274" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="275" ht="12.75" customHeight="1">
       <c r="B275" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>77</v>
@@ -3564,12 +3561,12 @@
     </row>
     <row r="278" ht="12.75" customHeight="1">
       <c r="C278" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="279" ht="12.75" customHeight="1">
       <c r="B279" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>77</v>
@@ -3593,7 +3590,7 @@
     </row>
     <row r="282" ht="12.75" customHeight="1">
       <c r="C282" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="283" ht="12.75" customHeight="1">
@@ -3601,13 +3598,13 @@
         <v>15.0</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C283" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E283" s="2">
         <v>71.0</v>
@@ -3628,18 +3625,18 @@
     </row>
     <row r="286" ht="12.75" customHeight="1">
       <c r="C286" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="287" ht="12.75" customHeight="1">
       <c r="B287" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E287" s="2">
         <v>72.0</v>
@@ -3647,22 +3644,22 @@
     </row>
     <row r="288" ht="12.75" customHeight="1">
       <c r="C288" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="289" ht="12.75" customHeight="1">
       <c r="C289" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="290" ht="12.75" customHeight="1">
       <c r="C290" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="291" ht="12.75" customHeight="1">
       <c r="B291" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>77</v>
@@ -3686,12 +3683,12 @@
     </row>
     <row r="294" ht="12.75" customHeight="1">
       <c r="C294" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="295" ht="12.75" customHeight="1">
       <c r="B295" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C295" s="2" t="s">
         <v>77</v>
@@ -3715,12 +3712,12 @@
     </row>
     <row r="298" ht="12.75" customHeight="1">
       <c r="C298" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="299" ht="12.75" customHeight="1">
       <c r="B299" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C299" s="2" t="s">
         <v>77</v>
@@ -3744,7 +3741,7 @@
     </row>
     <row r="302" ht="12.75" customHeight="1">
       <c r="C302" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="303" ht="12.75" customHeight="1">
@@ -3752,7 +3749,7 @@
         <v>16.0</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>77</v>
@@ -3779,18 +3776,18 @@
     </row>
     <row r="306" ht="12.75" customHeight="1">
       <c r="C306" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="307" ht="12.75" customHeight="1">
       <c r="B307" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E307" s="2">
         <v>77.0</v>
@@ -3798,22 +3795,22 @@
     </row>
     <row r="308" ht="12.75" customHeight="1">
       <c r="C308" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="309" ht="12.75" customHeight="1">
       <c r="C309" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="310" ht="12.75" customHeight="1">
       <c r="C310" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="311" ht="12.75" customHeight="1">
       <c r="B311" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>77</v>
@@ -3837,7 +3834,7 @@
     </row>
     <row r="314" ht="12.75" customHeight="1">
       <c r="C314" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="315" ht="12.75" customHeight="1">
@@ -3845,10 +3842,10 @@
         <v>1.0</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E315" s="2">
         <v>79.0</v>
@@ -3856,17 +3853,17 @@
     </row>
     <row r="316" ht="12.75" customHeight="1">
       <c r="C316" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="317" ht="12.75" customHeight="1">
       <c r="C317" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="318" ht="12.75" customHeight="1">
       <c r="C318" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="319" ht="12.75" customHeight="1">
@@ -3874,10 +3871,10 @@
         <v>3.0</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E319" s="2">
         <v>80.0</v>
@@ -3885,17 +3882,17 @@
     </row>
     <row r="320" ht="12.75" customHeight="1">
       <c r="C320" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="321" ht="12.75" customHeight="1">
       <c r="C321" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="322" ht="12.75" customHeight="1">
       <c r="C322" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="323" ht="12.75" customHeight="1">
@@ -3906,10 +3903,10 @@
         <v>4.0</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E323" s="2">
         <v>81.0</v>
@@ -3920,17 +3917,17 @@
     </row>
     <row r="324" ht="12.75" customHeight="1">
       <c r="C324" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="325" ht="12.75" customHeight="1">
       <c r="C325" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="326" ht="12.75" customHeight="1">
       <c r="C326" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="327" ht="12.75" customHeight="1">
@@ -3938,10 +3935,10 @@
         <v>2.0</v>
       </c>
       <c r="C327" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D327" s="2" t="s">
         <v>242</v>
-      </c>
-      <c r="D327" s="2" t="s">
-        <v>243</v>
       </c>
       <c r="E327" s="2">
         <v>82.0</v>
@@ -3949,17 +3946,17 @@
     </row>
     <row r="328" ht="12.75" customHeight="1">
       <c r="C328" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="329" ht="12.75" customHeight="1">
       <c r="C329" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="330" ht="12.75" customHeight="1">
       <c r="C330" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="331" ht="12.75" customHeight="1">
@@ -3967,10 +3964,10 @@
         <v>5.0</v>
       </c>
       <c r="C331" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D331" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="D331" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="E331" s="2">
         <v>83.0</v>
@@ -3978,17 +3975,17 @@
     </row>
     <row r="332" ht="12.75" customHeight="1">
       <c r="C332" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="333" ht="12.75" customHeight="1">
       <c r="C333" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="334" ht="12.75" customHeight="1">
       <c r="C334" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="335" ht="12.75" customHeight="1">
@@ -3996,10 +3993,10 @@
         <v>7.0</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E335" s="2">
         <v>84.0</v>
@@ -4007,17 +4004,17 @@
     </row>
     <row r="336" ht="12.75" customHeight="1">
       <c r="C336" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="337" ht="12.75" customHeight="1">
       <c r="C337" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="338" ht="12.75" customHeight="1">
       <c r="C338" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="339" ht="12.75" customHeight="1">
@@ -4025,10 +4022,10 @@
         <v>6.0</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E339" s="2">
         <v>85.0</v>
@@ -4036,17 +4033,17 @@
     </row>
     <row r="340" ht="12.75" customHeight="1">
       <c r="C340" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="341" ht="12.75" customHeight="1">
       <c r="C341" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="342" ht="12.75" customHeight="1">
       <c r="C342" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="343" ht="12.75" customHeight="1">
@@ -4057,10 +4054,10 @@
         <v>8.0</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E343" s="2">
         <v>86.0</v>
@@ -4071,17 +4068,17 @@
     </row>
     <row r="344" ht="12.75" customHeight="1">
       <c r="C344" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="345" ht="12.75" customHeight="1">
       <c r="C345" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="346" ht="12.75" customHeight="1">
       <c r="C346" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="347" ht="12.75" customHeight="1">
@@ -4089,10 +4086,10 @@
         <v>9.0</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E347" s="2">
         <v>87.0</v>
@@ -4100,17 +4097,17 @@
     </row>
     <row r="348" ht="12.75" customHeight="1">
       <c r="C348" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="349" ht="12.75" customHeight="1">
       <c r="C349" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="350" ht="12.75" customHeight="1">
       <c r="C350" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="351" ht="12.75" customHeight="1">
@@ -4118,10 +4115,10 @@
         <v>10.0</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E351" s="2">
         <v>88.0</v>
@@ -4129,28 +4126,28 @@
     </row>
     <row r="352" ht="12.75" customHeight="1">
       <c r="C352" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="353" ht="12.75" customHeight="1">
       <c r="C353" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="354" ht="12.75" customHeight="1">
       <c r="C354" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="355" ht="12.75" customHeight="1">
       <c r="B355" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C355" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="C355" s="2" t="s">
-        <v>253</v>
-      </c>
       <c r="D355" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E355" s="2">
         <v>89.0</v>
@@ -4158,28 +4155,28 @@
     </row>
     <row r="356" ht="12.75" customHeight="1">
       <c r="C356" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="357" ht="12.75" customHeight="1">
       <c r="C357" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="358" ht="12.75" customHeight="1">
       <c r="C358" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="359" ht="12.75" customHeight="1">
       <c r="B359" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C359" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D359" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="D359" s="2" t="s">
-        <v>254</v>
       </c>
       <c r="E359" s="2">
         <v>90.0</v>
@@ -4187,17 +4184,17 @@
     </row>
     <row r="360" ht="12.75" customHeight="1">
       <c r="C360" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="361" ht="12.75" customHeight="1">
       <c r="C361" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="362" ht="12.75" customHeight="1">
       <c r="C362" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="363" ht="12.75" customHeight="1">
@@ -4205,13 +4202,13 @@
         <v>19.0</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E363" s="2">
         <v>91.0</v>
@@ -4222,28 +4219,28 @@
     </row>
     <row r="364" ht="12.75" customHeight="1">
       <c r="C364" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="365" ht="12.75" customHeight="1">
       <c r="C365" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="366" ht="12.75" customHeight="1">
       <c r="C366" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="367" ht="12.75" customHeight="1">
       <c r="B367" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E367" s="2">
         <v>92.0</v>
@@ -4251,28 +4248,28 @@
     </row>
     <row r="368" ht="12.75" customHeight="1">
       <c r="C368" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="369" ht="12.75" customHeight="1">
       <c r="C369" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="370" ht="12.75" customHeight="1">
       <c r="C370" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="371" ht="12.75" customHeight="1">
       <c r="B371" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D371" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E371" s="2">
         <v>93.0</v>
@@ -4280,28 +4277,28 @@
     </row>
     <row r="372" ht="12.75" customHeight="1">
       <c r="C372" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="373" ht="12.75" customHeight="1">
       <c r="C373" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="374" ht="12.75" customHeight="1">
       <c r="C374" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="375" ht="12.75" customHeight="1">
       <c r="B375" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E375" s="2">
         <v>94.0</v>
@@ -4309,28 +4306,28 @@
     </row>
     <row r="376" ht="12.75" customHeight="1">
       <c r="C376" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="377" ht="12.75" customHeight="1">
       <c r="C377" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="378" ht="12.75" customHeight="1">
       <c r="C378" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="379" ht="12.75" customHeight="1">
       <c r="B379" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C379" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D379" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="D379" s="2" t="s">
-        <v>257</v>
       </c>
       <c r="E379" s="2">
         <v>95.0</v>
@@ -4338,17 +4335,17 @@
     </row>
     <row r="380" ht="12.75" customHeight="1">
       <c r="C380" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="381" ht="12.75" customHeight="1">
       <c r="C381" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="382" ht="12.75" customHeight="1">
       <c r="C382" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="383" ht="12.75" customHeight="1">
@@ -4356,13 +4353,13 @@
         <v>20.0</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D383" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E383" s="2">
         <v>96.0</v>
@@ -4373,22 +4370,22 @@
     </row>
     <row r="384" ht="12.75" customHeight="1">
       <c r="C384" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="385" ht="12.75" customHeight="1">
       <c r="C385" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="386" ht="12.75" customHeight="1">
       <c r="C386" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="387" ht="12.75" customHeight="1">
       <c r="B387" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C387" s="2" t="s">
         <v>77</v>
@@ -4412,12 +4409,12 @@
     </row>
     <row r="390" ht="12.75" customHeight="1">
       <c r="C390" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="391" ht="12.75" customHeight="1">
       <c r="B391" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C391" s="2" t="s">
         <v>77</v>
@@ -4441,12 +4438,12 @@
     </row>
     <row r="394" ht="12.75" customHeight="1">
       <c r="C394" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="395" ht="12.75" customHeight="1">
       <c r="B395" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C395" s="2" t="s">
         <v>77</v>
@@ -4470,12 +4467,12 @@
     </row>
     <row r="398" ht="12.75" customHeight="1">
       <c r="C398" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="399" ht="12.75" customHeight="1">
       <c r="B399" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C399" s="2" t="s">
         <v>77</v>
@@ -4499,7 +4496,7 @@
     </row>
     <row r="402" ht="12.75" customHeight="1">
       <c r="C402" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="403" ht="12.75" customHeight="1">
@@ -4507,7 +4504,7 @@
         <v>21.0</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C403" s="2" t="s">
         <v>77</v>
@@ -4534,18 +4531,18 @@
     </row>
     <row r="406" ht="12.75" customHeight="1">
       <c r="C406" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="407" ht="12.75" customHeight="1">
       <c r="B407" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C407" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D407" s="2" t="s">
         <v>265</v>
-      </c>
-      <c r="C407" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="D407" s="2" t="s">
-        <v>266</v>
       </c>
       <c r="E407" s="2">
         <v>102.0</v>
@@ -4553,22 +4550,22 @@
     </row>
     <row r="408" ht="12.75" customHeight="1">
       <c r="C408" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="409" ht="12.75" customHeight="1">
       <c r="C409" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="410" ht="12.75" customHeight="1">
       <c r="C410" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="411" ht="12.75" customHeight="1">
       <c r="B411" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C411" s="2" t="s">
         <v>77</v>
@@ -4592,18 +4589,18 @@
     </row>
     <row r="414" ht="12.75" customHeight="1">
       <c r="C414" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="415" ht="12.75" customHeight="1">
       <c r="B415" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D415" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E415" s="2">
         <v>104.0</v>
@@ -4611,22 +4608,22 @@
     </row>
     <row r="416" ht="12.75" customHeight="1">
       <c r="C416" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="417" ht="12.75" customHeight="1">
       <c r="C417" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="418" ht="12.75" customHeight="1">
       <c r="C418" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="419" ht="12.75" customHeight="1">
       <c r="B419" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C419" s="2" t="s">
         <v>77</v>
@@ -4650,7 +4647,7 @@
     </row>
     <row r="422" ht="12.75" customHeight="1">
       <c r="C422" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="423" ht="12.75" customHeight="1">
@@ -4658,7 +4655,7 @@
         <v>22.0</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C423" s="2" t="s">
         <v>77</v>
@@ -4685,18 +4682,18 @@
     </row>
     <row r="426" ht="12.75" customHeight="1">
       <c r="C426" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="427" ht="12.75" customHeight="1">
       <c r="B427" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C427" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="C427" s="2" t="s">
+      <c r="D427" s="2" t="s">
         <v>273</v>
-      </c>
-      <c r="D427" s="2" t="s">
-        <v>274</v>
       </c>
       <c r="E427" s="2">
         <v>107.0</v>
@@ -4704,28 +4701,28 @@
     </row>
     <row r="428" ht="12.75" customHeight="1">
       <c r="C428" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="429" ht="12.75" customHeight="1">
       <c r="C429" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="430" ht="12.75" customHeight="1">
       <c r="C430" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="431" ht="12.75" customHeight="1">
       <c r="B431" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C431" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D431" s="2" t="s">
         <v>277</v>
-      </c>
-      <c r="C431" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="D431" s="2" t="s">
-        <v>278</v>
       </c>
       <c r="E431" s="2">
         <v>108.0</v>
@@ -4733,28 +4730,28 @@
     </row>
     <row r="432" ht="12.75" customHeight="1">
       <c r="C432" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="433" ht="12.75" customHeight="1">
       <c r="C433" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="434" ht="12.75" customHeight="1">
       <c r="C434" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="435" ht="12.75" customHeight="1">
       <c r="B435" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E435" s="2">
         <v>109.0</v>
@@ -4762,28 +4759,28 @@
     </row>
     <row r="436" ht="12.75" customHeight="1">
       <c r="C436" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="437" ht="12.75" customHeight="1">
       <c r="C437" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="438" ht="12.75" customHeight="1">
       <c r="C438" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="439" ht="12.75" customHeight="1">
       <c r="B439" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C439" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="C439" s="2" t="s">
+      <c r="D439" s="2" t="s">
         <v>282</v>
-      </c>
-      <c r="D439" s="2" t="s">
-        <v>283</v>
       </c>
       <c r="E439" s="2">
         <v>110.0</v>
@@ -4791,17 +4788,17 @@
     </row>
     <row r="440" ht="12.75" customHeight="1">
       <c r="C440" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="441" ht="12.75" customHeight="1">
       <c r="C441" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="442" ht="12.75" customHeight="1">
       <c r="C442" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="443" ht="12.75" customHeight="1">
@@ -4809,13 +4806,13 @@
         <v>23.0</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E443" s="2">
         <v>111.0</v>
@@ -4826,28 +4823,28 @@
     </row>
     <row r="444" ht="12.75" customHeight="1">
       <c r="C444" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="445" ht="12.75" customHeight="1">
       <c r="C445" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="446" ht="12.75" customHeight="1">
       <c r="C446" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="447" ht="12.75" customHeight="1">
       <c r="B447" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E447" s="2">
         <v>112.0</v>
@@ -4855,28 +4852,28 @@
     </row>
     <row r="448" ht="12.75" customHeight="1">
       <c r="C448" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="449" ht="12.75" customHeight="1">
       <c r="C449" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="450" ht="12.75" customHeight="1">
       <c r="C450" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="451" ht="12.75" customHeight="1">
       <c r="B451" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C451" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C451" s="2" t="s">
+      <c r="D451" s="2" t="s">
         <v>289</v>
-      </c>
-      <c r="D451" s="2" t="s">
-        <v>290</v>
       </c>
       <c r="E451" s="2">
         <v>113.0</v>
@@ -4884,28 +4881,28 @@
     </row>
     <row r="452" ht="12.75" customHeight="1">
       <c r="C452" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="453" ht="12.75" customHeight="1">
       <c r="C453" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="454" ht="12.75" customHeight="1">
       <c r="C454" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="455" ht="12.75" customHeight="1">
       <c r="B455" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E455" s="2">
         <v>114.0</v>
@@ -4913,28 +4910,28 @@
     </row>
     <row r="456" ht="12.75" customHeight="1">
       <c r="C456" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="457" ht="12.75" customHeight="1">
       <c r="C457" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="458" ht="12.75" customHeight="1">
       <c r="C458" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="459" ht="12.75" customHeight="1">
       <c r="B459" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C459" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D459" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="D459" s="2" t="s">
-        <v>291</v>
       </c>
       <c r="E459" s="2">
         <v>116.0</v>
@@ -4942,17 +4939,17 @@
     </row>
     <row r="460" ht="12.75" customHeight="1">
       <c r="C460" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="461" ht="12.75" customHeight="1">
       <c r="C461" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="462" ht="12.75" customHeight="1">
       <c r="C462" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="463" ht="12.75" customHeight="1">
@@ -4960,13 +4957,13 @@
         <v>24.0</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D463" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E463" s="2">
         <v>117.0</v>
@@ -4977,28 +4974,28 @@
     </row>
     <row r="464" ht="12.75" customHeight="1">
       <c r="C464" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="465" ht="12.75" customHeight="1">
       <c r="C465" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="466" ht="12.75" customHeight="1">
       <c r="C466" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="467" ht="12.75" customHeight="1">
       <c r="B467" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C467" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C467" s="2" t="s">
-        <v>300</v>
-      </c>
       <c r="D467" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E467" s="2">
         <v>118.0</v>
@@ -5006,17 +5003,17 @@
     </row>
     <row r="468" ht="12.75" customHeight="1">
       <c r="C468" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="469" ht="12.75" customHeight="1">
       <c r="C469" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="470" ht="12.75" customHeight="1">
       <c r="C470" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="471" ht="12.75" customHeight="1">
@@ -5024,10 +5021,10 @@
         <v>1.0</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D471" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E471" s="2">
         <v>119.0</v>
@@ -5035,17 +5032,17 @@
     </row>
     <row r="472" ht="12.75" customHeight="1">
       <c r="C472" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="473" ht="12.75" customHeight="1">
       <c r="C473" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="474" ht="12.75" customHeight="1">
       <c r="C474" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="475" ht="12.75" customHeight="1">
@@ -5053,10 +5050,10 @@
         <v>3.0</v>
       </c>
       <c r="C475" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D475" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E475" s="2">
         <v>110.0</v>
@@ -5064,17 +5061,17 @@
     </row>
     <row r="476" ht="12.75" customHeight="1">
       <c r="C476" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="477" ht="12.75" customHeight="1">
       <c r="C477" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="478" ht="12.75" customHeight="1">
       <c r="C478" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="479" ht="12.75" customHeight="1">
@@ -5082,10 +5079,10 @@
         <v>2.0</v>
       </c>
       <c r="C479" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D479" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E479" s="2">
         <v>120.0</v>
@@ -5093,17 +5090,17 @@
     </row>
     <row r="480" ht="12.75" customHeight="1">
       <c r="C480" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="481" ht="12.75" customHeight="1">
       <c r="C481" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="482" ht="12.75" customHeight="1">
       <c r="C482" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="483" ht="12.75" customHeight="1">
@@ -5114,10 +5111,10 @@
         <v>4.0</v>
       </c>
       <c r="C483" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D483" s="2" t="s">
         <v>282</v>
-      </c>
-      <c r="D483" s="2" t="s">
-        <v>283</v>
       </c>
       <c r="E483" s="2">
         <v>121.0</v>
@@ -5128,17 +5125,17 @@
     </row>
     <row r="484" ht="12.75" customHeight="1">
       <c r="C484" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="485" ht="12.75" customHeight="1">
       <c r="C485" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="486" ht="12.75" customHeight="1">
       <c r="C486" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="487" ht="12.75" customHeight="1">
@@ -5146,10 +5143,10 @@
         <v>5.0</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D487" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E487" s="2">
         <v>122.0</v>
@@ -5157,17 +5154,17 @@
     </row>
     <row r="488" ht="12.75" customHeight="1">
       <c r="C488" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="489" ht="12.75" customHeight="1">
       <c r="C489" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="490" ht="12.75" customHeight="1">
       <c r="C490" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="491" ht="12.75" customHeight="1">
@@ -5175,10 +5172,10 @@
         <v>6.0</v>
       </c>
       <c r="C491" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D491" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E491" s="2">
         <v>123.0</v>
@@ -5186,22 +5183,22 @@
     </row>
     <row r="492" ht="12.75" customHeight="1">
       <c r="C492" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="493" ht="12.75" customHeight="1">
       <c r="C493" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="494" ht="12.75" customHeight="1">
       <c r="C494" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="495" ht="12.75" customHeight="1">
       <c r="B495" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C495" s="2" t="s">
         <v>77</v>
@@ -5225,18 +5222,18 @@
     </row>
     <row r="498" ht="12.75" customHeight="1">
       <c r="C498" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="499" ht="12.75" customHeight="1">
       <c r="B499" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C499" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="C499" s="2" t="s">
+      <c r="D499" s="2" t="s">
         <v>305</v>
-      </c>
-      <c r="D499" s="2" t="s">
-        <v>306</v>
       </c>
       <c r="E499" s="2">
         <v>125.0</v>
@@ -5244,17 +5241,17 @@
     </row>
     <row r="500" ht="12.75" customHeight="1">
       <c r="C500" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="501" ht="12.75" customHeight="1">
       <c r="C501" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="502" ht="12.75" customHeight="1">
       <c r="C502" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="503" ht="12.75" customHeight="1">
@@ -5262,13 +5259,13 @@
         <v>26.0</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C503" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D503" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E503" s="2">
         <v>126.0</v>
@@ -5279,22 +5276,22 @@
     </row>
     <row r="504" ht="12.75" customHeight="1">
       <c r="C504" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="505" ht="12.75" customHeight="1">
       <c r="C505" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="506" ht="12.75" customHeight="1">
       <c r="C506" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="507" ht="12.75" customHeight="1">
       <c r="B507" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C507" s="2" t="s">
         <v>77</v>
@@ -5308,28 +5305,28 @@
     </row>
     <row r="508" ht="12.75" customHeight="1">
       <c r="C508" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="509" ht="12.75" customHeight="1">
       <c r="C509" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="510" ht="12.75" customHeight="1">
       <c r="C510" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="511" ht="12.75" customHeight="1">
       <c r="B511" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C511" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D511" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E511" s="2">
         <v>128.0</v>
@@ -5337,22 +5334,22 @@
     </row>
     <row r="512" ht="12.75" customHeight="1">
       <c r="C512" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="513" ht="12.75" customHeight="1">
       <c r="C513" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="514" ht="12.75" customHeight="1">
       <c r="C514" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="515" ht="12.75" customHeight="1">
       <c r="B515" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C515" s="2" t="s">
         <v>77</v>
@@ -5366,22 +5363,22 @@
     </row>
     <row r="516" ht="12.75" customHeight="1">
       <c r="C516" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="517" ht="12.75" customHeight="1">
       <c r="C517" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="518" ht="12.75" customHeight="1">
       <c r="C518" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="519" ht="12.75" customHeight="1">
       <c r="B519" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C519" s="2" t="s">
         <v>77</v>
@@ -5395,17 +5392,17 @@
     </row>
     <row r="520" ht="12.75" customHeight="1">
       <c r="C520" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="521" ht="12.75" customHeight="1">
       <c r="C521" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="522" ht="12.75" customHeight="1">
       <c r="C522" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="523" ht="12.75" customHeight="1">
@@ -5413,7 +5410,7 @@
         <v>27.0</v>
       </c>
       <c r="B523" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C523" s="2" t="s">
         <v>77</v>
@@ -5440,12 +5437,12 @@
     </row>
     <row r="526" ht="12.75" customHeight="1">
       <c r="C526" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="527" ht="12.75" customHeight="1">
       <c r="B527" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C527" s="2" t="s">
         <v>77</v>
@@ -5469,12 +5466,12 @@
     </row>
     <row r="530" ht="12.75" customHeight="1">
       <c r="C530" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="531" ht="12.75" customHeight="1">
       <c r="B531" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C531" s="2" t="s">
         <v>77</v>
@@ -5503,13 +5500,13 @@
     </row>
     <row r="535" ht="12.75" customHeight="1">
       <c r="B535" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C535" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D535" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E535" s="2">
         <v>134.0</v>
@@ -5517,7 +5514,7 @@
     </row>
     <row r="536" ht="12.75" customHeight="1">
       <c r="C536" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="537" ht="12.75" customHeight="1">
@@ -5527,12 +5524,12 @@
     </row>
     <row r="538" ht="12.75" customHeight="1">
       <c r="C538" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="539" ht="12.75" customHeight="1">
       <c r="B539" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C539" s="2" t="s">
         <v>77</v>
@@ -5556,7 +5553,7 @@
     </row>
     <row r="542" ht="12.75" customHeight="1">
       <c r="C542" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="543" ht="12.75" customHeight="1">
@@ -5564,7 +5561,7 @@
         <v>28.0</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C543" s="2" t="s">
         <v>77</v>
@@ -5581,28 +5578,28 @@
     </row>
     <row r="544" ht="12.75" customHeight="1">
       <c r="C544" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="545" ht="12.75" customHeight="1">
       <c r="C545" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="546" ht="12.75" customHeight="1">
       <c r="C546" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="547" ht="12.75" customHeight="1">
       <c r="B547" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C547" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D547" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E547" s="2">
         <v>137.0</v>
@@ -5610,22 +5607,22 @@
     </row>
     <row r="548" ht="12.75" customHeight="1">
       <c r="C548" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="549" ht="12.75" customHeight="1">
       <c r="C549" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="550" ht="12.75" customHeight="1">
       <c r="C550" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="551" ht="12.75" customHeight="1">
       <c r="B551" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C551" s="2" t="s">
         <v>77</v>
@@ -5639,28 +5636,28 @@
     </row>
     <row r="552" ht="12.75" customHeight="1">
       <c r="C552" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="553" ht="12.75" customHeight="1">
       <c r="C553" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="554" ht="12.75" customHeight="1">
       <c r="C554" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="555" ht="12.75" customHeight="1">
       <c r="B555" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C555" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D555" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E555" s="2">
         <v>139.0</v>
@@ -5668,28 +5665,28 @@
     </row>
     <row r="556" ht="12.75" customHeight="1">
       <c r="C556" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="557" ht="12.75" customHeight="1">
       <c r="C557" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="558" ht="12.75" customHeight="1">
       <c r="C558" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="559" ht="12.75" customHeight="1">
       <c r="B559" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C559" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D559" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E559" s="2">
         <v>140.0</v>
@@ -5697,17 +5694,17 @@
     </row>
     <row r="560" ht="12.75" customHeight="1">
       <c r="C560" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="561" ht="12.75" customHeight="1">
       <c r="C561" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="562" ht="12.75" customHeight="1">
       <c r="C562" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="563" ht="12.75" customHeight="1">
@@ -5715,10 +5712,10 @@
         <v>29.0</v>
       </c>
       <c r="B563" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C563" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D563" s="2" t="s">
         <v>79</v>
@@ -5747,7 +5744,7 @@
     </row>
     <row r="567" ht="12.75" customHeight="1">
       <c r="B567" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C567" s="2" t="s">
         <v>77</v>
@@ -5771,12 +5768,12 @@
     </row>
     <row r="570" ht="12.75" customHeight="1">
       <c r="C570" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="571" ht="12.75" customHeight="1">
       <c r="B571" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C571" s="2" t="s">
         <v>77</v>
@@ -5800,12 +5797,12 @@
     </row>
     <row r="574" ht="12.75" customHeight="1">
       <c r="C574" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="575" ht="12.75" customHeight="1">
       <c r="B575" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C575" s="2" t="s">
         <v>77</v>
@@ -5829,12 +5826,12 @@
     </row>
     <row r="578" ht="12.75" customHeight="1">
       <c r="C578" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="579" ht="12.75" customHeight="1">
       <c r="B579" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C579" s="2" t="s">
         <v>77</v>
@@ -5858,7 +5855,7 @@
     </row>
     <row r="582" ht="12.75" customHeight="1">
       <c r="C582" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="583" ht="12.75" customHeight="1">
@@ -5866,7 +5863,7 @@
         <v>30.0</v>
       </c>
       <c r="B583" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C583" s="2">
         <v>24.0</v>
@@ -5898,13 +5895,13 @@
     </row>
     <row r="587" ht="12.75" customHeight="1">
       <c r="B587" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C587" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="C587" s="2" t="s">
+      <c r="D587" s="2" t="s">
         <v>331</v>
-      </c>
-      <c r="D587" s="2" t="s">
-        <v>332</v>
       </c>
       <c r="E587" s="2">
         <v>147.0</v>
@@ -5912,28 +5909,28 @@
     </row>
     <row r="588" ht="12.75" customHeight="1">
       <c r="C588" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="589" ht="12.75" customHeight="1">
       <c r="C589" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="590" ht="12.75" customHeight="1">
       <c r="C590" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="591" ht="12.75" customHeight="1">
       <c r="B591" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C591" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D591" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E591" s="2">
         <v>148.0</v>
@@ -5941,28 +5938,28 @@
     </row>
     <row r="592" ht="12.75" customHeight="1">
       <c r="C592" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="593" ht="12.75" customHeight="1">
       <c r="C593" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="594" ht="12.75" customHeight="1">
       <c r="C594" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="595" ht="12.75" customHeight="1">
       <c r="B595" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C595" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="C595" s="2" t="s">
-        <v>338</v>
-      </c>
       <c r="D595" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E595" s="2">
         <v>149.0</v>
@@ -5970,22 +5967,22 @@
     </row>
     <row r="596" ht="12.75" customHeight="1">
       <c r="C596" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="597" ht="12.75" customHeight="1">
       <c r="C597" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="598" ht="12.75" customHeight="1">
       <c r="C598" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="599" ht="12.75" customHeight="1">
       <c r="B599" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C599" s="2">
         <v>3.0</v>
@@ -6017,13 +6014,13 @@
         <v>31.0</v>
       </c>
       <c r="B603" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C603" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="C603" s="2" t="s">
-        <v>344</v>
-      </c>
       <c r="D603" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E603" s="2">
         <v>151.0</v>
@@ -6034,28 +6031,28 @@
     </row>
     <row r="604" ht="12.75" customHeight="1">
       <c r="C604" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="605" ht="12.75" customHeight="1">
       <c r="C605" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="606" ht="12.75" customHeight="1">
       <c r="C606" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="607" ht="12.75" customHeight="1">
       <c r="B607" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C607" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="C607" s="2" t="s">
-        <v>348</v>
-      </c>
       <c r="D607" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E607" s="2">
         <v>152.0</v>
@@ -6063,28 +6060,28 @@
     </row>
     <row r="608" ht="12.75" customHeight="1">
       <c r="C608" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="609" ht="12.75" customHeight="1">
       <c r="C609" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="610" ht="12.75" customHeight="1">
       <c r="C610" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="611" ht="12.75" customHeight="1">
       <c r="B611" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C611" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="C611" s="2" t="s">
+      <c r="D611" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="D611" s="2" t="s">
-        <v>351</v>
       </c>
       <c r="E611" s="2">
         <v>153.0</v>
@@ -6092,22 +6089,22 @@
     </row>
     <row r="612" ht="12.75" customHeight="1">
       <c r="C612" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="613" ht="12.75" customHeight="1">
       <c r="C613" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="614" ht="12.75" customHeight="1">
       <c r="C614" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="615" ht="12.75" customHeight="1">
       <c r="B615" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C615" s="2">
         <v>1.0</v>
@@ -6136,13 +6133,13 @@
     </row>
     <row r="619" ht="12.75" customHeight="1">
       <c r="B619" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C619" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="C619" s="2" t="s">
+      <c r="D619" s="2" t="s">
         <v>356</v>
-      </c>
-      <c r="D619" s="2" t="s">
-        <v>357</v>
       </c>
       <c r="E619" s="2">
         <v>155.0</v>
@@ -6150,17 +6147,17 @@
     </row>
     <row r="620" ht="12.75" customHeight="1">
       <c r="C620" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="621" ht="12.75" customHeight="1">
       <c r="C621" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="622" ht="12.75" customHeight="1">
       <c r="C622" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="623" ht="12.75" customHeight="1">
@@ -6168,13 +6165,13 @@
         <v>32.0</v>
       </c>
       <c r="B623" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C623" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D623" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="C623" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D623" s="2" t="s">
-        <v>361</v>
       </c>
       <c r="E623" s="2">
         <v>156.0</v>
@@ -6185,28 +6182,28 @@
     </row>
     <row r="624" ht="12.75" customHeight="1">
       <c r="C624" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="625" ht="12.75" customHeight="1">
       <c r="C625" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="626" ht="12.75" customHeight="1">
       <c r="C626" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="627" ht="12.75" customHeight="1">
       <c r="B627" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C627" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D627" s="2" t="s">
         <v>333</v>
-      </c>
-      <c r="D627" s="2" t="s">
-        <v>334</v>
       </c>
       <c r="E627" s="2">
         <v>157.0</v>
@@ -6214,28 +6211,28 @@
     </row>
     <row r="628" ht="12.75" customHeight="1">
       <c r="C628" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="629" ht="12.75" customHeight="1">
       <c r="C629" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="630" ht="12.75" customHeight="1">
       <c r="C630" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="631" ht="12.75" customHeight="1">
       <c r="B631" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C631" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D631" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="D631" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="E631" s="2">
         <v>158.0</v>
@@ -6243,28 +6240,28 @@
     </row>
     <row r="632" ht="12.75" customHeight="1">
       <c r="C632" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="633" ht="12.75" customHeight="1">
       <c r="C633" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="634" ht="12.75" customHeight="1">
       <c r="C634" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="635" ht="12.75" customHeight="1">
       <c r="B635" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C635" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D635" s="2" t="s">
         <v>365</v>
-      </c>
-      <c r="C635" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="D635" s="2" t="s">
-        <v>366</v>
       </c>
       <c r="E635" s="2">
         <v>159.0</v>
@@ -6272,28 +6269,28 @@
     </row>
     <row r="636" ht="12.75" customHeight="1">
       <c r="C636" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="637" ht="12.75" customHeight="1">
       <c r="C637" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="638" ht="12.75" customHeight="1">
       <c r="C638" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="639" ht="12.75" customHeight="1">
       <c r="B639" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C639" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="C639" s="2" t="s">
+      <c r="D639" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="D639" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="E639" s="2">
         <v>160.0</v>
@@ -6301,17 +6298,17 @@
     </row>
     <row r="640" ht="12.75" customHeight="1">
       <c r="C640" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="641" ht="12.75" customHeight="1">
       <c r="C641" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="642" ht="12.75" customHeight="1">
       <c r="C642" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="643" ht="12.75" customHeight="1"/>

--- a/English1.xlsx
+++ b/English1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="401">
   <si>
     <t>id</t>
   </si>
@@ -764,6 +764,9 @@
   t_es</t>
   </si>
   <si>
+    <t>Which one is 1?</t>
+  </si>
+  <si>
     <t>one</t>
   </si>
   <si>
@@ -776,6 +779,18 @@
     <t>four</t>
   </si>
   <si>
+    <t>Which one is 3?</t>
+  </si>
+  <si>
+    <t>Which one is 4?</t>
+  </si>
+  <si>
+    <t>Which one is 2?</t>
+  </si>
+  <si>
+    <t>Which one is 5?</t>
+  </si>
+  <si>
     <t>six</t>
   </si>
   <si>
@@ -788,24 +803,54 @@
     <t>eight</t>
   </si>
   <si>
+    <t>Which one is 7?</t>
+  </si>
+  <si>
+    <t>Which one is 6?</t>
+  </si>
+  <si>
+    <t>Which one is 8?</t>
+  </si>
+  <si>
+    <t>Which one is 9?</t>
+  </si>
+  <si>
     <t>nine</t>
   </si>
   <si>
     <t>ten</t>
   </si>
   <si>
+    <t>Which one is 10?</t>
+  </si>
+  <si>
+    <t>What do you call a female sibling?</t>
+  </si>
+  <si>
+    <t>queen</t>
+  </si>
+  <si>
     <t>sister</t>
   </si>
   <si>
-    <t>queen</t>
-  </si>
-  <si>
     <t>water</t>
   </si>
   <si>
     <t>brother</t>
   </si>
   <si>
+    <t>What is the clear liquid that we drink to stay hydrated?</t>
+  </si>
+  <si>
+    <t>What is the title of a female ruler or the wife of a king?</t>
+  </si>
+  <si>
+    <t>What do you call a male sibling?</t>
+  </si>
+  <si>
+    <t>Which large flightless bird is the biggest in the world?</t>
+  </si>
+  <si>
     <t>ostrich</t>
   </si>
   <si>
@@ -816,6 +861,15 @@
   </si>
   <si>
     <t>octopus</t>
+  </si>
+  <si>
+    <t>What is a piece of clothing worn on the upper body?</t>
+  </si>
+  <si>
+    <t>What do you wear on your feet to keep them warm before putting on shoes?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which sea creature has eight arms? </t>
   </si>
   <si>
     <t>Fill in the missing letter:
@@ -1050,6 +1104,18 @@
     <t>How many letters are there in the alphabet?</t>
   </si>
   <si>
+    <t>24 letters</t>
+  </si>
+  <si>
+    <t>26 letters</t>
+  </si>
+  <si>
+    <t>25 letters</t>
+  </si>
+  <si>
+    <t>27 letters</t>
+  </si>
+  <si>
     <t>What color is the sky?</t>
   </si>
   <si>
@@ -1089,6 +1155,18 @@
     <t>What is 2 + 2?</t>
   </si>
   <si>
+    <t>It's 3</t>
+  </si>
+  <si>
+    <t>It's 4</t>
+  </si>
+  <si>
+    <t>It's 5</t>
+  </si>
+  <si>
+    <t>It's 6</t>
+  </si>
+  <si>
     <t>Which fruit is red?</t>
   </si>
   <si>
@@ -1123,6 +1201,12 @@
   </si>
   <si>
     <t>What is 1 + 1?</t>
+  </si>
+  <si>
+    <t>It's 1</t>
+  </si>
+  <si>
+    <t>It's 2</t>
   </si>
   <si>
     <t>Which season is hot?</t>
@@ -1186,7 +1270,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color theme="1"/>
@@ -1195,6 +1279,10 @@
     </font>
     <font>
       <sz val="10.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -1218,7 +1306,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1228,6 +1316,9 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1483,13 +1574,13 @@
       <c r="A3" s="2">
         <v>1.0</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E3" s="2">
@@ -1500,28 +1591,28 @@
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1">
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1">
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="2">
@@ -1529,28 +1620,28 @@
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E11" s="2">
@@ -1558,28 +1649,28 @@
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1">
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" ht="12.75" customHeight="1">
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="2">
@@ -1587,28 +1678,28 @@
       </c>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="17" ht="12.75" customHeight="1">
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="18" ht="12.75" customHeight="1">
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="19" ht="12.75" customHeight="1">
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E19" s="2">
@@ -1616,17 +1707,17 @@
       </c>
     </row>
     <row r="20" ht="12.75" customHeight="1">
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="21" ht="12.75" customHeight="1">
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="22" ht="12.75" customHeight="1">
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1634,13 +1725,13 @@
       <c r="A23" s="2">
         <v>2.0</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="2">
@@ -1651,28 +1742,28 @@
       </c>
     </row>
     <row r="24" ht="12.75" customHeight="1">
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="25" ht="12.75" customHeight="1">
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="26" ht="12.75" customHeight="1">
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="27" ht="12.75" customHeight="1">
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E27" s="2">
@@ -1680,28 +1771,28 @@
       </c>
     </row>
     <row r="28" ht="12.75" customHeight="1">
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="29" ht="12.75" customHeight="1">
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="30" ht="12.75" customHeight="1">
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="31" ht="12.75" customHeight="1">
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E31" s="2">
@@ -1709,28 +1800,28 @@
       </c>
     </row>
     <row r="32" ht="12.75" customHeight="1">
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="33" ht="12.75" customHeight="1">
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="34" ht="12.75" customHeight="1">
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="35" ht="12.75" customHeight="1">
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E35" s="2">
@@ -1738,28 +1829,28 @@
       </c>
     </row>
     <row r="36" ht="12.75" customHeight="1">
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="37" ht="12.75" customHeight="1">
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="38" ht="12.75" customHeight="1">
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="2" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="39" ht="12.75" customHeight="1">
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E39" s="2">
@@ -1767,17 +1858,17 @@
       </c>
     </row>
     <row r="40" ht="12.75" customHeight="1">
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="2" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="41" ht="12.75" customHeight="1">
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="42" ht="12.75" customHeight="1">
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="2" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1785,13 +1876,13 @@
       <c r="A43" s="2">
         <v>3.0</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D43" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E43" s="2">
@@ -1802,28 +1893,28 @@
       </c>
     </row>
     <row r="44" ht="12.75" customHeight="1">
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="45" ht="12.75" customHeight="1">
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="46" ht="12.75" customHeight="1">
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="47" ht="12.75" customHeight="1">
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E47" s="2">
@@ -1831,28 +1922,28 @@
       </c>
     </row>
     <row r="48" ht="12.75" customHeight="1">
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="49" ht="12.75" customHeight="1">
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="50" ht="12.75" customHeight="1">
-      <c r="C50" s="3" t="s">
+      <c r="C50" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="51" ht="12.75" customHeight="1">
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="D51" s="2" t="s">
         <v>40</v>
       </c>
       <c r="E51" s="2">
@@ -1860,28 +1951,28 @@
       </c>
     </row>
     <row r="52" ht="12.75" customHeight="1">
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="53" ht="12.75" customHeight="1">
-      <c r="C53" s="3" t="s">
+      <c r="C53" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="54" ht="12.75" customHeight="1">
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="55" ht="12.75" customHeight="1">
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C55" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="D55" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E55" s="2">
@@ -1889,28 +1980,28 @@
       </c>
     </row>
     <row r="56" ht="12.75" customHeight="1">
-      <c r="C56" s="3" t="s">
+      <c r="C56" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="57" ht="12.75" customHeight="1">
-      <c r="C57" s="3" t="s">
+      <c r="C57" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="58" ht="12.75" customHeight="1">
-      <c r="C58" s="3" t="s">
+      <c r="C58" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="59" ht="12.75" customHeight="1">
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C59" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="D59" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E59" s="2">
@@ -1918,17 +2009,17 @@
       </c>
     </row>
     <row r="60" ht="12.75" customHeight="1">
-      <c r="C60" s="3" t="s">
+      <c r="C60" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="61" ht="12.75" customHeight="1">
-      <c r="C61" s="3" t="s">
+      <c r="C61" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="62" ht="12.75" customHeight="1">
-      <c r="C62" s="3" t="s">
+      <c r="C62" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1936,13 +2027,13 @@
       <c r="A63" s="2">
         <v>4.0</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C63" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="D63" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E63" s="2">
@@ -1953,28 +2044,28 @@
       </c>
     </row>
     <row r="64" ht="12.75" customHeight="1">
-      <c r="C64" s="3" t="s">
+      <c r="C64" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="65" ht="12.75" customHeight="1">
-      <c r="C65" s="3" t="s">
+      <c r="C65" s="2" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="66" ht="12.75" customHeight="1">
-      <c r="C66" s="3" t="s">
+      <c r="C66" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="67" ht="12.75" customHeight="1">
-      <c r="B67" s="3" t="s">
+      <c r="B67" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C67" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="D67" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E67" s="2">
@@ -1982,28 +2073,28 @@
       </c>
     </row>
     <row r="68" ht="12.75" customHeight="1">
-      <c r="C68" s="3" t="s">
+      <c r="C68" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="69" ht="12.75" customHeight="1">
-      <c r="C69" s="3" t="s">
+      <c r="C69" s="2" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="70" ht="12.75" customHeight="1">
-      <c r="C70" s="3" t="s">
+      <c r="C70" s="2" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="71" ht="12.75" customHeight="1">
-      <c r="B71" s="3" t="s">
+      <c r="B71" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C71" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="D71" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E71" s="2">
@@ -2011,28 +2102,28 @@
       </c>
     </row>
     <row r="72" ht="12.75" customHeight="1">
-      <c r="C72" s="3" t="s">
+      <c r="C72" s="2" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="73" ht="12.75" customHeight="1">
-      <c r="C73" s="3" t="s">
+      <c r="C73" s="2" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="74" ht="12.75" customHeight="1">
-      <c r="C74" s="3" t="s">
+      <c r="C74" s="2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="75" ht="12.75" customHeight="1">
-      <c r="B75" s="3" t="s">
+      <c r="B75" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C75" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D75" s="3" t="s">
+      <c r="D75" s="2" t="s">
         <v>40</v>
       </c>
       <c r="E75" s="2">
@@ -2040,28 +2131,28 @@
       </c>
     </row>
     <row r="76" ht="12.75" customHeight="1">
-      <c r="C76" s="3" t="s">
+      <c r="C76" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="77" ht="12.75" customHeight="1">
-      <c r="C77" s="3" t="s">
+      <c r="C77" s="2" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="78" ht="12.75" customHeight="1">
-      <c r="C78" s="3" t="s">
+      <c r="C78" s="2" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="79" ht="12.75" customHeight="1">
-      <c r="B79" s="3" t="s">
+      <c r="B79" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C79" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="D79" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E79" s="2">
@@ -2069,17 +2160,17 @@
       </c>
     </row>
     <row r="80" ht="12.75" customHeight="1">
-      <c r="C80" s="3" t="s">
+      <c r="C80" s="2" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="81" ht="12.75" customHeight="1">
-      <c r="C81" s="3" t="s">
+      <c r="C81" s="2" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="82" ht="12.75" customHeight="1">
-      <c r="C82" s="3" t="s">
+      <c r="C82" s="2" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2087,13 +2178,13 @@
       <c r="A83" s="2">
         <v>5.0</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="B83" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C83" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="D83" s="2" t="s">
         <v>67</v>
       </c>
       <c r="E83" s="2">
@@ -2104,28 +2195,28 @@
       </c>
     </row>
     <row r="84" ht="12.75" customHeight="1">
-      <c r="C84" s="3" t="s">
+      <c r="C84" s="2" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="85" ht="12.75" customHeight="1">
-      <c r="C85" s="3" t="s">
+      <c r="C85" s="2" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="86" ht="12.75" customHeight="1">
-      <c r="C86" s="3" t="s">
+      <c r="C86" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="87" ht="12.75" customHeight="1">
-      <c r="B87" s="3" t="s">
+      <c r="B87" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="C87" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D87" s="3" t="s">
+      <c r="D87" s="2" t="s">
         <v>68</v>
       </c>
       <c r="E87" s="2">
@@ -2133,28 +2224,28 @@
       </c>
     </row>
     <row r="88" ht="12.75" customHeight="1">
-      <c r="C88" s="3" t="s">
+      <c r="C88" s="2" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="89" ht="12.75" customHeight="1">
-      <c r="C89" s="3" t="s">
+      <c r="C89" s="2" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="90" ht="12.75" customHeight="1">
-      <c r="C90" s="3" t="s">
+      <c r="C90" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="91" ht="12.75" customHeight="1">
-      <c r="B91" s="3" t="s">
+      <c r="B91" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="C91" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D91" s="3" t="s">
+      <c r="D91" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E91" s="2">
@@ -2162,28 +2253,28 @@
       </c>
     </row>
     <row r="92" ht="12.75" customHeight="1">
-      <c r="C92" s="3" t="s">
+      <c r="C92" s="2" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="93" ht="12.75" customHeight="1">
-      <c r="C93" s="3" t="s">
+      <c r="C93" s="2" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="94" ht="12.75" customHeight="1">
-      <c r="C94" s="3" t="s">
+      <c r="C94" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="95" ht="12.75" customHeight="1">
-      <c r="B95" s="3" t="s">
+      <c r="B95" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="C95" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D95" s="3" t="s">
+      <c r="D95" s="2" t="s">
         <v>70</v>
       </c>
       <c r="E95" s="2">
@@ -2191,28 +2282,28 @@
       </c>
     </row>
     <row r="96" ht="12.75" customHeight="1">
-      <c r="C96" s="3" t="s">
+      <c r="C96" s="2" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="97" ht="12.75" customHeight="1">
-      <c r="C97" s="3" t="s">
+      <c r="C97" s="2" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="98" ht="12.75" customHeight="1">
-      <c r="C98" s="3" t="s">
+      <c r="C98" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="99" ht="12.75" customHeight="1">
-      <c r="B99" s="3" t="s">
+      <c r="B99" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C99" s="3" t="s">
+      <c r="C99" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D99" s="3" t="s">
+      <c r="D99" s="2" t="s">
         <v>75</v>
       </c>
       <c r="E99" s="2">
@@ -2220,17 +2311,17 @@
       </c>
     </row>
     <row r="100" ht="12.75" customHeight="1">
-      <c r="C100" s="3" t="s">
+      <c r="C100" s="2" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="101" ht="12.75" customHeight="1">
-      <c r="C101" s="3" t="s">
+      <c r="C101" s="2" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="102" ht="12.75" customHeight="1">
-      <c r="C102" s="3" t="s">
+      <c r="C102" s="2" t="s">
         <v>75</v>
       </c>
     </row>
@@ -2238,13 +2329,13 @@
       <c r="A103" s="2">
         <v>6.0</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="B103" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="C103" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D103" s="3" t="s">
+      <c r="D103" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E103" s="2">
@@ -2255,28 +2346,28 @@
       </c>
     </row>
     <row r="104" ht="12.75" customHeight="1">
-      <c r="C104" s="3" t="s">
+      <c r="C104" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="105" ht="12.75" customHeight="1">
-      <c r="C105" s="3" t="s">
+      <c r="C105" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="106" ht="12.75" customHeight="1">
-      <c r="C106" s="3" t="s">
+      <c r="C106" s="2" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="107" ht="12.75" customHeight="1">
-      <c r="B107" s="3" t="s">
+      <c r="B107" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C107" s="3" t="s">
+      <c r="C107" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D107" s="3" t="s">
+      <c r="D107" s="2" t="s">
         <v>82</v>
       </c>
       <c r="E107" s="2">
@@ -2284,28 +2375,28 @@
       </c>
     </row>
     <row r="108" ht="12.75" customHeight="1">
-      <c r="C108" s="3" t="s">
+      <c r="C108" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="109" ht="12.75" customHeight="1">
-      <c r="C109" s="3" t="s">
+      <c r="C109" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="110" ht="12.75" customHeight="1">
-      <c r="C110" s="3" t="s">
+      <c r="C110" s="2" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="111" ht="12.75" customHeight="1">
-      <c r="B111" s="3" t="s">
+      <c r="B111" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C111" s="3" t="s">
+      <c r="C111" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D111" s="3" t="s">
+      <c r="D111" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E111" s="2">
@@ -2313,28 +2404,28 @@
       </c>
     </row>
     <row r="112" ht="12.75" customHeight="1">
-      <c r="C112" s="3" t="s">
+      <c r="C112" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="113" ht="12.75" customHeight="1">
-      <c r="C113" s="3" t="s">
+      <c r="C113" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="114" ht="12.75" customHeight="1">
-      <c r="C114" s="3" t="s">
+      <c r="C114" s="2" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="115" ht="12.75" customHeight="1">
-      <c r="B115" s="3" t="s">
+      <c r="B115" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C115" s="3" t="s">
+      <c r="C115" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D115" s="3" t="s">
+      <c r="D115" s="2" t="s">
         <v>85</v>
       </c>
       <c r="E115" s="2">
@@ -2342,28 +2433,28 @@
       </c>
     </row>
     <row r="116" ht="12.75" customHeight="1">
-      <c r="C116" s="3" t="s">
+      <c r="C116" s="2" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="117" ht="12.75" customHeight="1">
-      <c r="C117" s="3" t="s">
+      <c r="C117" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="118" ht="12.75" customHeight="1">
-      <c r="C118" s="3" t="s">
+      <c r="C118" s="2" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="119" ht="12.75" customHeight="1">
-      <c r="B119" s="3" t="s">
+      <c r="B119" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C119" s="3" t="s">
+      <c r="C119" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D119" s="3" t="s">
+      <c r="D119" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E119" s="2">
@@ -2371,17 +2462,17 @@
       </c>
     </row>
     <row r="120" ht="12.75" customHeight="1">
-      <c r="C120" s="3" t="s">
+      <c r="C120" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="121" ht="12.75" customHeight="1">
-      <c r="C121" s="3" t="s">
+      <c r="C121" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="122" ht="12.75" customHeight="1">
-      <c r="C122" s="3" t="s">
+      <c r="C122" s="2" t="s">
         <v>80</v>
       </c>
     </row>
@@ -2389,7 +2480,7 @@
       <c r="A123" s="2">
         <v>7.0</v>
       </c>
-      <c r="B123" s="3" t="s">
+      <c r="B123" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C123" s="2" t="s">
@@ -2406,22 +2497,22 @@
       </c>
     </row>
     <row r="124" ht="12.75" customHeight="1">
-      <c r="C124" s="3" t="s">
+      <c r="C124" s="2" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="125" ht="12.75" customHeight="1">
-      <c r="C125" s="3" t="s">
+      <c r="C125" s="2" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="126" ht="12.75" customHeight="1">
-      <c r="C126" s="3" t="s">
+      <c r="C126" s="2" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="127" ht="12.75" customHeight="1">
-      <c r="B127" s="3" t="s">
+      <c r="B127" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C127" s="2" t="s">
@@ -2435,7 +2526,7 @@
       </c>
     </row>
     <row r="128" ht="12.75" customHeight="1">
-      <c r="C128" s="3" t="s">
+      <c r="C128" s="2" t="s">
         <v>94</v>
       </c>
     </row>
@@ -2445,18 +2536,18 @@
       </c>
     </row>
     <row r="130" ht="12.75" customHeight="1">
-      <c r="C130" s="3" t="s">
+      <c r="C130" s="2" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="131" ht="12.75" customHeight="1">
-      <c r="B131" s="3" t="s">
+      <c r="B131" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C131" s="3" t="s">
+      <c r="C131" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D131" s="3" t="s">
+      <c r="D131" s="2" t="s">
         <v>97</v>
       </c>
       <c r="E131" s="2">
@@ -2469,7 +2560,7 @@
       </c>
     </row>
     <row r="133" ht="12.75" customHeight="1">
-      <c r="C133" s="3" t="s">
+      <c r="C133" s="2" t="s">
         <v>98</v>
       </c>
     </row>
@@ -2479,13 +2570,13 @@
       </c>
     </row>
     <row r="135" ht="12.75" customHeight="1">
-      <c r="B135" s="3" t="s">
+      <c r="B135" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C135" s="3" t="s">
+      <c r="C135" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D135" s="3" t="s">
+      <c r="D135" s="2" t="s">
         <v>101</v>
       </c>
       <c r="E135" s="2">
@@ -2493,28 +2584,28 @@
       </c>
     </row>
     <row r="136" ht="12.75" customHeight="1">
-      <c r="C136" s="3" t="s">
+      <c r="C136" s="2" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="137" ht="12.75" customHeight="1">
-      <c r="C137" s="3" t="s">
+      <c r="C137" s="2" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="138" ht="12.75" customHeight="1">
-      <c r="C138" s="3" t="s">
+      <c r="C138" s="2" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="139" ht="12.75" customHeight="1">
-      <c r="B139" s="3" t="s">
+      <c r="B139" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C139" s="3" t="s">
+      <c r="C139" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D139" s="3" t="s">
+      <c r="D139" s="2" t="s">
         <v>106</v>
       </c>
       <c r="E139" s="2">
@@ -2522,17 +2613,17 @@
       </c>
     </row>
     <row r="140" ht="12.75" customHeight="1">
-      <c r="C140" s="3" t="s">
+      <c r="C140" s="2" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="141" ht="12.75" customHeight="1">
-      <c r="C141" s="3" t="s">
+      <c r="C141" s="2" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="142" ht="12.75" customHeight="1">
-      <c r="C142" s="3" t="s">
+      <c r="C142" s="2" t="s">
         <v>108</v>
       </c>
     </row>
@@ -2540,10 +2631,10 @@
       <c r="A143" s="2">
         <v>8.0</v>
       </c>
-      <c r="B143" s="3" t="s">
+      <c r="B143" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C143" s="3" t="s">
+      <c r="C143" s="2" t="s">
         <v>110</v>
       </c>
       <c r="D143" s="2" t="s">
@@ -2557,7 +2648,7 @@
       </c>
     </row>
     <row r="144" ht="12.75" customHeight="1">
-      <c r="C144" s="3" t="s">
+      <c r="C144" s="2" t="s">
         <v>112</v>
       </c>
     </row>
@@ -2567,12 +2658,12 @@
       </c>
     </row>
     <row r="146" ht="12.75" customHeight="1">
-      <c r="C146" s="3" t="s">
+      <c r="C146" s="2" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="147" ht="12.75" customHeight="1">
-      <c r="B147" s="3" t="s">
+      <c r="B147" s="2" t="s">
         <v>114</v>
       </c>
       <c r="C147" s="2" t="s">
@@ -2591,17 +2682,17 @@
       </c>
     </row>
     <row r="149" ht="12.75" customHeight="1">
-      <c r="C149" s="3" t="s">
+      <c r="C149" s="2" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="150" ht="12.75" customHeight="1">
-      <c r="C150" s="3" t="s">
+      <c r="C150" s="2" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="151" ht="12.75" customHeight="1">
-      <c r="B151" s="3" t="s">
+      <c r="B151" s="2" t="s">
         <v>117</v>
       </c>
       <c r="C151" s="2" t="s">
@@ -2615,7 +2706,7 @@
       </c>
     </row>
     <row r="152" ht="12.75" customHeight="1">
-      <c r="C152" s="3" t="s">
+      <c r="C152" s="2" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2625,15 +2716,15 @@
       </c>
     </row>
     <row r="154" ht="12.75" customHeight="1">
-      <c r="C154" s="3" t="s">
+      <c r="C154" s="2" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="155" ht="12.75" customHeight="1">
-      <c r="B155" s="3" t="s">
+      <c r="B155" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C155" s="3" t="s">
+      <c r="C155" s="2" t="s">
         <v>120</v>
       </c>
       <c r="D155" s="2" t="s">
@@ -2644,7 +2735,7 @@
       </c>
     </row>
     <row r="156" ht="12.75" customHeight="1">
-      <c r="C156" s="3" t="s">
+      <c r="C156" s="2" t="s">
         <v>122</v>
       </c>
     </row>
@@ -2654,15 +2745,15 @@
       </c>
     </row>
     <row r="158" ht="12.75" customHeight="1">
-      <c r="C158" s="3" t="s">
+      <c r="C158" s="2" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="159" ht="12.75" customHeight="1">
-      <c r="B159" s="3" t="s">
+      <c r="B159" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C159" s="3" t="s">
+      <c r="C159" s="2" t="s">
         <v>125</v>
       </c>
       <c r="D159" s="2" t="s">
@@ -2673,7 +2764,7 @@
       </c>
     </row>
     <row r="160" ht="12.75" customHeight="1">
-      <c r="C160" s="3" t="s">
+      <c r="C160" s="2" t="s">
         <v>127</v>
       </c>
     </row>
@@ -2683,7 +2774,7 @@
       </c>
     </row>
     <row r="162" ht="12.75" customHeight="1">
-      <c r="C162" s="3" t="s">
+      <c r="C162" s="2" t="s">
         <v>128</v>
       </c>
     </row>
@@ -2691,7 +2782,7 @@
       <c r="A163" s="2">
         <v>9.0</v>
       </c>
-      <c r="B163" s="3" t="s">
+      <c r="B163" s="2" t="s">
         <v>129</v>
       </c>
       <c r="C163" s="2" t="s">
@@ -2708,25 +2799,25 @@
       </c>
     </row>
     <row r="164" ht="12.75" customHeight="1">
-      <c r="C164" s="3" t="s">
+      <c r="C164" s="2" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="165" ht="12.75" customHeight="1">
-      <c r="C165" s="3" t="s">
+      <c r="C165" s="2" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="166" ht="12.75" customHeight="1">
-      <c r="C166" s="3" t="s">
+      <c r="C166" s="2" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="167" ht="12.75" customHeight="1">
-      <c r="B167" s="3" t="s">
+      <c r="B167" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C167" s="3" t="s">
+      <c r="C167" s="2" t="s">
         <v>130</v>
       </c>
       <c r="D167" s="2" t="s">
@@ -2742,20 +2833,20 @@
       </c>
     </row>
     <row r="169" ht="12.75" customHeight="1">
-      <c r="C169" s="3" t="s">
+      <c r="C169" s="2" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="170" ht="12.75" customHeight="1">
-      <c r="C170" s="3" t="s">
+      <c r="C170" s="2" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="171" ht="12.75" customHeight="1">
-      <c r="B171" s="3" t="s">
+      <c r="B171" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C171" s="3" t="s">
+      <c r="C171" s="2" t="s">
         <v>131</v>
       </c>
       <c r="D171" s="2" t="s">
@@ -2766,12 +2857,12 @@
       </c>
     </row>
     <row r="172" ht="12.75" customHeight="1">
-      <c r="C172" s="3" t="s">
+      <c r="C172" s="2" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="173" ht="12.75" customHeight="1">
-      <c r="C173" s="3" t="s">
+      <c r="C173" s="2" t="s">
         <v>135</v>
       </c>
     </row>
@@ -2781,10 +2872,10 @@
       </c>
     </row>
     <row r="175" ht="12.75" customHeight="1">
-      <c r="B175" s="3" t="s">
+      <c r="B175" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C175" s="3" t="s">
+      <c r="C175" s="2" t="s">
         <v>141</v>
       </c>
       <c r="D175" s="2" t="s">
@@ -2795,7 +2886,7 @@
       </c>
     </row>
     <row r="176" ht="12.75" customHeight="1">
-      <c r="C176" s="3" t="s">
+      <c r="C176" s="2" t="s">
         <v>130</v>
       </c>
     </row>
@@ -2805,15 +2896,15 @@
       </c>
     </row>
     <row r="178" ht="12.75" customHeight="1">
-      <c r="C178" s="3" t="s">
+      <c r="C178" s="2" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="179" ht="12.75" customHeight="1">
-      <c r="B179" s="3" t="s">
+      <c r="B179" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C179" s="3" t="s">
+      <c r="C179" s="2" t="s">
         <v>143</v>
       </c>
       <c r="D179" s="2" t="s">
@@ -2829,12 +2920,12 @@
       </c>
     </row>
     <row r="181" ht="12.75" customHeight="1">
-      <c r="C181" s="3" t="s">
+      <c r="C181" s="2" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="182" ht="12.75" customHeight="1">
-      <c r="C182" s="3" t="s">
+      <c r="C182" s="2" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2842,10 +2933,10 @@
       <c r="A183" s="2">
         <v>10.0</v>
       </c>
-      <c r="B183" s="3" t="s">
+      <c r="B183" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C183" s="3" t="s">
+      <c r="C183" s="2" t="s">
         <v>148</v>
       </c>
       <c r="D183" s="2" t="s">
@@ -2859,7 +2950,7 @@
       </c>
     </row>
     <row r="184" ht="12.75" customHeight="1">
-      <c r="C184" s="3" t="s">
+      <c r="C184" s="2" t="s">
         <v>150</v>
       </c>
     </row>
@@ -2869,12 +2960,12 @@
       </c>
     </row>
     <row r="186" ht="12.75" customHeight="1">
-      <c r="C186" s="3" t="s">
+      <c r="C186" s="2" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="187" ht="12.75" customHeight="1">
-      <c r="B187" s="3" t="s">
+      <c r="B187" s="2" t="s">
         <v>152</v>
       </c>
       <c r="C187" s="2" t="s">
@@ -2888,25 +2979,25 @@
       </c>
     </row>
     <row r="188" ht="12.75" customHeight="1">
-      <c r="C188" s="3" t="s">
+      <c r="C188" s="2" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="189" ht="12.75" customHeight="1">
-      <c r="C189" s="3" t="s">
+      <c r="C189" s="2" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="190" ht="12.75" customHeight="1">
-      <c r="C190" s="3" t="s">
+      <c r="C190" s="2" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="191" ht="12.75" customHeight="1">
-      <c r="B191" s="3" t="s">
+      <c r="B191" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C191" s="3" t="s">
+      <c r="C191" s="2" t="s">
         <v>156</v>
       </c>
       <c r="D191" s="2" t="s">
@@ -2922,17 +3013,17 @@
       </c>
     </row>
     <row r="193" ht="12.75" customHeight="1">
-      <c r="C193" s="3" t="s">
+      <c r="C193" s="2" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="194" ht="12.75" customHeight="1">
-      <c r="C194" s="3" t="s">
+      <c r="C194" s="2" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="195" ht="12.75" customHeight="1">
-      <c r="B195" s="3" t="s">
+      <c r="B195" s="2" t="s">
         <v>158</v>
       </c>
       <c r="C195" s="2" t="s">
@@ -2946,25 +3037,25 @@
       </c>
     </row>
     <row r="196" ht="12.75" customHeight="1">
-      <c r="C196" s="3" t="s">
+      <c r="C196" s="2" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="197" ht="12.75" customHeight="1">
-      <c r="C197" s="3" t="s">
+      <c r="C197" s="2" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="198" ht="12.75" customHeight="1">
-      <c r="C198" s="3" t="s">
+      <c r="C198" s="2" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="199" ht="12.75" customHeight="1">
-      <c r="B199" s="3" t="s">
+      <c r="B199" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C199" s="3" t="s">
+      <c r="C199" s="2" t="s">
         <v>164</v>
       </c>
       <c r="D199" s="2" t="s">
@@ -2975,12 +3066,12 @@
       </c>
     </row>
     <row r="200" ht="12.75" customHeight="1">
-      <c r="C200" s="3" t="s">
+      <c r="C200" s="2" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="201" ht="12.75" customHeight="1">
-      <c r="C201" s="3" t="s">
+      <c r="C201" s="2" t="s">
         <v>167</v>
       </c>
     </row>
@@ -2993,7 +3084,7 @@
       <c r="A203" s="2">
         <v>11.0</v>
       </c>
-      <c r="B203" s="3" t="s">
+      <c r="B203" s="2" t="s">
         <v>168</v>
       </c>
       <c r="C203" s="2" t="s">
@@ -3025,7 +3116,7 @@
       </c>
     </row>
     <row r="207" ht="12.75" customHeight="1">
-      <c r="B207" s="3" t="s">
+      <c r="B207" s="2" t="s">
         <v>173</v>
       </c>
       <c r="C207" s="2" t="s">
@@ -3054,7 +3145,7 @@
       </c>
     </row>
     <row r="211" ht="12.75" customHeight="1">
-      <c r="B211" s="3" t="s">
+      <c r="B211" s="2" t="s">
         <v>178</v>
       </c>
       <c r="C211" s="2" t="s">
@@ -3083,10 +3174,10 @@
       </c>
     </row>
     <row r="215" ht="12.75" customHeight="1">
-      <c r="B215" s="3" t="s">
+      <c r="B215" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C215" s="3" t="s">
+      <c r="C215" s="2" t="s">
         <v>184</v>
       </c>
       <c r="D215" s="2" t="s">
@@ -3097,12 +3188,12 @@
       </c>
     </row>
     <row r="216" ht="12.75" customHeight="1">
-      <c r="C216" s="3" t="s">
+      <c r="C216" s="2" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="217" ht="12.75" customHeight="1">
-      <c r="C217" s="3" t="s">
+      <c r="C217" s="2" t="s">
         <v>187</v>
       </c>
     </row>
@@ -3112,7 +3203,7 @@
       </c>
     </row>
     <row r="219" ht="12.75" customHeight="1">
-      <c r="B219" s="3" t="s">
+      <c r="B219" s="2" t="s">
         <v>188</v>
       </c>
       <c r="C219" s="2" t="s">
@@ -3126,12 +3217,12 @@
       </c>
     </row>
     <row r="220" ht="12.75" customHeight="1">
-      <c r="C220" s="3" t="s">
+      <c r="C220" s="2" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="221" ht="12.75" customHeight="1">
-      <c r="C221" s="3" t="s">
+      <c r="C221" s="2" t="s">
         <v>187</v>
       </c>
     </row>
@@ -3144,7 +3235,7 @@
       <c r="A223" s="2">
         <v>12.0</v>
       </c>
-      <c r="B223" s="3" t="s">
+      <c r="B223" s="2" t="s">
         <v>189</v>
       </c>
       <c r="C223" s="2" t="s">
@@ -3161,7 +3252,7 @@
       </c>
     </row>
     <row r="224" ht="12.75" customHeight="1">
-      <c r="C224" s="3" t="s">
+      <c r="C224" s="2" t="s">
         <v>186</v>
       </c>
     </row>
@@ -3176,7 +3267,7 @@
       </c>
     </row>
     <row r="227" ht="12.75" customHeight="1">
-      <c r="B227" s="3" t="s">
+      <c r="B227" s="2" t="s">
         <v>191</v>
       </c>
       <c r="C227" s="2" t="s">
@@ -3205,7 +3296,7 @@
       </c>
     </row>
     <row r="231" ht="12.75" customHeight="1">
-      <c r="B231" s="3" t="s">
+      <c r="B231" s="2" t="s">
         <v>192</v>
       </c>
       <c r="C231" s="2" t="s">
@@ -3219,7 +3310,7 @@
       </c>
     </row>
     <row r="232" ht="12.75" customHeight="1">
-      <c r="C232" s="3" t="s">
+      <c r="C232" s="2" t="s">
         <v>186</v>
       </c>
     </row>
@@ -3234,7 +3325,7 @@
       </c>
     </row>
     <row r="235" ht="12.75" customHeight="1">
-      <c r="B235" s="3" t="s">
+      <c r="B235" s="2" t="s">
         <v>193</v>
       </c>
       <c r="C235" s="2" t="s">
@@ -3263,7 +3354,7 @@
       </c>
     </row>
     <row r="239" ht="12.75" customHeight="1">
-      <c r="B239" s="3" t="s">
+      <c r="B239" s="2" t="s">
         <v>195</v>
       </c>
       <c r="C239" s="2" t="s">
@@ -3295,7 +3386,7 @@
       <c r="A243" s="2">
         <v>13.0</v>
       </c>
-      <c r="B243" s="3" t="s">
+      <c r="B243" s="2" t="s">
         <v>196</v>
       </c>
       <c r="C243" s="2" t="s">
@@ -3327,7 +3418,7 @@
       </c>
     </row>
     <row r="247" ht="12.75" customHeight="1">
-      <c r="B247" s="3" t="s">
+      <c r="B247" s="2" t="s">
         <v>201</v>
       </c>
       <c r="C247" s="2" t="s">
@@ -3356,7 +3447,7 @@
       </c>
     </row>
     <row r="251" ht="12.75" customHeight="1">
-      <c r="B251" s="3" t="s">
+      <c r="B251" s="2" t="s">
         <v>202</v>
       </c>
       <c r="C251" s="2" t="s">
@@ -3385,7 +3476,7 @@
       </c>
     </row>
     <row r="255" ht="12.75" customHeight="1">
-      <c r="B255" s="3" t="s">
+      <c r="B255" s="2" t="s">
         <v>203</v>
       </c>
       <c r="C255" s="2" t="s">
@@ -3414,7 +3505,7 @@
       </c>
     </row>
     <row r="259" ht="12.75" customHeight="1">
-      <c r="B259" s="3" t="s">
+      <c r="B259" s="2" t="s">
         <v>208</v>
       </c>
       <c r="C259" s="2" t="s">
@@ -3446,7 +3537,7 @@
       <c r="A263" s="2">
         <v>14.0</v>
       </c>
-      <c r="B263" s="3" t="s">
+      <c r="B263" s="2" t="s">
         <v>213</v>
       </c>
       <c r="C263" s="2" t="s">
@@ -3478,7 +3569,7 @@
       </c>
     </row>
     <row r="267" ht="12.75" customHeight="1">
-      <c r="B267" s="3" t="s">
+      <c r="B267" s="2" t="s">
         <v>218</v>
       </c>
       <c r="C267" s="2" t="s">
@@ -3507,7 +3598,7 @@
       </c>
     </row>
     <row r="271" ht="12.75" customHeight="1">
-      <c r="B271" s="3" t="s">
+      <c r="B271" s="2" t="s">
         <v>223</v>
       </c>
       <c r="C271" s="2" t="s">
@@ -3536,7 +3627,7 @@
       </c>
     </row>
     <row r="275" ht="12.75" customHeight="1">
-      <c r="B275" s="3" t="s">
+      <c r="B275" s="2" t="s">
         <v>228</v>
       </c>
       <c r="C275" s="2" t="s">
@@ -3565,7 +3656,7 @@
       </c>
     </row>
     <row r="279" ht="12.75" customHeight="1">
-      <c r="B279" s="3" t="s">
+      <c r="B279" s="2" t="s">
         <v>229</v>
       </c>
       <c r="C279" s="2" t="s">
@@ -3597,7 +3688,7 @@
       <c r="A283" s="2">
         <v>15.0</v>
       </c>
-      <c r="B283" s="3" t="s">
+      <c r="B283" s="2" t="s">
         <v>230</v>
       </c>
       <c r="C283" s="2" t="s">
@@ -3629,7 +3720,7 @@
       </c>
     </row>
     <row r="287" ht="12.75" customHeight="1">
-      <c r="B287" s="3" t="s">
+      <c r="B287" s="2" t="s">
         <v>231</v>
       </c>
       <c r="C287" s="2" t="s">
@@ -3658,7 +3749,7 @@
       </c>
     </row>
     <row r="291" ht="12.75" customHeight="1">
-      <c r="B291" s="3" t="s">
+      <c r="B291" s="2" t="s">
         <v>233</v>
       </c>
       <c r="C291" s="2" t="s">
@@ -3687,7 +3778,7 @@
       </c>
     </row>
     <row r="295" ht="12.75" customHeight="1">
-      <c r="B295" s="3" t="s">
+      <c r="B295" s="2" t="s">
         <v>234</v>
       </c>
       <c r="C295" s="2" t="s">
@@ -3716,7 +3807,7 @@
       </c>
     </row>
     <row r="299" ht="12.75" customHeight="1">
-      <c r="B299" s="3" t="s">
+      <c r="B299" s="2" t="s">
         <v>235</v>
       </c>
       <c r="C299" s="2" t="s">
@@ -3748,7 +3839,7 @@
       <c r="A303" s="2">
         <v>16.0</v>
       </c>
-      <c r="B303" s="3" t="s">
+      <c r="B303" s="2" t="s">
         <v>236</v>
       </c>
       <c r="C303" s="2" t="s">
@@ -3780,7 +3871,7 @@
       </c>
     </row>
     <row r="307" ht="12.75" customHeight="1">
-      <c r="B307" s="3" t="s">
+      <c r="B307" s="2" t="s">
         <v>237</v>
       </c>
       <c r="C307" s="2" t="s">
@@ -3809,7 +3900,7 @@
       </c>
     </row>
     <row r="311" ht="12.75" customHeight="1">
-      <c r="B311" s="3" t="s">
+      <c r="B311" s="2" t="s">
         <v>240</v>
       </c>
       <c r="C311" s="2" t="s">
@@ -3838,14 +3929,14 @@
       </c>
     </row>
     <row r="315" ht="12.75" customHeight="1">
-      <c r="B315" s="3">
-        <v>1.0</v>
+      <c r="B315" s="3" t="s">
+        <v>241</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E315" s="2">
         <v>79.0</v>
@@ -3853,28 +3944,28 @@
     </row>
     <row r="316" ht="12.75" customHeight="1">
       <c r="C316" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="317" ht="12.75" customHeight="1">
       <c r="C317" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="318" ht="12.75" customHeight="1">
       <c r="C318" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="319" ht="12.75" customHeight="1">
+      <c r="B319" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C319" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D319" s="2" t="s">
         <v>244</v>
-      </c>
-    </row>
-    <row r="319" ht="12.75" customHeight="1">
-      <c r="B319" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="C319" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="D319" s="2" t="s">
-        <v>243</v>
       </c>
       <c r="E319" s="2">
         <v>80.0</v>
@@ -3882,31 +3973,31 @@
     </row>
     <row r="320" ht="12.75" customHeight="1">
       <c r="C320" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="321" ht="12.75" customHeight="1">
       <c r="C321" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="322" ht="12.75" customHeight="1">
       <c r="C322" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="323" ht="12.75" customHeight="1">
       <c r="A323" s="2">
         <v>17.0</v>
       </c>
-      <c r="B323" s="3">
-        <v>4.0</v>
+      <c r="B323" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E323" s="2">
         <v>81.0</v>
@@ -3917,28 +4008,28 @@
     </row>
     <row r="324" ht="12.75" customHeight="1">
       <c r="C324" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="325" ht="12.75" customHeight="1">
       <c r="C325" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="326" ht="12.75" customHeight="1">
       <c r="C326" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="327" ht="12.75" customHeight="1">
-      <c r="B327" s="3">
-        <v>2.0</v>
+      <c r="B327" s="4" t="s">
+        <v>248</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E327" s="2">
         <v>82.0</v>
@@ -3946,28 +4037,28 @@
     </row>
     <row r="328" ht="12.75" customHeight="1">
       <c r="C328" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="329" ht="12.75" customHeight="1">
       <c r="C329" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="330" ht="12.75" customHeight="1">
       <c r="C330" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="331" ht="12.75" customHeight="1">
-      <c r="B331" s="3">
-        <v>5.0</v>
+      <c r="B331" s="3" t="s">
+        <v>249</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E331" s="2">
         <v>83.0</v>
@@ -3975,28 +4066,28 @@
     </row>
     <row r="332" ht="12.75" customHeight="1">
       <c r="C332" s="2" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="333" ht="12.75" customHeight="1">
       <c r="C333" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="334" ht="12.75" customHeight="1">
       <c r="C334" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="335" ht="12.75" customHeight="1">
-      <c r="B335" s="3">
-        <v>7.0</v>
+      <c r="B335" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="E335" s="2">
         <v>84.0</v>
@@ -4004,28 +4095,28 @@
     </row>
     <row r="336" ht="12.75" customHeight="1">
       <c r="C336" s="2" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="337" ht="12.75" customHeight="1">
       <c r="C337" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="338" ht="12.75" customHeight="1">
       <c r="C338" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="339" ht="12.75" customHeight="1">
-      <c r="B339" s="3">
-        <v>6.0</v>
+      <c r="B339" s="3" t="s">
+        <v>255</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E339" s="2">
         <v>85.0</v>
@@ -4033,31 +4124,31 @@
     </row>
     <row r="340" ht="12.75" customHeight="1">
       <c r="C340" s="2" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="341" ht="12.75" customHeight="1">
       <c r="C341" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="342" ht="12.75" customHeight="1">
       <c r="C342" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="343" ht="12.75" customHeight="1">
       <c r="A343" s="2">
         <v>18.0</v>
       </c>
-      <c r="B343" s="3">
-        <v>8.0</v>
+      <c r="B343" s="3" t="s">
+        <v>256</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="E343" s="2">
         <v>86.0</v>
@@ -4068,28 +4159,28 @@
     </row>
     <row r="344" ht="12.75" customHeight="1">
       <c r="C344" s="2" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="345" ht="12.75" customHeight="1">
       <c r="C345" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="346" ht="12.75" customHeight="1">
       <c r="C346" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="347" ht="12.75" customHeight="1">
-      <c r="B347" s="3">
-        <v>9.0</v>
+      <c r="B347" s="3" t="s">
+        <v>257</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="E347" s="2">
         <v>87.0</v>
@@ -4097,28 +4188,28 @@
     </row>
     <row r="348" ht="12.75" customHeight="1">
       <c r="C348" s="2" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
     </row>
     <row r="349" ht="12.75" customHeight="1">
       <c r="C349" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="350" ht="12.75" customHeight="1">
       <c r="C350" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="351" ht="12.75" customHeight="1">
+      <c r="B351" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C351" s="2" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="351" ht="12.75" customHeight="1">
-      <c r="B351" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="C351" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="D351" s="2" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="E351" s="2">
         <v>88.0</v>
@@ -4126,28 +4217,28 @@
     </row>
     <row r="352" ht="12.75" customHeight="1">
       <c r="C352" s="2" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
     </row>
     <row r="353" ht="12.75" customHeight="1">
       <c r="C353" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="354" ht="12.75" customHeight="1">
       <c r="C354" s="2" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
     </row>
     <row r="355" ht="12.75" customHeight="1">
-      <c r="B355" s="2" t="s">
-        <v>251</v>
+      <c r="B355" s="3" t="s">
+        <v>261</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="E355" s="2">
         <v>89.0</v>
@@ -4155,28 +4246,28 @@
     </row>
     <row r="356" ht="12.75" customHeight="1">
       <c r="C356" s="2" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="357" ht="12.75" customHeight="1">
       <c r="C357" s="2" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
     </row>
     <row r="358" ht="12.75" customHeight="1">
       <c r="C358" s="2" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
     </row>
     <row r="359" ht="12.75" customHeight="1">
-      <c r="B359" s="2" t="s">
-        <v>253</v>
+      <c r="B359" s="3" t="s">
+        <v>266</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="E359" s="2">
         <v>90.0</v>
@@ -4184,31 +4275,31 @@
     </row>
     <row r="360" ht="12.75" customHeight="1">
       <c r="C360" s="2" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="361" ht="12.75" customHeight="1">
       <c r="C361" s="2" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
     </row>
     <row r="362" ht="12.75" customHeight="1">
       <c r="C362" s="2" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
     </row>
     <row r="363" ht="12.75" customHeight="1">
       <c r="A363" s="2">
         <v>19.0</v>
       </c>
-      <c r="B363" s="2" t="s">
-        <v>252</v>
+      <c r="B363" s="3" t="s">
+        <v>267</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="E363" s="2">
         <v>91.0</v>
@@ -4219,28 +4310,28 @@
     </row>
     <row r="364" ht="12.75" customHeight="1">
       <c r="C364" s="2" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="365" ht="12.75" customHeight="1">
       <c r="C365" s="2" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
     </row>
     <row r="366" ht="12.75" customHeight="1">
       <c r="C366" s="2" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
     </row>
     <row r="367" ht="12.75" customHeight="1">
-      <c r="B367" s="2" t="s">
-        <v>254</v>
+      <c r="B367" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="E367" s="2">
         <v>92.0</v>
@@ -4248,28 +4339,28 @@
     </row>
     <row r="368" ht="12.75" customHeight="1">
       <c r="C368" s="2" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="369" ht="12.75" customHeight="1">
       <c r="C369" s="2" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
     </row>
     <row r="370" ht="12.75" customHeight="1">
       <c r="C370" s="2" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
     </row>
     <row r="371" ht="12.75" customHeight="1">
-      <c r="B371" s="2" t="s">
-        <v>255</v>
+      <c r="B371" s="3" t="s">
+        <v>269</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="D371" s="2" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="E371" s="2">
         <v>93.0</v>
@@ -4277,28 +4368,28 @@
     </row>
     <row r="372" ht="12.75" customHeight="1">
       <c r="C372" s="2" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
     </row>
     <row r="373" ht="12.75" customHeight="1">
       <c r="C373" s="2" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
     </row>
     <row r="374" ht="12.75" customHeight="1">
       <c r="C374" s="2" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
     </row>
     <row r="375" ht="12.75" customHeight="1">
-      <c r="B375" s="2" t="s">
-        <v>257</v>
+      <c r="B375" s="3" t="s">
+        <v>274</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="E375" s="2">
         <v>94.0</v>
@@ -4306,28 +4397,28 @@
     </row>
     <row r="376" ht="12.75" customHeight="1">
       <c r="C376" s="2" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
     </row>
     <row r="377" ht="12.75" customHeight="1">
       <c r="C377" s="2" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
     </row>
     <row r="378" ht="12.75" customHeight="1">
       <c r="C378" s="2" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
     </row>
     <row r="379" ht="12.75" customHeight="1">
-      <c r="B379" s="2" t="s">
-        <v>256</v>
+      <c r="B379" s="3" t="s">
+        <v>275</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="D379" s="2" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="E379" s="2">
         <v>95.0</v>
@@ -4335,31 +4426,31 @@
     </row>
     <row r="380" ht="12.75" customHeight="1">
       <c r="C380" s="2" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
     </row>
     <row r="381" ht="12.75" customHeight="1">
       <c r="C381" s="2" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
     </row>
     <row r="382" ht="12.75" customHeight="1">
       <c r="C382" s="2" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
     </row>
     <row r="383" ht="12.75" customHeight="1">
       <c r="A383" s="2">
         <v>20.0</v>
       </c>
-      <c r="B383" s="2" t="s">
-        <v>258</v>
+      <c r="B383" s="3" t="s">
+        <v>276</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="D383" s="2" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="E383" s="2">
         <v>96.0</v>
@@ -4370,22 +4461,22 @@
     </row>
     <row r="384" ht="12.75" customHeight="1">
       <c r="C384" s="2" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
     </row>
     <row r="385" ht="12.75" customHeight="1">
       <c r="C385" s="2" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
     </row>
     <row r="386" ht="12.75" customHeight="1">
       <c r="C386" s="2" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
     </row>
     <row r="387" ht="12.75" customHeight="1">
-      <c r="B387" s="3" t="s">
-        <v>259</v>
+      <c r="B387" s="2" t="s">
+        <v>277</v>
       </c>
       <c r="C387" s="2" t="s">
         <v>77</v>
@@ -4413,8 +4504,8 @@
       </c>
     </row>
     <row r="391" ht="12.75" customHeight="1">
-      <c r="B391" s="3" t="s">
-        <v>260</v>
+      <c r="B391" s="2" t="s">
+        <v>278</v>
       </c>
       <c r="C391" s="2" t="s">
         <v>77</v>
@@ -4442,8 +4533,8 @@
       </c>
     </row>
     <row r="395" ht="12.75" customHeight="1">
-      <c r="B395" s="3" t="s">
-        <v>261</v>
+      <c r="B395" s="2" t="s">
+        <v>279</v>
       </c>
       <c r="C395" s="2" t="s">
         <v>77</v>
@@ -4471,8 +4562,8 @@
       </c>
     </row>
     <row r="399" ht="12.75" customHeight="1">
-      <c r="B399" s="3" t="s">
-        <v>262</v>
+      <c r="B399" s="2" t="s">
+        <v>280</v>
       </c>
       <c r="C399" s="2" t="s">
         <v>77</v>
@@ -4503,8 +4594,8 @@
       <c r="A403" s="2">
         <v>21.0</v>
       </c>
-      <c r="B403" s="3" t="s">
-        <v>263</v>
+      <c r="B403" s="2" t="s">
+        <v>281</v>
       </c>
       <c r="C403" s="2" t="s">
         <v>77</v>
@@ -4535,14 +4626,14 @@
       </c>
     </row>
     <row r="407" ht="12.75" customHeight="1">
-      <c r="B407" s="3" t="s">
-        <v>264</v>
+      <c r="B407" s="2" t="s">
+        <v>282</v>
       </c>
       <c r="C407" s="2" t="s">
         <v>232</v>
       </c>
       <c r="D407" s="2" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="E407" s="2">
         <v>102.0</v>
@@ -4550,7 +4641,7 @@
     </row>
     <row r="408" ht="12.75" customHeight="1">
       <c r="C408" s="2" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
     </row>
     <row r="409" ht="12.75" customHeight="1">
@@ -4560,12 +4651,12 @@
     </row>
     <row r="410" ht="12.75" customHeight="1">
       <c r="C410" s="2" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
     </row>
     <row r="411" ht="12.75" customHeight="1">
-      <c r="B411" s="3" t="s">
-        <v>267</v>
+      <c r="B411" s="2" t="s">
+        <v>285</v>
       </c>
       <c r="C411" s="2" t="s">
         <v>77</v>
@@ -4593,8 +4684,8 @@
       </c>
     </row>
     <row r="415" ht="12.75" customHeight="1">
-      <c r="B415" s="3" t="s">
-        <v>268</v>
+      <c r="B415" s="2" t="s">
+        <v>286</v>
       </c>
       <c r="C415" s="2" t="s">
         <v>232</v>
@@ -4608,7 +4699,7 @@
     </row>
     <row r="416" ht="12.75" customHeight="1">
       <c r="C416" s="2" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
     </row>
     <row r="417" ht="12.75" customHeight="1">
@@ -4618,12 +4709,12 @@
     </row>
     <row r="418" ht="12.75" customHeight="1">
       <c r="C418" s="2" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
     </row>
     <row r="419" ht="12.75" customHeight="1">
-      <c r="B419" s="3" t="s">
-        <v>269</v>
+      <c r="B419" s="2" t="s">
+        <v>287</v>
       </c>
       <c r="C419" s="2" t="s">
         <v>77</v>
@@ -4654,8 +4745,8 @@
       <c r="A423" s="2">
         <v>22.0</v>
       </c>
-      <c r="B423" s="3" t="s">
-        <v>270</v>
+      <c r="B423" s="2" t="s">
+        <v>288</v>
       </c>
       <c r="C423" s="2" t="s">
         <v>77</v>
@@ -4687,13 +4778,13 @@
     </row>
     <row r="427" ht="12.75" customHeight="1">
       <c r="B427" s="2" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="D427" s="2" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="E427" s="2">
         <v>107.0</v>
@@ -4701,28 +4792,28 @@
     </row>
     <row r="428" ht="12.75" customHeight="1">
       <c r="C428" s="2" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
     </row>
     <row r="429" ht="12.75" customHeight="1">
       <c r="C429" s="2" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
     </row>
     <row r="430" ht="12.75" customHeight="1">
       <c r="C430" s="2" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
     </row>
     <row r="431" ht="12.75" customHeight="1">
       <c r="B431" s="2" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="E431" s="2">
         <v>108.0</v>
@@ -4730,28 +4821,28 @@
     </row>
     <row r="432" ht="12.75" customHeight="1">
       <c r="C432" s="2" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
     </row>
     <row r="433" ht="12.75" customHeight="1">
       <c r="C433" s="2" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
     </row>
     <row r="434" ht="12.75" customHeight="1">
       <c r="C434" s="2" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
     </row>
     <row r="435" ht="12.75" customHeight="1">
       <c r="B435" s="2" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="E435" s="2">
         <v>109.0</v>
@@ -4759,28 +4850,28 @@
     </row>
     <row r="436" ht="12.75" customHeight="1">
       <c r="C436" s="2" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
     </row>
     <row r="437" ht="12.75" customHeight="1">
       <c r="C437" s="2" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="438" ht="12.75" customHeight="1">
       <c r="C438" s="2" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
     </row>
     <row r="439" ht="12.75" customHeight="1">
-      <c r="B439" s="3" t="s">
-        <v>280</v>
+      <c r="B439" s="2" t="s">
+        <v>298</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="E439" s="2">
         <v>110.0</v>
@@ -4788,17 +4879,17 @@
     </row>
     <row r="440" ht="12.75" customHeight="1">
       <c r="C440" s="2" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
     </row>
     <row r="441" ht="12.75" customHeight="1">
       <c r="C441" s="2" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
     </row>
     <row r="442" ht="12.75" customHeight="1">
       <c r="C442" s="2" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
     </row>
     <row r="443" ht="12.75" customHeight="1">
@@ -4806,13 +4897,13 @@
         <v>23.0</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="E443" s="2">
         <v>111.0</v>
@@ -4823,28 +4914,28 @@
     </row>
     <row r="444" ht="12.75" customHeight="1">
       <c r="C444" s="2" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
     </row>
     <row r="445" ht="12.75" customHeight="1">
       <c r="C445" s="2" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="446" ht="12.75" customHeight="1">
       <c r="C446" s="2" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
     </row>
     <row r="447" ht="12.75" customHeight="1">
       <c r="B447" s="2" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="E447" s="2">
         <v>112.0</v>
@@ -4852,28 +4943,28 @@
     </row>
     <row r="448" ht="12.75" customHeight="1">
       <c r="C448" s="2" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
     </row>
     <row r="449" ht="12.75" customHeight="1">
       <c r="C449" s="2" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="450" ht="12.75" customHeight="1">
       <c r="C450" s="2" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
     </row>
     <row r="451" ht="12.75" customHeight="1">
       <c r="B451" s="2" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="E451" s="2">
         <v>113.0</v>
@@ -4881,28 +4972,28 @@
     </row>
     <row r="452" ht="12.75" customHeight="1">
       <c r="C452" s="2" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
     </row>
     <row r="453" ht="12.75" customHeight="1">
       <c r="C453" s="2" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
     </row>
     <row r="454" ht="12.75" customHeight="1">
       <c r="C454" s="2" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
     </row>
     <row r="455" ht="12.75" customHeight="1">
       <c r="B455" s="2" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="E455" s="2">
         <v>114.0</v>
@@ -4910,28 +5001,28 @@
     </row>
     <row r="456" ht="12.75" customHeight="1">
       <c r="C456" s="2" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
     </row>
     <row r="457" ht="12.75" customHeight="1">
       <c r="C457" s="2" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
     </row>
     <row r="458" ht="12.75" customHeight="1">
       <c r="C458" s="2" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
     </row>
     <row r="459" ht="12.75" customHeight="1">
       <c r="B459" s="2" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="E459" s="2">
         <v>116.0</v>
@@ -4939,17 +5030,17 @@
     </row>
     <row r="460" ht="12.75" customHeight="1">
       <c r="C460" s="2" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
     </row>
     <row r="461" ht="12.75" customHeight="1">
       <c r="C461" s="2" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
     </row>
     <row r="462" ht="12.75" customHeight="1">
       <c r="C462" s="2" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
     </row>
     <row r="463" ht="12.75" customHeight="1">
@@ -4957,13 +5048,13 @@
         <v>24.0</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="D463" s="2" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="E463" s="2">
         <v>117.0</v>
@@ -4974,28 +5065,28 @@
     </row>
     <row r="464" ht="12.75" customHeight="1">
       <c r="C464" s="2" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
     </row>
     <row r="465" ht="12.75" customHeight="1">
       <c r="C465" s="2" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
     </row>
     <row r="466" ht="12.75" customHeight="1">
       <c r="C466" s="2" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
     </row>
     <row r="467" ht="12.75" customHeight="1">
       <c r="B467" s="2" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="D467" s="2" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="E467" s="2">
         <v>118.0</v>
@@ -5003,28 +5094,28 @@
     </row>
     <row r="468" ht="12.75" customHeight="1">
       <c r="C468" s="2" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
     </row>
     <row r="469" ht="12.75" customHeight="1">
       <c r="C469" s="2" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
     </row>
     <row r="470" ht="12.75" customHeight="1">
       <c r="C470" s="2" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
     </row>
     <row r="471" ht="12.75" customHeight="1">
-      <c r="B471" s="3">
-        <v>1.0</v>
+      <c r="B471" s="3" t="s">
+        <v>241</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="D471" s="2" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="E471" s="2">
         <v>119.0</v>
@@ -5032,28 +5123,28 @@
     </row>
     <row r="472" ht="12.75" customHeight="1">
       <c r="C472" s="2" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
     </row>
     <row r="473" ht="12.75" customHeight="1">
       <c r="C473" s="2" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
     </row>
     <row r="474" ht="12.75" customHeight="1">
       <c r="C474" s="2" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
     </row>
     <row r="475" ht="12.75" customHeight="1">
-      <c r="B475" s="3">
-        <v>3.0</v>
+      <c r="B475" s="3" t="s">
+        <v>246</v>
       </c>
       <c r="C475" s="2" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="D475" s="2" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E475" s="2">
         <v>110.0</v>
@@ -5061,28 +5152,28 @@
     </row>
     <row r="476" ht="12.75" customHeight="1">
       <c r="C476" s="2" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
     </row>
     <row r="477" ht="12.75" customHeight="1">
       <c r="C477" s="2" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
     </row>
     <row r="478" ht="12.75" customHeight="1">
       <c r="C478" s="2" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
     </row>
     <row r="479" ht="12.75" customHeight="1">
-      <c r="B479" s="3">
-        <v>2.0</v>
+      <c r="B479" s="3" t="s">
+        <v>248</v>
       </c>
       <c r="C479" s="2" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="D479" s="2" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="E479" s="2">
         <v>120.0</v>
@@ -5090,31 +5181,31 @@
     </row>
     <row r="480" ht="12.75" customHeight="1">
       <c r="C480" s="2" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
     </row>
     <row r="481" ht="12.75" customHeight="1">
       <c r="C481" s="2" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
     </row>
     <row r="482" ht="12.75" customHeight="1">
       <c r="C482" s="2" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
     </row>
     <row r="483" ht="12.75" customHeight="1">
       <c r="A483" s="2">
         <v>25.0</v>
       </c>
-      <c r="B483" s="3">
-        <v>4.0</v>
+      <c r="B483" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="D483" s="2" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="E483" s="2">
         <v>121.0</v>
@@ -5125,28 +5216,28 @@
     </row>
     <row r="484" ht="12.75" customHeight="1">
       <c r="C484" s="2" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
     </row>
     <row r="485" ht="12.75" customHeight="1">
       <c r="C485" s="2" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
     </row>
     <row r="486" ht="12.75" customHeight="1">
       <c r="C486" s="2" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
     </row>
     <row r="487" ht="12.75" customHeight="1">
-      <c r="B487" s="3">
-        <v>5.0</v>
+      <c r="B487" s="3" t="s">
+        <v>249</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="D487" s="2" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="E487" s="2">
         <v>122.0</v>
@@ -5154,28 +5245,28 @@
     </row>
     <row r="488" ht="12.75" customHeight="1">
       <c r="C488" s="2" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
     </row>
     <row r="489" ht="12.75" customHeight="1">
       <c r="C489" s="2" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
     </row>
     <row r="490" ht="12.75" customHeight="1">
       <c r="C490" s="2" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
     </row>
     <row r="491" ht="12.75" customHeight="1">
-      <c r="B491" s="3">
-        <v>6.0</v>
+      <c r="B491" s="3" t="s">
+        <v>255</v>
       </c>
       <c r="C491" s="2" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="D491" s="2" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="E491" s="2">
         <v>123.0</v>
@@ -5183,22 +5274,22 @@
     </row>
     <row r="492" ht="12.75" customHeight="1">
       <c r="C492" s="2" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
     </row>
     <row r="493" ht="12.75" customHeight="1">
       <c r="C493" s="2" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
     </row>
     <row r="494" ht="12.75" customHeight="1">
       <c r="C494" s="2" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
     </row>
     <row r="495" ht="12.75" customHeight="1">
-      <c r="B495" s="3" t="s">
-        <v>302</v>
+      <c r="B495" s="2" t="s">
+        <v>320</v>
       </c>
       <c r="C495" s="2" t="s">
         <v>77</v>
@@ -5226,14 +5317,14 @@
       </c>
     </row>
     <row r="499" ht="12.75" customHeight="1">
-      <c r="B499" s="3" t="s">
-        <v>303</v>
+      <c r="B499" s="2" t="s">
+        <v>321</v>
       </c>
       <c r="C499" s="2" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="D499" s="2" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="E499" s="2">
         <v>125.0</v>
@@ -5241,7 +5332,7 @@
     </row>
     <row r="500" ht="12.75" customHeight="1">
       <c r="C500" s="2" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
     </row>
     <row r="501" ht="12.75" customHeight="1">
@@ -5259,13 +5350,13 @@
         <v>26.0</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="C503" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D503" s="2" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="E503" s="2">
         <v>126.0</v>
@@ -5276,22 +5367,22 @@
     </row>
     <row r="504" ht="12.75" customHeight="1">
       <c r="C504" s="2" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
     </row>
     <row r="505" ht="12.75" customHeight="1">
       <c r="C505" s="2" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
     </row>
     <row r="506" ht="12.75" customHeight="1">
       <c r="C506" s="2" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
     </row>
     <row r="507" ht="12.75" customHeight="1">
       <c r="B507" s="2" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="C507" s="2" t="s">
         <v>77</v>
@@ -5305,28 +5396,28 @@
     </row>
     <row r="508" ht="12.75" customHeight="1">
       <c r="C508" s="2" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
     </row>
     <row r="509" ht="12.75" customHeight="1">
       <c r="C509" s="2" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
     </row>
     <row r="510" ht="12.75" customHeight="1">
       <c r="C510" s="2" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
     </row>
     <row r="511" ht="12.75" customHeight="1">
       <c r="B511" s="2" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="C511" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D511" s="2" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="E511" s="2">
         <v>128.0</v>
@@ -5334,22 +5425,22 @@
     </row>
     <row r="512" ht="12.75" customHeight="1">
       <c r="C512" s="2" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
     </row>
     <row r="513" ht="12.75" customHeight="1">
       <c r="C513" s="2" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
     </row>
     <row r="514" ht="12.75" customHeight="1">
       <c r="C514" s="2" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
     </row>
     <row r="515" ht="12.75" customHeight="1">
       <c r="B515" s="2" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="C515" s="2" t="s">
         <v>77</v>
@@ -5363,22 +5454,22 @@
     </row>
     <row r="516" ht="12.75" customHeight="1">
       <c r="C516" s="2" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
     </row>
     <row r="517" ht="12.75" customHeight="1">
       <c r="C517" s="2" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
     </row>
     <row r="518" ht="12.75" customHeight="1">
       <c r="C518" s="2" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
     </row>
     <row r="519" ht="12.75" customHeight="1">
       <c r="B519" s="2" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="C519" s="2" t="s">
         <v>77</v>
@@ -5392,25 +5483,25 @@
     </row>
     <row r="520" ht="12.75" customHeight="1">
       <c r="C520" s="2" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
     </row>
     <row r="521" ht="12.75" customHeight="1">
       <c r="C521" s="2" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
     </row>
     <row r="522" ht="12.75" customHeight="1">
       <c r="C522" s="2" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
     </row>
     <row r="523" ht="12.75" customHeight="1">
       <c r="A523" s="2">
         <v>27.0</v>
       </c>
-      <c r="B523" s="3" t="s">
-        <v>314</v>
+      <c r="B523" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="C523" s="2" t="s">
         <v>77</v>
@@ -5441,8 +5532,8 @@
       </c>
     </row>
     <row r="527" ht="12.75" customHeight="1">
-      <c r="B527" s="3" t="s">
-        <v>315</v>
+      <c r="B527" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="C527" s="2" t="s">
         <v>77</v>
@@ -5470,8 +5561,8 @@
       </c>
     </row>
     <row r="531" ht="12.75" customHeight="1">
-      <c r="B531" s="3" t="s">
-        <v>316</v>
+      <c r="B531" s="2" t="s">
+        <v>334</v>
       </c>
       <c r="C531" s="2" t="s">
         <v>77</v>
@@ -5499,8 +5590,8 @@
       </c>
     </row>
     <row r="535" ht="12.75" customHeight="1">
-      <c r="B535" s="3" t="s">
-        <v>317</v>
+      <c r="B535" s="2" t="s">
+        <v>335</v>
       </c>
       <c r="C535" s="2" t="s">
         <v>239</v>
@@ -5528,8 +5619,8 @@
       </c>
     </row>
     <row r="539" ht="12.75" customHeight="1">
-      <c r="B539" s="3" t="s">
-        <v>318</v>
+      <c r="B539" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="C539" s="2" t="s">
         <v>77</v>
@@ -5561,7 +5652,7 @@
         <v>28.0</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="C543" s="2" t="s">
         <v>77</v>
@@ -5578,28 +5669,28 @@
     </row>
     <row r="544" ht="12.75" customHeight="1">
       <c r="C544" s="2" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
     </row>
     <row r="545" ht="12.75" customHeight="1">
       <c r="C545" s="2" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
     </row>
     <row r="546" ht="12.75" customHeight="1">
       <c r="C546" s="2" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
     </row>
     <row r="547" ht="12.75" customHeight="1">
       <c r="B547" s="2" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="C547" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D547" s="2" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="E547" s="2">
         <v>137.0</v>
@@ -5607,22 +5698,22 @@
     </row>
     <row r="548" ht="12.75" customHeight="1">
       <c r="C548" s="2" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
     </row>
     <row r="549" ht="12.75" customHeight="1">
       <c r="C549" s="2" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
     </row>
     <row r="550" ht="12.75" customHeight="1">
       <c r="C550" s="2" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
     </row>
     <row r="551" ht="12.75" customHeight="1">
       <c r="B551" s="2" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="C551" s="2" t="s">
         <v>77</v>
@@ -5636,28 +5727,28 @@
     </row>
     <row r="552" ht="12.75" customHeight="1">
       <c r="C552" s="2" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
     </row>
     <row r="553" ht="12.75" customHeight="1">
       <c r="C553" s="2" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
     </row>
     <row r="554" ht="12.75" customHeight="1">
       <c r="C554" s="2" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
     </row>
     <row r="555" ht="12.75" customHeight="1">
       <c r="B555" s="2" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="C555" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D555" s="2" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="E555" s="2">
         <v>139.0</v>
@@ -5665,28 +5756,28 @@
     </row>
     <row r="556" ht="12.75" customHeight="1">
       <c r="C556" s="2" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
     </row>
     <row r="557" ht="12.75" customHeight="1">
       <c r="C557" s="2" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
     </row>
     <row r="558" ht="12.75" customHeight="1">
       <c r="C558" s="2" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
     </row>
     <row r="559" ht="12.75" customHeight="1">
       <c r="B559" s="2" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="C559" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D559" s="2" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="E559" s="2">
         <v>140.0</v>
@@ -5694,25 +5785,25 @@
     </row>
     <row r="560" ht="12.75" customHeight="1">
       <c r="C560" s="2" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
     </row>
     <row r="561" ht="12.75" customHeight="1">
       <c r="C561" s="2" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
     </row>
     <row r="562" ht="12.75" customHeight="1">
       <c r="C562" s="2" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
     </row>
     <row r="563" ht="12.75" customHeight="1">
       <c r="A563" s="2">
         <v>29.0</v>
       </c>
-      <c r="B563" s="3" t="s">
-        <v>323</v>
+      <c r="B563" s="2" t="s">
+        <v>341</v>
       </c>
       <c r="C563" s="2" t="s">
         <v>194</v>
@@ -5743,8 +5834,8 @@
       </c>
     </row>
     <row r="567" ht="12.75" customHeight="1">
-      <c r="B567" s="3" t="s">
-        <v>324</v>
+      <c r="B567" s="2" t="s">
+        <v>342</v>
       </c>
       <c r="C567" s="2" t="s">
         <v>77</v>
@@ -5772,8 +5863,8 @@
       </c>
     </row>
     <row r="571" ht="12.75" customHeight="1">
-      <c r="B571" s="3" t="s">
-        <v>325</v>
+      <c r="B571" s="2" t="s">
+        <v>343</v>
       </c>
       <c r="C571" s="2" t="s">
         <v>77</v>
@@ -5801,8 +5892,8 @@
       </c>
     </row>
     <row r="575" ht="12.75" customHeight="1">
-      <c r="B575" s="3" t="s">
-        <v>326</v>
+      <c r="B575" s="2" t="s">
+        <v>344</v>
       </c>
       <c r="C575" s="2" t="s">
         <v>77</v>
@@ -5830,8 +5921,8 @@
       </c>
     </row>
     <row r="579" ht="12.75" customHeight="1">
-      <c r="B579" s="3" t="s">
-        <v>327</v>
+      <c r="B579" s="2" t="s">
+        <v>345</v>
       </c>
       <c r="C579" s="2" t="s">
         <v>77</v>
@@ -5863,13 +5954,13 @@
         <v>30.0</v>
       </c>
       <c r="B583" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="C583" s="2">
-        <v>24.0</v>
-      </c>
-      <c r="D583" s="2">
-        <v>26.0</v>
+        <v>346</v>
+      </c>
+      <c r="C583" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="D583" s="3" t="s">
+        <v>348</v>
       </c>
       <c r="E583" s="2">
         <v>146.0</v>
@@ -5879,29 +5970,29 @@
       </c>
     </row>
     <row r="584" ht="12.75" customHeight="1">
-      <c r="C584" s="2">
-        <v>25.0</v>
+      <c r="C584" s="3" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="585" ht="12.75" customHeight="1">
-      <c r="C585" s="2">
-        <v>26.0</v>
+      <c r="C585" s="3" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="586" ht="12.75" customHeight="1">
-      <c r="C586" s="2">
-        <v>27.0</v>
+      <c r="C586" s="3" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="587" ht="12.75" customHeight="1">
       <c r="B587" s="2" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="C587" s="2" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="D587" s="2" t="s">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="E587" s="2">
         <v>147.0</v>
@@ -5909,22 +6000,22 @@
     </row>
     <row r="588" ht="12.75" customHeight="1">
       <c r="C588" s="2" t="s">
-        <v>331</v>
+        <v>353</v>
       </c>
     </row>
     <row r="589" ht="12.75" customHeight="1">
       <c r="C589" s="2" t="s">
-        <v>332</v>
+        <v>354</v>
       </c>
     </row>
     <row r="590" ht="12.75" customHeight="1">
       <c r="C590" s="2" t="s">
-        <v>333</v>
+        <v>355</v>
       </c>
     </row>
     <row r="591" ht="12.75" customHeight="1">
       <c r="B591" s="2" t="s">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="C591" s="2" t="s">
         <v>153</v>
@@ -5948,18 +6039,18 @@
     </row>
     <row r="594" ht="12.75" customHeight="1">
       <c r="C594" s="2" t="s">
-        <v>335</v>
+        <v>357</v>
       </c>
     </row>
     <row r="595" ht="12.75" customHeight="1">
       <c r="B595" s="2" t="s">
-        <v>336</v>
+        <v>358</v>
       </c>
       <c r="C595" s="2" t="s">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="D595" s="2" t="s">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="E595" s="2">
         <v>149.0</v>
@@ -5967,46 +6058,46 @@
     </row>
     <row r="596" ht="12.75" customHeight="1">
       <c r="C596" s="2" t="s">
-        <v>338</v>
+        <v>360</v>
       </c>
     </row>
     <row r="597" ht="12.75" customHeight="1">
       <c r="C597" s="2" t="s">
-        <v>339</v>
+        <v>361</v>
       </c>
     </row>
     <row r="598" ht="12.75" customHeight="1">
       <c r="C598" s="2" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
     </row>
     <row r="599" ht="12.75" customHeight="1">
       <c r="B599" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="C599" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="D599" s="2">
-        <v>4.0</v>
+        <v>363</v>
+      </c>
+      <c r="C599" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="D599" s="3" t="s">
+        <v>365</v>
       </c>
       <c r="E599" s="2">
         <v>150.0</v>
       </c>
     </row>
     <row r="600" ht="12.75" customHeight="1">
-      <c r="C600" s="2">
-        <v>4.0</v>
+      <c r="C600" s="3" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="601" ht="12.75" customHeight="1">
-      <c r="C601" s="2">
-        <v>5.0</v>
+      <c r="C601" s="3" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="602" ht="12.75" customHeight="1">
-      <c r="C602" s="2">
-        <v>6.0</v>
+      <c r="C602" s="3" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="603" ht="12.75" customHeight="1">
@@ -6014,13 +6105,13 @@
         <v>31.0</v>
       </c>
       <c r="B603" s="2" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="C603" s="2" t="s">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="D603" s="2" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="E603" s="2">
         <v>151.0</v>
@@ -6031,28 +6122,28 @@
     </row>
     <row r="604" ht="12.75" customHeight="1">
       <c r="C604" s="2" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
     </row>
     <row r="605" ht="12.75" customHeight="1">
       <c r="C605" s="2" t="s">
-        <v>344</v>
+        <v>370</v>
       </c>
     </row>
     <row r="606" ht="12.75" customHeight="1">
       <c r="C606" s="2" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
     </row>
     <row r="607" ht="12.75" customHeight="1">
       <c r="B607" s="2" t="s">
-        <v>346</v>
+        <v>372</v>
       </c>
       <c r="C607" s="2" t="s">
-        <v>347</v>
+        <v>373</v>
       </c>
       <c r="D607" s="2" t="s">
-        <v>347</v>
+        <v>373</v>
       </c>
       <c r="E607" s="2">
         <v>152.0</v>
@@ -6075,13 +6166,13 @@
     </row>
     <row r="611" ht="12.75" customHeight="1">
       <c r="B611" s="2" t="s">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="C611" s="2" t="s">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="D611" s="2" t="s">
-        <v>350</v>
+        <v>376</v>
       </c>
       <c r="E611" s="2">
         <v>153.0</v>
@@ -6089,57 +6180,57 @@
     </row>
     <row r="612" ht="12.75" customHeight="1">
       <c r="C612" s="2" t="s">
-        <v>350</v>
+        <v>376</v>
       </c>
     </row>
     <row r="613" ht="12.75" customHeight="1">
       <c r="C613" s="2" t="s">
-        <v>351</v>
+        <v>377</v>
       </c>
     </row>
     <row r="614" ht="12.75" customHeight="1">
       <c r="C614" s="2" t="s">
-        <v>352</v>
+        <v>378</v>
       </c>
     </row>
     <row r="615" ht="12.75" customHeight="1">
       <c r="B615" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="C615" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D615" s="2">
-        <v>2.0</v>
+        <v>379</v>
+      </c>
+      <c r="C615" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="D615" s="3" t="s">
+        <v>381</v>
       </c>
       <c r="E615" s="2">
         <v>154.0</v>
       </c>
     </row>
     <row r="616" ht="12.75" customHeight="1">
-      <c r="C616" s="2">
-        <v>2.0</v>
+      <c r="C616" s="3" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="617" ht="12.75" customHeight="1">
-      <c r="C617" s="2">
-        <v>3.0</v>
+      <c r="C617" s="3" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="618" ht="12.75" customHeight="1">
-      <c r="C618" s="2">
-        <v>4.0</v>
+      <c r="C618" s="3" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="619" ht="12.75" customHeight="1">
       <c r="B619" s="2" t="s">
-        <v>354</v>
+        <v>382</v>
       </c>
       <c r="C619" s="2" t="s">
-        <v>355</v>
+        <v>383</v>
       </c>
       <c r="D619" s="2" t="s">
-        <v>356</v>
+        <v>384</v>
       </c>
       <c r="E619" s="2">
         <v>155.0</v>
@@ -6147,17 +6238,17 @@
     </row>
     <row r="620" ht="12.75" customHeight="1">
       <c r="C620" s="2" t="s">
-        <v>357</v>
+        <v>385</v>
       </c>
     </row>
     <row r="621" ht="12.75" customHeight="1">
       <c r="C621" s="2" t="s">
-        <v>356</v>
+        <v>384</v>
       </c>
     </row>
     <row r="622" ht="12.75" customHeight="1">
       <c r="C622" s="2" t="s">
-        <v>358</v>
+        <v>386</v>
       </c>
     </row>
     <row r="623" ht="12.75" customHeight="1">
@@ -6165,13 +6256,13 @@
         <v>32.0</v>
       </c>
       <c r="B623" s="2" t="s">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="C623" s="2" t="s">
         <v>154</v>
       </c>
       <c r="D623" s="2" t="s">
-        <v>360</v>
+        <v>388</v>
       </c>
       <c r="E623" s="2">
         <v>156.0</v>
@@ -6182,7 +6273,7 @@
     </row>
     <row r="624" ht="12.75" customHeight="1">
       <c r="C624" s="2" t="s">
-        <v>360</v>
+        <v>388</v>
       </c>
     </row>
     <row r="625" ht="12.75" customHeight="1">
@@ -6192,18 +6283,18 @@
     </row>
     <row r="626" ht="12.75" customHeight="1">
       <c r="C626" s="2" t="s">
-        <v>361</v>
+        <v>389</v>
       </c>
     </row>
     <row r="627" ht="12.75" customHeight="1">
       <c r="B627" s="2" t="s">
-        <v>362</v>
+        <v>390</v>
       </c>
       <c r="C627" s="2" t="s">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="D627" s="2" t="s">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="E627" s="2">
         <v>157.0</v>
@@ -6211,22 +6302,22 @@
     </row>
     <row r="628" ht="12.75" customHeight="1">
       <c r="C628" s="2" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
     </row>
     <row r="629" ht="12.75" customHeight="1">
       <c r="C629" s="2" t="s">
-        <v>333</v>
+        <v>355</v>
       </c>
     </row>
     <row r="630" ht="12.75" customHeight="1">
       <c r="C630" s="2" t="s">
-        <v>331</v>
+        <v>353</v>
       </c>
     </row>
     <row r="631" ht="12.75" customHeight="1">
       <c r="B631" s="2" t="s">
-        <v>363</v>
+        <v>391</v>
       </c>
       <c r="C631" s="2" t="s">
         <v>153</v>
@@ -6255,13 +6346,13 @@
     </row>
     <row r="635" ht="12.75" customHeight="1">
       <c r="B635" s="2" t="s">
-        <v>364</v>
+        <v>392</v>
       </c>
       <c r="C635" s="2" t="s">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="D635" s="2" t="s">
-        <v>365</v>
+        <v>393</v>
       </c>
       <c r="E635" s="2">
         <v>159.0</v>
@@ -6269,28 +6360,28 @@
     </row>
     <row r="636" ht="12.75" customHeight="1">
       <c r="C636" s="2" t="s">
-        <v>365</v>
+        <v>393</v>
       </c>
     </row>
     <row r="637" ht="12.75" customHeight="1">
       <c r="C637" s="2" t="s">
-        <v>366</v>
+        <v>394</v>
       </c>
     </row>
     <row r="638" ht="12.75" customHeight="1">
       <c r="C638" s="2" t="s">
-        <v>367</v>
+        <v>395</v>
       </c>
     </row>
     <row r="639" ht="12.75" customHeight="1">
       <c r="B639" s="2" t="s">
-        <v>368</v>
+        <v>396</v>
       </c>
       <c r="C639" s="2" t="s">
-        <v>369</v>
+        <v>397</v>
       </c>
       <c r="D639" s="2" t="s">
-        <v>370</v>
+        <v>398</v>
       </c>
       <c r="E639" s="2">
         <v>160.0</v>
@@ -6298,17 +6389,17 @@
     </row>
     <row r="640" ht="12.75" customHeight="1">
       <c r="C640" s="2" t="s">
-        <v>371</v>
+        <v>399</v>
       </c>
     </row>
     <row r="641" ht="12.75" customHeight="1">
       <c r="C641" s="2" t="s">
-        <v>370</v>
+        <v>398</v>
       </c>
     </row>
     <row r="642" ht="12.75" customHeight="1">
       <c r="C642" s="2" t="s">
-        <v>372</v>
+        <v>400</v>
       </c>
     </row>
     <row r="643" ht="12.75" customHeight="1"/>

--- a/English1.xlsx
+++ b/English1.xlsx
@@ -36,7 +36,7 @@
     <t>correctAnswer</t>
   </si>
   <si>
-    <t>What is the name of a person that starts with the letter 'B'?</t>
+    <t>What is the name of a person that starts with the letter 'B'??</t>
   </si>
   <si>
     <t>Bill</t>
@@ -1270,7 +1270,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color theme="1"/>
@@ -1285,11 +1285,6 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1317,8 +1312,8 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1574,7 +1569,7 @@
       <c r="A3" s="2">
         <v>1.0</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -3929,7 +3924,7 @@
       </c>
     </row>
     <row r="315" ht="12.75" customHeight="1">
-      <c r="B315" s="3" t="s">
+      <c r="B315" s="2" t="s">
         <v>241</v>
       </c>
       <c r="C315" s="2" t="s">
@@ -3958,7 +3953,7 @@
       </c>
     </row>
     <row r="319" ht="12.75" customHeight="1">
-      <c r="B319" s="3" t="s">
+      <c r="B319" s="2" t="s">
         <v>246</v>
       </c>
       <c r="C319" s="2" t="s">
@@ -3990,7 +3985,7 @@
       <c r="A323" s="2">
         <v>17.0</v>
       </c>
-      <c r="B323" s="3" t="s">
+      <c r="B323" s="2" t="s">
         <v>247</v>
       </c>
       <c r="C323" s="2" t="s">
@@ -4051,7 +4046,7 @@
       </c>
     </row>
     <row r="331" ht="12.75" customHeight="1">
-      <c r="B331" s="3" t="s">
+      <c r="B331" s="2" t="s">
         <v>249</v>
       </c>
       <c r="C331" s="2" t="s">
@@ -4080,7 +4075,7 @@
       </c>
     </row>
     <row r="335" ht="12.75" customHeight="1">
-      <c r="B335" s="3" t="s">
+      <c r="B335" s="2" t="s">
         <v>254</v>
       </c>
       <c r="C335" s="2" t="s">
@@ -4109,7 +4104,7 @@
       </c>
     </row>
     <row r="339" ht="12.75" customHeight="1">
-      <c r="B339" s="3" t="s">
+      <c r="B339" s="2" t="s">
         <v>255</v>
       </c>
       <c r="C339" s="2" t="s">
@@ -4141,7 +4136,7 @@
       <c r="A343" s="2">
         <v>18.0</v>
       </c>
-      <c r="B343" s="3" t="s">
+      <c r="B343" s="2" t="s">
         <v>256</v>
       </c>
       <c r="C343" s="2" t="s">
@@ -4173,7 +4168,7 @@
       </c>
     </row>
     <row r="347" ht="12.75" customHeight="1">
-      <c r="B347" s="3" t="s">
+      <c r="B347" s="2" t="s">
         <v>257</v>
       </c>
       <c r="C347" s="2" t="s">
@@ -4202,7 +4197,7 @@
       </c>
     </row>
     <row r="351" ht="12.75" customHeight="1">
-      <c r="B351" s="3" t="s">
+      <c r="B351" s="2" t="s">
         <v>260</v>
       </c>
       <c r="C351" s="2" t="s">
@@ -4231,7 +4226,7 @@
       </c>
     </row>
     <row r="355" ht="12.75" customHeight="1">
-      <c r="B355" s="3" t="s">
+      <c r="B355" s="2" t="s">
         <v>261</v>
       </c>
       <c r="C355" s="2" t="s">
@@ -4260,7 +4255,7 @@
       </c>
     </row>
     <row r="359" ht="12.75" customHeight="1">
-      <c r="B359" s="3" t="s">
+      <c r="B359" s="2" t="s">
         <v>266</v>
       </c>
       <c r="C359" s="2" t="s">
@@ -4292,7 +4287,7 @@
       <c r="A363" s="2">
         <v>19.0</v>
       </c>
-      <c r="B363" s="3" t="s">
+      <c r="B363" s="2" t="s">
         <v>267</v>
       </c>
       <c r="C363" s="2" t="s">
@@ -4324,7 +4319,7 @@
       </c>
     </row>
     <row r="367" ht="12.75" customHeight="1">
-      <c r="B367" s="3" t="s">
+      <c r="B367" s="2" t="s">
         <v>268</v>
       </c>
       <c r="C367" s="2" t="s">
@@ -4353,7 +4348,7 @@
       </c>
     </row>
     <row r="371" ht="12.75" customHeight="1">
-      <c r="B371" s="3" t="s">
+      <c r="B371" s="2" t="s">
         <v>269</v>
       </c>
       <c r="C371" s="2" t="s">
@@ -4382,7 +4377,7 @@
       </c>
     </row>
     <row r="375" ht="12.75" customHeight="1">
-      <c r="B375" s="3" t="s">
+      <c r="B375" s="2" t="s">
         <v>274</v>
       </c>
       <c r="C375" s="2" t="s">
@@ -4411,7 +4406,7 @@
       </c>
     </row>
     <row r="379" ht="12.75" customHeight="1">
-      <c r="B379" s="3" t="s">
+      <c r="B379" s="2" t="s">
         <v>275</v>
       </c>
       <c r="C379" s="2" t="s">
@@ -4443,7 +4438,7 @@
       <c r="A383" s="2">
         <v>20.0</v>
       </c>
-      <c r="B383" s="3" t="s">
+      <c r="B383" s="2" t="s">
         <v>276</v>
       </c>
       <c r="C383" s="2" t="s">
@@ -5108,7 +5103,7 @@
       </c>
     </row>
     <row r="471" ht="12.75" customHeight="1">
-      <c r="B471" s="3" t="s">
+      <c r="B471" s="2" t="s">
         <v>241</v>
       </c>
       <c r="C471" s="2" t="s">
@@ -5137,7 +5132,7 @@
       </c>
     </row>
     <row r="475" ht="12.75" customHeight="1">
-      <c r="B475" s="3" t="s">
+      <c r="B475" s="2" t="s">
         <v>246</v>
       </c>
       <c r="C475" s="2" t="s">
@@ -5166,7 +5161,7 @@
       </c>
     </row>
     <row r="479" ht="12.75" customHeight="1">
-      <c r="B479" s="3" t="s">
+      <c r="B479" s="2" t="s">
         <v>248</v>
       </c>
       <c r="C479" s="2" t="s">
@@ -5198,7 +5193,7 @@
       <c r="A483" s="2">
         <v>25.0</v>
       </c>
-      <c r="B483" s="3" t="s">
+      <c r="B483" s="2" t="s">
         <v>247</v>
       </c>
       <c r="C483" s="2" t="s">
@@ -5230,7 +5225,7 @@
       </c>
     </row>
     <row r="487" ht="12.75" customHeight="1">
-      <c r="B487" s="3" t="s">
+      <c r="B487" s="2" t="s">
         <v>249</v>
       </c>
       <c r="C487" s="2" t="s">
@@ -5259,7 +5254,7 @@
       </c>
     </row>
     <row r="491" ht="12.75" customHeight="1">
-      <c r="B491" s="3" t="s">
+      <c r="B491" s="2" t="s">
         <v>255</v>
       </c>
       <c r="C491" s="2" t="s">
@@ -5956,10 +5951,10 @@
       <c r="B583" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C583" s="3" t="s">
+      <c r="C583" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="D583" s="3" t="s">
+      <c r="D583" s="2" t="s">
         <v>348</v>
       </c>
       <c r="E583" s="2">
@@ -5970,17 +5965,17 @@
       </c>
     </row>
     <row r="584" ht="12.75" customHeight="1">
-      <c r="C584" s="3" t="s">
+      <c r="C584" s="2" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="585" ht="12.75" customHeight="1">
-      <c r="C585" s="3" t="s">
+      <c r="C585" s="2" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="586" ht="12.75" customHeight="1">
-      <c r="C586" s="3" t="s">
+      <c r="C586" s="2" t="s">
         <v>350</v>
       </c>
     </row>
@@ -6075,10 +6070,10 @@
       <c r="B599" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C599" s="3" t="s">
+      <c r="C599" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="D599" s="3" t="s">
+      <c r="D599" s="2" t="s">
         <v>365</v>
       </c>
       <c r="E599" s="2">
@@ -6086,17 +6081,17 @@
       </c>
     </row>
     <row r="600" ht="12.75" customHeight="1">
-      <c r="C600" s="3" t="s">
+      <c r="C600" s="2" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="601" ht="12.75" customHeight="1">
-      <c r="C601" s="3" t="s">
+      <c r="C601" s="2" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="602" ht="12.75" customHeight="1">
-      <c r="C602" s="3" t="s">
+      <c r="C602" s="2" t="s">
         <v>367</v>
       </c>
     </row>
@@ -6197,10 +6192,10 @@
       <c r="B615" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="C615" s="3" t="s">
+      <c r="C615" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="D615" s="3" t="s">
+      <c r="D615" s="2" t="s">
         <v>381</v>
       </c>
       <c r="E615" s="2">
@@ -6208,17 +6203,17 @@
       </c>
     </row>
     <row r="616" ht="12.75" customHeight="1">
-      <c r="C616" s="3" t="s">
+      <c r="C616" s="2" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="617" ht="12.75" customHeight="1">
-      <c r="C617" s="3" t="s">
+      <c r="C617" s="2" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="618" ht="12.75" customHeight="1">
-      <c r="C618" s="3" t="s">
+      <c r="C618" s="2" t="s">
         <v>365</v>
       </c>
     </row>
